--- a/idecba/ipcba_evol.xlsx
+++ b/idecba/ipcba_evol.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\10.32.3.50\Centro_Doc\BANCO DE DATOS\CARPETAS BCO DE DATOS\IPCBA\INDICE MENSUAL BASE 2021 = 100\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\SRV03\Centro_Doc\BANCO DE DATOS\CARPETAS BCO DE DATOS\IPCBA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E1BD39F-EB10-4AAD-A105-203C86621FD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="384" yWindow="384" windowWidth="22392" windowHeight="11604" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="26370" windowHeight="1890"/>
   </bookViews>
   <sheets>
     <sheet name="Evol_gral_estac_reg_resto" sheetId="1" r:id="rId1"/>
@@ -259,13 +258,13 @@
     <t>Instituto de Estadística y Censos de la Ciudad Autónoma de Buenos Aires (Jefatura de Gabinete de Ministros - GCBA). IPCBA.</t>
   </si>
   <si>
-    <t>IPCBA (base 2021 = 100). Evolución del nivel general, estacionales, regulados y resto IPCBA. Índices y variaciones porcentuales respecto del mes anterior. Ciudad de Buenos Aires. Febrero de 2022 / julio de 2026</t>
+    <t>IPCBA (base 2021 = 100). Evolución del nivel general, estacionales, regulados y resto IPCBA. Índices y variaciones porcentuales respecto del mes anterior. Ciudad de Buenos Aires. Febrero de 2022 / agosto de 2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
@@ -2839,14 +2838,17 @@
     <xf numFmtId="0" fontId="1" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="41" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="48" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="48" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="54" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="45" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2866,7 +2868,13 @@
     <xf numFmtId="0" fontId="55" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="55" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="55" fillId="0" borderId="9" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2902,7 +2910,7 @@
     <xf numFmtId="0" fontId="56" fillId="2" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="42" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="17" fontId="44" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2910,37 +2918,41 @@
     </xf>
     <xf numFmtId="0" fontId="40" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="53" fillId="2" borderId="0" xfId="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="54" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="54" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="54" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="54" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="17" fontId="41" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="17" fontId="41" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="56" fillId="0" borderId="6" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="54" fillId="3" borderId="0" xfId="634" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="56" fillId="2" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="54" fillId="3" borderId="0" xfId="634" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="79" fillId="3" borderId="0" xfId="634" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="79" fillId="3" borderId="0" xfId="634" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="40" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="4" fontId="54" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="52" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="52" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="42" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="justify" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="45" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2961,1241 +2973,1241 @@
   </cellXfs>
   <cellStyles count="1489">
     <cellStyle name="20% - Énfasis1" xfId="20" builtinId="30" customBuiltin="1"/>
-    <cellStyle name="20% - Énfasis1 10" xfId="159" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
-    <cellStyle name="20% - Énfasis1 10 2" xfId="454" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
-    <cellStyle name="20% - Énfasis1 10 2 2" xfId="637" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
-    <cellStyle name="20% - Énfasis1 10 3" xfId="636" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
-    <cellStyle name="20% - Énfasis1 11" xfId="173" xr:uid="{00000000-0005-0000-0000-000005000000}"/>
-    <cellStyle name="20% - Énfasis1 11 2" xfId="468" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
-    <cellStyle name="20% - Énfasis1 11 2 2" xfId="639" xr:uid="{00000000-0005-0000-0000-000007000000}"/>
-    <cellStyle name="20% - Énfasis1 11 3" xfId="638" xr:uid="{00000000-0005-0000-0000-000008000000}"/>
-    <cellStyle name="20% - Énfasis1 12" xfId="187" xr:uid="{00000000-0005-0000-0000-000009000000}"/>
-    <cellStyle name="20% - Énfasis1 12 2" xfId="482" xr:uid="{00000000-0005-0000-0000-00000A000000}"/>
-    <cellStyle name="20% - Énfasis1 12 2 2" xfId="641" xr:uid="{00000000-0005-0000-0000-00000B000000}"/>
-    <cellStyle name="20% - Énfasis1 12 3" xfId="640" xr:uid="{00000000-0005-0000-0000-00000C000000}"/>
-    <cellStyle name="20% - Énfasis1 13" xfId="201" xr:uid="{00000000-0005-0000-0000-00000D000000}"/>
-    <cellStyle name="20% - Énfasis1 13 2" xfId="496" xr:uid="{00000000-0005-0000-0000-00000E000000}"/>
-    <cellStyle name="20% - Énfasis1 13 2 2" xfId="643" xr:uid="{00000000-0005-0000-0000-00000F000000}"/>
-    <cellStyle name="20% - Énfasis1 13 3" xfId="642" xr:uid="{00000000-0005-0000-0000-000010000000}"/>
-    <cellStyle name="20% - Énfasis1 14" xfId="215" xr:uid="{00000000-0005-0000-0000-000011000000}"/>
-    <cellStyle name="20% - Énfasis1 14 2" xfId="510" xr:uid="{00000000-0005-0000-0000-000012000000}"/>
-    <cellStyle name="20% - Énfasis1 14 2 2" xfId="645" xr:uid="{00000000-0005-0000-0000-000013000000}"/>
-    <cellStyle name="20% - Énfasis1 14 3" xfId="644" xr:uid="{00000000-0005-0000-0000-000014000000}"/>
-    <cellStyle name="20% - Énfasis1 15" xfId="229" xr:uid="{00000000-0005-0000-0000-000015000000}"/>
-    <cellStyle name="20% - Énfasis1 15 2" xfId="524" xr:uid="{00000000-0005-0000-0000-000016000000}"/>
-    <cellStyle name="20% - Énfasis1 15 2 2" xfId="647" xr:uid="{00000000-0005-0000-0000-000017000000}"/>
-    <cellStyle name="20% - Énfasis1 15 3" xfId="646" xr:uid="{00000000-0005-0000-0000-000018000000}"/>
-    <cellStyle name="20% - Énfasis1 16" xfId="243" xr:uid="{00000000-0005-0000-0000-000019000000}"/>
-    <cellStyle name="20% - Énfasis1 16 2" xfId="538" xr:uid="{00000000-0005-0000-0000-00001A000000}"/>
-    <cellStyle name="20% - Énfasis1 16 2 2" xfId="649" xr:uid="{00000000-0005-0000-0000-00001B000000}"/>
-    <cellStyle name="20% - Énfasis1 16 3" xfId="648" xr:uid="{00000000-0005-0000-0000-00001C000000}"/>
-    <cellStyle name="20% - Énfasis1 17" xfId="257" xr:uid="{00000000-0005-0000-0000-00001D000000}"/>
-    <cellStyle name="20% - Énfasis1 17 2" xfId="552" xr:uid="{00000000-0005-0000-0000-00001E000000}"/>
-    <cellStyle name="20% - Énfasis1 17 2 2" xfId="651" xr:uid="{00000000-0005-0000-0000-00001F000000}"/>
-    <cellStyle name="20% - Énfasis1 17 3" xfId="650" xr:uid="{00000000-0005-0000-0000-000020000000}"/>
-    <cellStyle name="20% - Énfasis1 18" xfId="271" xr:uid="{00000000-0005-0000-0000-000021000000}"/>
-    <cellStyle name="20% - Énfasis1 18 2" xfId="566" xr:uid="{00000000-0005-0000-0000-000022000000}"/>
-    <cellStyle name="20% - Énfasis1 18 2 2" xfId="653" xr:uid="{00000000-0005-0000-0000-000023000000}"/>
-    <cellStyle name="20% - Énfasis1 18 3" xfId="652" xr:uid="{00000000-0005-0000-0000-000024000000}"/>
-    <cellStyle name="20% - Énfasis1 19" xfId="285" xr:uid="{00000000-0005-0000-0000-000025000000}"/>
-    <cellStyle name="20% - Énfasis1 19 2" xfId="580" xr:uid="{00000000-0005-0000-0000-000026000000}"/>
-    <cellStyle name="20% - Énfasis1 19 2 2" xfId="655" xr:uid="{00000000-0005-0000-0000-000027000000}"/>
-    <cellStyle name="20% - Énfasis1 19 3" xfId="654" xr:uid="{00000000-0005-0000-0000-000028000000}"/>
-    <cellStyle name="20% - Énfasis1 2" xfId="47" xr:uid="{00000000-0005-0000-0000-000029000000}"/>
-    <cellStyle name="20% - Énfasis1 2 2" xfId="342" xr:uid="{00000000-0005-0000-0000-00002A000000}"/>
-    <cellStyle name="20% - Énfasis1 2 2 2" xfId="657" xr:uid="{00000000-0005-0000-0000-00002B000000}"/>
-    <cellStyle name="20% - Énfasis1 2 3" xfId="656" xr:uid="{00000000-0005-0000-0000-00002C000000}"/>
-    <cellStyle name="20% - Énfasis1 20" xfId="299" xr:uid="{00000000-0005-0000-0000-00002D000000}"/>
-    <cellStyle name="20% - Énfasis1 20 2" xfId="594" xr:uid="{00000000-0005-0000-0000-00002E000000}"/>
-    <cellStyle name="20% - Énfasis1 20 2 2" xfId="659" xr:uid="{00000000-0005-0000-0000-00002F000000}"/>
-    <cellStyle name="20% - Énfasis1 20 3" xfId="658" xr:uid="{00000000-0005-0000-0000-000030000000}"/>
-    <cellStyle name="20% - Énfasis1 21" xfId="313" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
-    <cellStyle name="20% - Énfasis1 21 2" xfId="608" xr:uid="{00000000-0005-0000-0000-000032000000}"/>
-    <cellStyle name="20% - Énfasis1 21 2 2" xfId="661" xr:uid="{00000000-0005-0000-0000-000033000000}"/>
-    <cellStyle name="20% - Énfasis1 21 3" xfId="660" xr:uid="{00000000-0005-0000-0000-000034000000}"/>
-    <cellStyle name="20% - Énfasis1 22" xfId="622" xr:uid="{00000000-0005-0000-0000-000035000000}"/>
-    <cellStyle name="20% - Énfasis1 22 2" xfId="663" xr:uid="{00000000-0005-0000-0000-000036000000}"/>
-    <cellStyle name="20% - Énfasis1 22 3" xfId="662" xr:uid="{00000000-0005-0000-0000-000037000000}"/>
-    <cellStyle name="20% - Énfasis1 23" xfId="326" xr:uid="{00000000-0005-0000-0000-000038000000}"/>
-    <cellStyle name="20% - Énfasis1 23 2" xfId="664" xr:uid="{00000000-0005-0000-0000-000039000000}"/>
-    <cellStyle name="20% - Énfasis1 24" xfId="635" xr:uid="{00000000-0005-0000-0000-00003A000000}"/>
-    <cellStyle name="20% - Énfasis1 25" xfId="1266" xr:uid="{00000000-0005-0000-0000-00003B000000}"/>
-    <cellStyle name="20% - Énfasis1 26" xfId="1280" xr:uid="{00000000-0005-0000-0000-00003C000000}"/>
-    <cellStyle name="20% - Énfasis1 27" xfId="1294" xr:uid="{00000000-0005-0000-0000-00003D000000}"/>
-    <cellStyle name="20% - Énfasis1 28" xfId="1308" xr:uid="{00000000-0005-0000-0000-00003E000000}"/>
-    <cellStyle name="20% - Énfasis1 29" xfId="1322" xr:uid="{00000000-0005-0000-0000-00003F000000}"/>
-    <cellStyle name="20% - Énfasis1 3" xfId="61" xr:uid="{00000000-0005-0000-0000-000040000000}"/>
-    <cellStyle name="20% - Énfasis1 3 2" xfId="356" xr:uid="{00000000-0005-0000-0000-000041000000}"/>
-    <cellStyle name="20% - Énfasis1 3 2 2" xfId="666" xr:uid="{00000000-0005-0000-0000-000042000000}"/>
-    <cellStyle name="20% - Énfasis1 3 3" xfId="665" xr:uid="{00000000-0005-0000-0000-000043000000}"/>
-    <cellStyle name="20% - Énfasis1 30" xfId="1336" xr:uid="{00000000-0005-0000-0000-000044000000}"/>
-    <cellStyle name="20% - Énfasis1 31" xfId="1350" xr:uid="{00000000-0005-0000-0000-000045000000}"/>
-    <cellStyle name="20% - Énfasis1 32" xfId="1364" xr:uid="{00000000-0005-0000-0000-000046000000}"/>
-    <cellStyle name="20% - Énfasis1 33" xfId="1378" xr:uid="{00000000-0005-0000-0000-000047000000}"/>
-    <cellStyle name="20% - Énfasis1 34" xfId="1392" xr:uid="{00000000-0005-0000-0000-000048000000}"/>
-    <cellStyle name="20% - Énfasis1 35" xfId="1406" xr:uid="{00000000-0005-0000-0000-000049000000}"/>
-    <cellStyle name="20% - Énfasis1 36" xfId="1420" xr:uid="{00000000-0005-0000-0000-00004A000000}"/>
-    <cellStyle name="20% - Énfasis1 37" xfId="1434" xr:uid="{00000000-0005-0000-0000-00004B000000}"/>
-    <cellStyle name="20% - Énfasis1 38" xfId="1448" xr:uid="{00000000-0005-0000-0000-00004C000000}"/>
-    <cellStyle name="20% - Énfasis1 39" xfId="1462" xr:uid="{00000000-0005-0000-0000-00004D000000}"/>
-    <cellStyle name="20% - Énfasis1 4" xfId="75" xr:uid="{00000000-0005-0000-0000-00004E000000}"/>
-    <cellStyle name="20% - Énfasis1 4 2" xfId="370" xr:uid="{00000000-0005-0000-0000-00004F000000}"/>
-    <cellStyle name="20% - Énfasis1 4 2 2" xfId="668" xr:uid="{00000000-0005-0000-0000-000050000000}"/>
-    <cellStyle name="20% - Énfasis1 4 3" xfId="667" xr:uid="{00000000-0005-0000-0000-000051000000}"/>
-    <cellStyle name="20% - Énfasis1 40" xfId="1477" xr:uid="{00000000-0005-0000-0000-000052000000}"/>
-    <cellStyle name="20% - Énfasis1 5" xfId="89" xr:uid="{00000000-0005-0000-0000-000053000000}"/>
-    <cellStyle name="20% - Énfasis1 5 2" xfId="384" xr:uid="{00000000-0005-0000-0000-000054000000}"/>
-    <cellStyle name="20% - Énfasis1 5 2 2" xfId="670" xr:uid="{00000000-0005-0000-0000-000055000000}"/>
-    <cellStyle name="20% - Énfasis1 5 3" xfId="669" xr:uid="{00000000-0005-0000-0000-000056000000}"/>
-    <cellStyle name="20% - Énfasis1 6" xfId="103" xr:uid="{00000000-0005-0000-0000-000057000000}"/>
-    <cellStyle name="20% - Énfasis1 6 2" xfId="398" xr:uid="{00000000-0005-0000-0000-000058000000}"/>
-    <cellStyle name="20% - Énfasis1 6 2 2" xfId="672" xr:uid="{00000000-0005-0000-0000-000059000000}"/>
-    <cellStyle name="20% - Énfasis1 6 3" xfId="671" xr:uid="{00000000-0005-0000-0000-00005A000000}"/>
-    <cellStyle name="20% - Énfasis1 7" xfId="117" xr:uid="{00000000-0005-0000-0000-00005B000000}"/>
-    <cellStyle name="20% - Énfasis1 7 2" xfId="412" xr:uid="{00000000-0005-0000-0000-00005C000000}"/>
-    <cellStyle name="20% - Énfasis1 7 2 2" xfId="674" xr:uid="{00000000-0005-0000-0000-00005D000000}"/>
-    <cellStyle name="20% - Énfasis1 7 3" xfId="673" xr:uid="{00000000-0005-0000-0000-00005E000000}"/>
-    <cellStyle name="20% - Énfasis1 8" xfId="131" xr:uid="{00000000-0005-0000-0000-00005F000000}"/>
-    <cellStyle name="20% - Énfasis1 8 2" xfId="426" xr:uid="{00000000-0005-0000-0000-000060000000}"/>
-    <cellStyle name="20% - Énfasis1 8 2 2" xfId="676" xr:uid="{00000000-0005-0000-0000-000061000000}"/>
-    <cellStyle name="20% - Énfasis1 8 3" xfId="675" xr:uid="{00000000-0005-0000-0000-000062000000}"/>
-    <cellStyle name="20% - Énfasis1 9" xfId="145" xr:uid="{00000000-0005-0000-0000-000063000000}"/>
-    <cellStyle name="20% - Énfasis1 9 2" xfId="440" xr:uid="{00000000-0005-0000-0000-000064000000}"/>
-    <cellStyle name="20% - Énfasis1 9 2 2" xfId="678" xr:uid="{00000000-0005-0000-0000-000065000000}"/>
-    <cellStyle name="20% - Énfasis1 9 3" xfId="677" xr:uid="{00000000-0005-0000-0000-000066000000}"/>
+    <cellStyle name="20% - Énfasis1 10" xfId="159"/>
+    <cellStyle name="20% - Énfasis1 10 2" xfId="454"/>
+    <cellStyle name="20% - Énfasis1 10 2 2" xfId="637"/>
+    <cellStyle name="20% - Énfasis1 10 3" xfId="636"/>
+    <cellStyle name="20% - Énfasis1 11" xfId="173"/>
+    <cellStyle name="20% - Énfasis1 11 2" xfId="468"/>
+    <cellStyle name="20% - Énfasis1 11 2 2" xfId="639"/>
+    <cellStyle name="20% - Énfasis1 11 3" xfId="638"/>
+    <cellStyle name="20% - Énfasis1 12" xfId="187"/>
+    <cellStyle name="20% - Énfasis1 12 2" xfId="482"/>
+    <cellStyle name="20% - Énfasis1 12 2 2" xfId="641"/>
+    <cellStyle name="20% - Énfasis1 12 3" xfId="640"/>
+    <cellStyle name="20% - Énfasis1 13" xfId="201"/>
+    <cellStyle name="20% - Énfasis1 13 2" xfId="496"/>
+    <cellStyle name="20% - Énfasis1 13 2 2" xfId="643"/>
+    <cellStyle name="20% - Énfasis1 13 3" xfId="642"/>
+    <cellStyle name="20% - Énfasis1 14" xfId="215"/>
+    <cellStyle name="20% - Énfasis1 14 2" xfId="510"/>
+    <cellStyle name="20% - Énfasis1 14 2 2" xfId="645"/>
+    <cellStyle name="20% - Énfasis1 14 3" xfId="644"/>
+    <cellStyle name="20% - Énfasis1 15" xfId="229"/>
+    <cellStyle name="20% - Énfasis1 15 2" xfId="524"/>
+    <cellStyle name="20% - Énfasis1 15 2 2" xfId="647"/>
+    <cellStyle name="20% - Énfasis1 15 3" xfId="646"/>
+    <cellStyle name="20% - Énfasis1 16" xfId="243"/>
+    <cellStyle name="20% - Énfasis1 16 2" xfId="538"/>
+    <cellStyle name="20% - Énfasis1 16 2 2" xfId="649"/>
+    <cellStyle name="20% - Énfasis1 16 3" xfId="648"/>
+    <cellStyle name="20% - Énfasis1 17" xfId="257"/>
+    <cellStyle name="20% - Énfasis1 17 2" xfId="552"/>
+    <cellStyle name="20% - Énfasis1 17 2 2" xfId="651"/>
+    <cellStyle name="20% - Énfasis1 17 3" xfId="650"/>
+    <cellStyle name="20% - Énfasis1 18" xfId="271"/>
+    <cellStyle name="20% - Énfasis1 18 2" xfId="566"/>
+    <cellStyle name="20% - Énfasis1 18 2 2" xfId="653"/>
+    <cellStyle name="20% - Énfasis1 18 3" xfId="652"/>
+    <cellStyle name="20% - Énfasis1 19" xfId="285"/>
+    <cellStyle name="20% - Énfasis1 19 2" xfId="580"/>
+    <cellStyle name="20% - Énfasis1 19 2 2" xfId="655"/>
+    <cellStyle name="20% - Énfasis1 19 3" xfId="654"/>
+    <cellStyle name="20% - Énfasis1 2" xfId="47"/>
+    <cellStyle name="20% - Énfasis1 2 2" xfId="342"/>
+    <cellStyle name="20% - Énfasis1 2 2 2" xfId="657"/>
+    <cellStyle name="20% - Énfasis1 2 3" xfId="656"/>
+    <cellStyle name="20% - Énfasis1 20" xfId="299"/>
+    <cellStyle name="20% - Énfasis1 20 2" xfId="594"/>
+    <cellStyle name="20% - Énfasis1 20 2 2" xfId="659"/>
+    <cellStyle name="20% - Énfasis1 20 3" xfId="658"/>
+    <cellStyle name="20% - Énfasis1 21" xfId="313"/>
+    <cellStyle name="20% - Énfasis1 21 2" xfId="608"/>
+    <cellStyle name="20% - Énfasis1 21 2 2" xfId="661"/>
+    <cellStyle name="20% - Énfasis1 21 3" xfId="660"/>
+    <cellStyle name="20% - Énfasis1 22" xfId="622"/>
+    <cellStyle name="20% - Énfasis1 22 2" xfId="663"/>
+    <cellStyle name="20% - Énfasis1 22 3" xfId="662"/>
+    <cellStyle name="20% - Énfasis1 23" xfId="326"/>
+    <cellStyle name="20% - Énfasis1 23 2" xfId="664"/>
+    <cellStyle name="20% - Énfasis1 24" xfId="635"/>
+    <cellStyle name="20% - Énfasis1 25" xfId="1266"/>
+    <cellStyle name="20% - Énfasis1 26" xfId="1280"/>
+    <cellStyle name="20% - Énfasis1 27" xfId="1294"/>
+    <cellStyle name="20% - Énfasis1 28" xfId="1308"/>
+    <cellStyle name="20% - Énfasis1 29" xfId="1322"/>
+    <cellStyle name="20% - Énfasis1 3" xfId="61"/>
+    <cellStyle name="20% - Énfasis1 3 2" xfId="356"/>
+    <cellStyle name="20% - Énfasis1 3 2 2" xfId="666"/>
+    <cellStyle name="20% - Énfasis1 3 3" xfId="665"/>
+    <cellStyle name="20% - Énfasis1 30" xfId="1336"/>
+    <cellStyle name="20% - Énfasis1 31" xfId="1350"/>
+    <cellStyle name="20% - Énfasis1 32" xfId="1364"/>
+    <cellStyle name="20% - Énfasis1 33" xfId="1378"/>
+    <cellStyle name="20% - Énfasis1 34" xfId="1392"/>
+    <cellStyle name="20% - Énfasis1 35" xfId="1406"/>
+    <cellStyle name="20% - Énfasis1 36" xfId="1420"/>
+    <cellStyle name="20% - Énfasis1 37" xfId="1434"/>
+    <cellStyle name="20% - Énfasis1 38" xfId="1448"/>
+    <cellStyle name="20% - Énfasis1 39" xfId="1462"/>
+    <cellStyle name="20% - Énfasis1 4" xfId="75"/>
+    <cellStyle name="20% - Énfasis1 4 2" xfId="370"/>
+    <cellStyle name="20% - Énfasis1 4 2 2" xfId="668"/>
+    <cellStyle name="20% - Énfasis1 4 3" xfId="667"/>
+    <cellStyle name="20% - Énfasis1 40" xfId="1477"/>
+    <cellStyle name="20% - Énfasis1 5" xfId="89"/>
+    <cellStyle name="20% - Énfasis1 5 2" xfId="384"/>
+    <cellStyle name="20% - Énfasis1 5 2 2" xfId="670"/>
+    <cellStyle name="20% - Énfasis1 5 3" xfId="669"/>
+    <cellStyle name="20% - Énfasis1 6" xfId="103"/>
+    <cellStyle name="20% - Énfasis1 6 2" xfId="398"/>
+    <cellStyle name="20% - Énfasis1 6 2 2" xfId="672"/>
+    <cellStyle name="20% - Énfasis1 6 3" xfId="671"/>
+    <cellStyle name="20% - Énfasis1 7" xfId="117"/>
+    <cellStyle name="20% - Énfasis1 7 2" xfId="412"/>
+    <cellStyle name="20% - Énfasis1 7 2 2" xfId="674"/>
+    <cellStyle name="20% - Énfasis1 7 3" xfId="673"/>
+    <cellStyle name="20% - Énfasis1 8" xfId="131"/>
+    <cellStyle name="20% - Énfasis1 8 2" xfId="426"/>
+    <cellStyle name="20% - Énfasis1 8 2 2" xfId="676"/>
+    <cellStyle name="20% - Énfasis1 8 3" xfId="675"/>
+    <cellStyle name="20% - Énfasis1 9" xfId="145"/>
+    <cellStyle name="20% - Énfasis1 9 2" xfId="440"/>
+    <cellStyle name="20% - Énfasis1 9 2 2" xfId="678"/>
+    <cellStyle name="20% - Énfasis1 9 3" xfId="677"/>
     <cellStyle name="20% - Énfasis2" xfId="24" builtinId="34" customBuiltin="1"/>
-    <cellStyle name="20% - Énfasis2 10" xfId="161" xr:uid="{00000000-0005-0000-0000-000068000000}"/>
-    <cellStyle name="20% - Énfasis2 10 2" xfId="456" xr:uid="{00000000-0005-0000-0000-000069000000}"/>
-    <cellStyle name="20% - Énfasis2 10 2 2" xfId="681" xr:uid="{00000000-0005-0000-0000-00006A000000}"/>
-    <cellStyle name="20% - Énfasis2 10 3" xfId="680" xr:uid="{00000000-0005-0000-0000-00006B000000}"/>
-    <cellStyle name="20% - Énfasis2 11" xfId="175" xr:uid="{00000000-0005-0000-0000-00006C000000}"/>
-    <cellStyle name="20% - Énfasis2 11 2" xfId="470" xr:uid="{00000000-0005-0000-0000-00006D000000}"/>
-    <cellStyle name="20% - Énfasis2 11 2 2" xfId="683" xr:uid="{00000000-0005-0000-0000-00006E000000}"/>
-    <cellStyle name="20% - Énfasis2 11 3" xfId="682" xr:uid="{00000000-0005-0000-0000-00006F000000}"/>
-    <cellStyle name="20% - Énfasis2 12" xfId="189" xr:uid="{00000000-0005-0000-0000-000070000000}"/>
-    <cellStyle name="20% - Énfasis2 12 2" xfId="484" xr:uid="{00000000-0005-0000-0000-000071000000}"/>
-    <cellStyle name="20% - Énfasis2 12 2 2" xfId="685" xr:uid="{00000000-0005-0000-0000-000072000000}"/>
-    <cellStyle name="20% - Énfasis2 12 3" xfId="684" xr:uid="{00000000-0005-0000-0000-000073000000}"/>
-    <cellStyle name="20% - Énfasis2 13" xfId="203" xr:uid="{00000000-0005-0000-0000-000074000000}"/>
-    <cellStyle name="20% - Énfasis2 13 2" xfId="498" xr:uid="{00000000-0005-0000-0000-000075000000}"/>
-    <cellStyle name="20% - Énfasis2 13 2 2" xfId="687" xr:uid="{00000000-0005-0000-0000-000076000000}"/>
-    <cellStyle name="20% - Énfasis2 13 3" xfId="686" xr:uid="{00000000-0005-0000-0000-000077000000}"/>
-    <cellStyle name="20% - Énfasis2 14" xfId="217" xr:uid="{00000000-0005-0000-0000-000078000000}"/>
-    <cellStyle name="20% - Énfasis2 14 2" xfId="512" xr:uid="{00000000-0005-0000-0000-000079000000}"/>
-    <cellStyle name="20% - Énfasis2 14 2 2" xfId="689" xr:uid="{00000000-0005-0000-0000-00007A000000}"/>
-    <cellStyle name="20% - Énfasis2 14 3" xfId="688" xr:uid="{00000000-0005-0000-0000-00007B000000}"/>
-    <cellStyle name="20% - Énfasis2 15" xfId="231" xr:uid="{00000000-0005-0000-0000-00007C000000}"/>
-    <cellStyle name="20% - Énfasis2 15 2" xfId="526" xr:uid="{00000000-0005-0000-0000-00007D000000}"/>
-    <cellStyle name="20% - Énfasis2 15 2 2" xfId="691" xr:uid="{00000000-0005-0000-0000-00007E000000}"/>
-    <cellStyle name="20% - Énfasis2 15 3" xfId="690" xr:uid="{00000000-0005-0000-0000-00007F000000}"/>
-    <cellStyle name="20% - Énfasis2 16" xfId="245" xr:uid="{00000000-0005-0000-0000-000080000000}"/>
-    <cellStyle name="20% - Énfasis2 16 2" xfId="540" xr:uid="{00000000-0005-0000-0000-000081000000}"/>
-    <cellStyle name="20% - Énfasis2 16 2 2" xfId="693" xr:uid="{00000000-0005-0000-0000-000082000000}"/>
-    <cellStyle name="20% - Énfasis2 16 3" xfId="692" xr:uid="{00000000-0005-0000-0000-000083000000}"/>
-    <cellStyle name="20% - Énfasis2 17" xfId="259" xr:uid="{00000000-0005-0000-0000-000084000000}"/>
-    <cellStyle name="20% - Énfasis2 17 2" xfId="554" xr:uid="{00000000-0005-0000-0000-000085000000}"/>
-    <cellStyle name="20% - Énfasis2 17 2 2" xfId="695" xr:uid="{00000000-0005-0000-0000-000086000000}"/>
-    <cellStyle name="20% - Énfasis2 17 3" xfId="694" xr:uid="{00000000-0005-0000-0000-000087000000}"/>
-    <cellStyle name="20% - Énfasis2 18" xfId="273" xr:uid="{00000000-0005-0000-0000-000088000000}"/>
-    <cellStyle name="20% - Énfasis2 18 2" xfId="568" xr:uid="{00000000-0005-0000-0000-000089000000}"/>
-    <cellStyle name="20% - Énfasis2 18 2 2" xfId="697" xr:uid="{00000000-0005-0000-0000-00008A000000}"/>
-    <cellStyle name="20% - Énfasis2 18 3" xfId="696" xr:uid="{00000000-0005-0000-0000-00008B000000}"/>
-    <cellStyle name="20% - Énfasis2 19" xfId="287" xr:uid="{00000000-0005-0000-0000-00008C000000}"/>
-    <cellStyle name="20% - Énfasis2 19 2" xfId="582" xr:uid="{00000000-0005-0000-0000-00008D000000}"/>
-    <cellStyle name="20% - Énfasis2 19 2 2" xfId="699" xr:uid="{00000000-0005-0000-0000-00008E000000}"/>
-    <cellStyle name="20% - Énfasis2 19 3" xfId="698" xr:uid="{00000000-0005-0000-0000-00008F000000}"/>
-    <cellStyle name="20% - Énfasis2 2" xfId="49" xr:uid="{00000000-0005-0000-0000-000090000000}"/>
-    <cellStyle name="20% - Énfasis2 2 2" xfId="344" xr:uid="{00000000-0005-0000-0000-000091000000}"/>
-    <cellStyle name="20% - Énfasis2 2 2 2" xfId="701" xr:uid="{00000000-0005-0000-0000-000092000000}"/>
-    <cellStyle name="20% - Énfasis2 2 3" xfId="700" xr:uid="{00000000-0005-0000-0000-000093000000}"/>
-    <cellStyle name="20% - Énfasis2 20" xfId="301" xr:uid="{00000000-0005-0000-0000-000094000000}"/>
-    <cellStyle name="20% - Énfasis2 20 2" xfId="596" xr:uid="{00000000-0005-0000-0000-000095000000}"/>
-    <cellStyle name="20% - Énfasis2 20 2 2" xfId="703" xr:uid="{00000000-0005-0000-0000-000096000000}"/>
-    <cellStyle name="20% - Énfasis2 20 3" xfId="702" xr:uid="{00000000-0005-0000-0000-000097000000}"/>
-    <cellStyle name="20% - Énfasis2 21" xfId="315" xr:uid="{00000000-0005-0000-0000-000098000000}"/>
-    <cellStyle name="20% - Énfasis2 21 2" xfId="610" xr:uid="{00000000-0005-0000-0000-000099000000}"/>
-    <cellStyle name="20% - Énfasis2 21 2 2" xfId="705" xr:uid="{00000000-0005-0000-0000-00009A000000}"/>
-    <cellStyle name="20% - Énfasis2 21 3" xfId="704" xr:uid="{00000000-0005-0000-0000-00009B000000}"/>
-    <cellStyle name="20% - Énfasis2 22" xfId="624" xr:uid="{00000000-0005-0000-0000-00009C000000}"/>
-    <cellStyle name="20% - Énfasis2 22 2" xfId="707" xr:uid="{00000000-0005-0000-0000-00009D000000}"/>
-    <cellStyle name="20% - Énfasis2 22 3" xfId="706" xr:uid="{00000000-0005-0000-0000-00009E000000}"/>
-    <cellStyle name="20% - Énfasis2 23" xfId="328" xr:uid="{00000000-0005-0000-0000-00009F000000}"/>
-    <cellStyle name="20% - Énfasis2 23 2" xfId="708" xr:uid="{00000000-0005-0000-0000-0000A0000000}"/>
-    <cellStyle name="20% - Énfasis2 24" xfId="679" xr:uid="{00000000-0005-0000-0000-0000A1000000}"/>
-    <cellStyle name="20% - Énfasis2 25" xfId="1268" xr:uid="{00000000-0005-0000-0000-0000A2000000}"/>
-    <cellStyle name="20% - Énfasis2 26" xfId="1282" xr:uid="{00000000-0005-0000-0000-0000A3000000}"/>
-    <cellStyle name="20% - Énfasis2 27" xfId="1296" xr:uid="{00000000-0005-0000-0000-0000A4000000}"/>
-    <cellStyle name="20% - Énfasis2 28" xfId="1310" xr:uid="{00000000-0005-0000-0000-0000A5000000}"/>
-    <cellStyle name="20% - Énfasis2 29" xfId="1324" xr:uid="{00000000-0005-0000-0000-0000A6000000}"/>
-    <cellStyle name="20% - Énfasis2 3" xfId="63" xr:uid="{00000000-0005-0000-0000-0000A7000000}"/>
-    <cellStyle name="20% - Énfasis2 3 2" xfId="358" xr:uid="{00000000-0005-0000-0000-0000A8000000}"/>
-    <cellStyle name="20% - Énfasis2 3 2 2" xfId="710" xr:uid="{00000000-0005-0000-0000-0000A9000000}"/>
-    <cellStyle name="20% - Énfasis2 3 3" xfId="709" xr:uid="{00000000-0005-0000-0000-0000AA000000}"/>
-    <cellStyle name="20% - Énfasis2 30" xfId="1338" xr:uid="{00000000-0005-0000-0000-0000AB000000}"/>
-    <cellStyle name="20% - Énfasis2 31" xfId="1352" xr:uid="{00000000-0005-0000-0000-0000AC000000}"/>
-    <cellStyle name="20% - Énfasis2 32" xfId="1366" xr:uid="{00000000-0005-0000-0000-0000AD000000}"/>
-    <cellStyle name="20% - Énfasis2 33" xfId="1380" xr:uid="{00000000-0005-0000-0000-0000AE000000}"/>
-    <cellStyle name="20% - Énfasis2 34" xfId="1394" xr:uid="{00000000-0005-0000-0000-0000AF000000}"/>
-    <cellStyle name="20% - Énfasis2 35" xfId="1408" xr:uid="{00000000-0005-0000-0000-0000B0000000}"/>
-    <cellStyle name="20% - Énfasis2 36" xfId="1422" xr:uid="{00000000-0005-0000-0000-0000B1000000}"/>
-    <cellStyle name="20% - Énfasis2 37" xfId="1436" xr:uid="{00000000-0005-0000-0000-0000B2000000}"/>
-    <cellStyle name="20% - Énfasis2 38" xfId="1450" xr:uid="{00000000-0005-0000-0000-0000B3000000}"/>
-    <cellStyle name="20% - Énfasis2 39" xfId="1464" xr:uid="{00000000-0005-0000-0000-0000B4000000}"/>
-    <cellStyle name="20% - Énfasis2 4" xfId="77" xr:uid="{00000000-0005-0000-0000-0000B5000000}"/>
-    <cellStyle name="20% - Énfasis2 4 2" xfId="372" xr:uid="{00000000-0005-0000-0000-0000B6000000}"/>
-    <cellStyle name="20% - Énfasis2 4 2 2" xfId="712" xr:uid="{00000000-0005-0000-0000-0000B7000000}"/>
-    <cellStyle name="20% - Énfasis2 4 3" xfId="711" xr:uid="{00000000-0005-0000-0000-0000B8000000}"/>
-    <cellStyle name="20% - Énfasis2 40" xfId="1479" xr:uid="{00000000-0005-0000-0000-0000B9000000}"/>
-    <cellStyle name="20% - Énfasis2 5" xfId="91" xr:uid="{00000000-0005-0000-0000-0000BA000000}"/>
-    <cellStyle name="20% - Énfasis2 5 2" xfId="386" xr:uid="{00000000-0005-0000-0000-0000BB000000}"/>
-    <cellStyle name="20% - Énfasis2 5 2 2" xfId="714" xr:uid="{00000000-0005-0000-0000-0000BC000000}"/>
-    <cellStyle name="20% - Énfasis2 5 3" xfId="713" xr:uid="{00000000-0005-0000-0000-0000BD000000}"/>
-    <cellStyle name="20% - Énfasis2 6" xfId="105" xr:uid="{00000000-0005-0000-0000-0000BE000000}"/>
-    <cellStyle name="20% - Énfasis2 6 2" xfId="400" xr:uid="{00000000-0005-0000-0000-0000BF000000}"/>
-    <cellStyle name="20% - Énfasis2 6 2 2" xfId="716" xr:uid="{00000000-0005-0000-0000-0000C0000000}"/>
-    <cellStyle name="20% - Énfasis2 6 3" xfId="715" xr:uid="{00000000-0005-0000-0000-0000C1000000}"/>
-    <cellStyle name="20% - Énfasis2 7" xfId="119" xr:uid="{00000000-0005-0000-0000-0000C2000000}"/>
-    <cellStyle name="20% - Énfasis2 7 2" xfId="414" xr:uid="{00000000-0005-0000-0000-0000C3000000}"/>
-    <cellStyle name="20% - Énfasis2 7 2 2" xfId="718" xr:uid="{00000000-0005-0000-0000-0000C4000000}"/>
-    <cellStyle name="20% - Énfasis2 7 3" xfId="717" xr:uid="{00000000-0005-0000-0000-0000C5000000}"/>
-    <cellStyle name="20% - Énfasis2 8" xfId="133" xr:uid="{00000000-0005-0000-0000-0000C6000000}"/>
-    <cellStyle name="20% - Énfasis2 8 2" xfId="428" xr:uid="{00000000-0005-0000-0000-0000C7000000}"/>
-    <cellStyle name="20% - Énfasis2 8 2 2" xfId="720" xr:uid="{00000000-0005-0000-0000-0000C8000000}"/>
-    <cellStyle name="20% - Énfasis2 8 3" xfId="719" xr:uid="{00000000-0005-0000-0000-0000C9000000}"/>
-    <cellStyle name="20% - Énfasis2 9" xfId="147" xr:uid="{00000000-0005-0000-0000-0000CA000000}"/>
-    <cellStyle name="20% - Énfasis2 9 2" xfId="442" xr:uid="{00000000-0005-0000-0000-0000CB000000}"/>
-    <cellStyle name="20% - Énfasis2 9 2 2" xfId="722" xr:uid="{00000000-0005-0000-0000-0000CC000000}"/>
-    <cellStyle name="20% - Énfasis2 9 3" xfId="721" xr:uid="{00000000-0005-0000-0000-0000CD000000}"/>
+    <cellStyle name="20% - Énfasis2 10" xfId="161"/>
+    <cellStyle name="20% - Énfasis2 10 2" xfId="456"/>
+    <cellStyle name="20% - Énfasis2 10 2 2" xfId="681"/>
+    <cellStyle name="20% - Énfasis2 10 3" xfId="680"/>
+    <cellStyle name="20% - Énfasis2 11" xfId="175"/>
+    <cellStyle name="20% - Énfasis2 11 2" xfId="470"/>
+    <cellStyle name="20% - Énfasis2 11 2 2" xfId="683"/>
+    <cellStyle name="20% - Énfasis2 11 3" xfId="682"/>
+    <cellStyle name="20% - Énfasis2 12" xfId="189"/>
+    <cellStyle name="20% - Énfasis2 12 2" xfId="484"/>
+    <cellStyle name="20% - Énfasis2 12 2 2" xfId="685"/>
+    <cellStyle name="20% - Énfasis2 12 3" xfId="684"/>
+    <cellStyle name="20% - Énfasis2 13" xfId="203"/>
+    <cellStyle name="20% - Énfasis2 13 2" xfId="498"/>
+    <cellStyle name="20% - Énfasis2 13 2 2" xfId="687"/>
+    <cellStyle name="20% - Énfasis2 13 3" xfId="686"/>
+    <cellStyle name="20% - Énfasis2 14" xfId="217"/>
+    <cellStyle name="20% - Énfasis2 14 2" xfId="512"/>
+    <cellStyle name="20% - Énfasis2 14 2 2" xfId="689"/>
+    <cellStyle name="20% - Énfasis2 14 3" xfId="688"/>
+    <cellStyle name="20% - Énfasis2 15" xfId="231"/>
+    <cellStyle name="20% - Énfasis2 15 2" xfId="526"/>
+    <cellStyle name="20% - Énfasis2 15 2 2" xfId="691"/>
+    <cellStyle name="20% - Énfasis2 15 3" xfId="690"/>
+    <cellStyle name="20% - Énfasis2 16" xfId="245"/>
+    <cellStyle name="20% - Énfasis2 16 2" xfId="540"/>
+    <cellStyle name="20% - Énfasis2 16 2 2" xfId="693"/>
+    <cellStyle name="20% - Énfasis2 16 3" xfId="692"/>
+    <cellStyle name="20% - Énfasis2 17" xfId="259"/>
+    <cellStyle name="20% - Énfasis2 17 2" xfId="554"/>
+    <cellStyle name="20% - Énfasis2 17 2 2" xfId="695"/>
+    <cellStyle name="20% - Énfasis2 17 3" xfId="694"/>
+    <cellStyle name="20% - Énfasis2 18" xfId="273"/>
+    <cellStyle name="20% - Énfasis2 18 2" xfId="568"/>
+    <cellStyle name="20% - Énfasis2 18 2 2" xfId="697"/>
+    <cellStyle name="20% - Énfasis2 18 3" xfId="696"/>
+    <cellStyle name="20% - Énfasis2 19" xfId="287"/>
+    <cellStyle name="20% - Énfasis2 19 2" xfId="582"/>
+    <cellStyle name="20% - Énfasis2 19 2 2" xfId="699"/>
+    <cellStyle name="20% - Énfasis2 19 3" xfId="698"/>
+    <cellStyle name="20% - Énfasis2 2" xfId="49"/>
+    <cellStyle name="20% - Énfasis2 2 2" xfId="344"/>
+    <cellStyle name="20% - Énfasis2 2 2 2" xfId="701"/>
+    <cellStyle name="20% - Énfasis2 2 3" xfId="700"/>
+    <cellStyle name="20% - Énfasis2 20" xfId="301"/>
+    <cellStyle name="20% - Énfasis2 20 2" xfId="596"/>
+    <cellStyle name="20% - Énfasis2 20 2 2" xfId="703"/>
+    <cellStyle name="20% - Énfasis2 20 3" xfId="702"/>
+    <cellStyle name="20% - Énfasis2 21" xfId="315"/>
+    <cellStyle name="20% - Énfasis2 21 2" xfId="610"/>
+    <cellStyle name="20% - Énfasis2 21 2 2" xfId="705"/>
+    <cellStyle name="20% - Énfasis2 21 3" xfId="704"/>
+    <cellStyle name="20% - Énfasis2 22" xfId="624"/>
+    <cellStyle name="20% - Énfasis2 22 2" xfId="707"/>
+    <cellStyle name="20% - Énfasis2 22 3" xfId="706"/>
+    <cellStyle name="20% - Énfasis2 23" xfId="328"/>
+    <cellStyle name="20% - Énfasis2 23 2" xfId="708"/>
+    <cellStyle name="20% - Énfasis2 24" xfId="679"/>
+    <cellStyle name="20% - Énfasis2 25" xfId="1268"/>
+    <cellStyle name="20% - Énfasis2 26" xfId="1282"/>
+    <cellStyle name="20% - Énfasis2 27" xfId="1296"/>
+    <cellStyle name="20% - Énfasis2 28" xfId="1310"/>
+    <cellStyle name="20% - Énfasis2 29" xfId="1324"/>
+    <cellStyle name="20% - Énfasis2 3" xfId="63"/>
+    <cellStyle name="20% - Énfasis2 3 2" xfId="358"/>
+    <cellStyle name="20% - Énfasis2 3 2 2" xfId="710"/>
+    <cellStyle name="20% - Énfasis2 3 3" xfId="709"/>
+    <cellStyle name="20% - Énfasis2 30" xfId="1338"/>
+    <cellStyle name="20% - Énfasis2 31" xfId="1352"/>
+    <cellStyle name="20% - Énfasis2 32" xfId="1366"/>
+    <cellStyle name="20% - Énfasis2 33" xfId="1380"/>
+    <cellStyle name="20% - Énfasis2 34" xfId="1394"/>
+    <cellStyle name="20% - Énfasis2 35" xfId="1408"/>
+    <cellStyle name="20% - Énfasis2 36" xfId="1422"/>
+    <cellStyle name="20% - Énfasis2 37" xfId="1436"/>
+    <cellStyle name="20% - Énfasis2 38" xfId="1450"/>
+    <cellStyle name="20% - Énfasis2 39" xfId="1464"/>
+    <cellStyle name="20% - Énfasis2 4" xfId="77"/>
+    <cellStyle name="20% - Énfasis2 4 2" xfId="372"/>
+    <cellStyle name="20% - Énfasis2 4 2 2" xfId="712"/>
+    <cellStyle name="20% - Énfasis2 4 3" xfId="711"/>
+    <cellStyle name="20% - Énfasis2 40" xfId="1479"/>
+    <cellStyle name="20% - Énfasis2 5" xfId="91"/>
+    <cellStyle name="20% - Énfasis2 5 2" xfId="386"/>
+    <cellStyle name="20% - Énfasis2 5 2 2" xfId="714"/>
+    <cellStyle name="20% - Énfasis2 5 3" xfId="713"/>
+    <cellStyle name="20% - Énfasis2 6" xfId="105"/>
+    <cellStyle name="20% - Énfasis2 6 2" xfId="400"/>
+    <cellStyle name="20% - Énfasis2 6 2 2" xfId="716"/>
+    <cellStyle name="20% - Énfasis2 6 3" xfId="715"/>
+    <cellStyle name="20% - Énfasis2 7" xfId="119"/>
+    <cellStyle name="20% - Énfasis2 7 2" xfId="414"/>
+    <cellStyle name="20% - Énfasis2 7 2 2" xfId="718"/>
+    <cellStyle name="20% - Énfasis2 7 3" xfId="717"/>
+    <cellStyle name="20% - Énfasis2 8" xfId="133"/>
+    <cellStyle name="20% - Énfasis2 8 2" xfId="428"/>
+    <cellStyle name="20% - Énfasis2 8 2 2" xfId="720"/>
+    <cellStyle name="20% - Énfasis2 8 3" xfId="719"/>
+    <cellStyle name="20% - Énfasis2 9" xfId="147"/>
+    <cellStyle name="20% - Énfasis2 9 2" xfId="442"/>
+    <cellStyle name="20% - Énfasis2 9 2 2" xfId="722"/>
+    <cellStyle name="20% - Énfasis2 9 3" xfId="721"/>
     <cellStyle name="20% - Énfasis3" xfId="28" builtinId="38" customBuiltin="1"/>
-    <cellStyle name="20% - Énfasis3 10" xfId="163" xr:uid="{00000000-0005-0000-0000-0000CF000000}"/>
-    <cellStyle name="20% - Énfasis3 10 2" xfId="458" xr:uid="{00000000-0005-0000-0000-0000D0000000}"/>
-    <cellStyle name="20% - Énfasis3 10 2 2" xfId="725" xr:uid="{00000000-0005-0000-0000-0000D1000000}"/>
-    <cellStyle name="20% - Énfasis3 10 3" xfId="724" xr:uid="{00000000-0005-0000-0000-0000D2000000}"/>
-    <cellStyle name="20% - Énfasis3 11" xfId="177" xr:uid="{00000000-0005-0000-0000-0000D3000000}"/>
-    <cellStyle name="20% - Énfasis3 11 2" xfId="472" xr:uid="{00000000-0005-0000-0000-0000D4000000}"/>
-    <cellStyle name="20% - Énfasis3 11 2 2" xfId="727" xr:uid="{00000000-0005-0000-0000-0000D5000000}"/>
-    <cellStyle name="20% - Énfasis3 11 3" xfId="726" xr:uid="{00000000-0005-0000-0000-0000D6000000}"/>
-    <cellStyle name="20% - Énfasis3 12" xfId="191" xr:uid="{00000000-0005-0000-0000-0000D7000000}"/>
-    <cellStyle name="20% - Énfasis3 12 2" xfId="486" xr:uid="{00000000-0005-0000-0000-0000D8000000}"/>
-    <cellStyle name="20% - Énfasis3 12 2 2" xfId="729" xr:uid="{00000000-0005-0000-0000-0000D9000000}"/>
-    <cellStyle name="20% - Énfasis3 12 3" xfId="728" xr:uid="{00000000-0005-0000-0000-0000DA000000}"/>
-    <cellStyle name="20% - Énfasis3 13" xfId="205" xr:uid="{00000000-0005-0000-0000-0000DB000000}"/>
-    <cellStyle name="20% - Énfasis3 13 2" xfId="500" xr:uid="{00000000-0005-0000-0000-0000DC000000}"/>
-    <cellStyle name="20% - Énfasis3 13 2 2" xfId="731" xr:uid="{00000000-0005-0000-0000-0000DD000000}"/>
-    <cellStyle name="20% - Énfasis3 13 3" xfId="730" xr:uid="{00000000-0005-0000-0000-0000DE000000}"/>
-    <cellStyle name="20% - Énfasis3 14" xfId="219" xr:uid="{00000000-0005-0000-0000-0000DF000000}"/>
-    <cellStyle name="20% - Énfasis3 14 2" xfId="514" xr:uid="{00000000-0005-0000-0000-0000E0000000}"/>
-    <cellStyle name="20% - Énfasis3 14 2 2" xfId="733" xr:uid="{00000000-0005-0000-0000-0000E1000000}"/>
-    <cellStyle name="20% - Énfasis3 14 3" xfId="732" xr:uid="{00000000-0005-0000-0000-0000E2000000}"/>
-    <cellStyle name="20% - Énfasis3 15" xfId="233" xr:uid="{00000000-0005-0000-0000-0000E3000000}"/>
-    <cellStyle name="20% - Énfasis3 15 2" xfId="528" xr:uid="{00000000-0005-0000-0000-0000E4000000}"/>
-    <cellStyle name="20% - Énfasis3 15 2 2" xfId="735" xr:uid="{00000000-0005-0000-0000-0000E5000000}"/>
-    <cellStyle name="20% - Énfasis3 15 3" xfId="734" xr:uid="{00000000-0005-0000-0000-0000E6000000}"/>
-    <cellStyle name="20% - Énfasis3 16" xfId="247" xr:uid="{00000000-0005-0000-0000-0000E7000000}"/>
-    <cellStyle name="20% - Énfasis3 16 2" xfId="542" xr:uid="{00000000-0005-0000-0000-0000E8000000}"/>
-    <cellStyle name="20% - Énfasis3 16 2 2" xfId="737" xr:uid="{00000000-0005-0000-0000-0000E9000000}"/>
-    <cellStyle name="20% - Énfasis3 16 3" xfId="736" xr:uid="{00000000-0005-0000-0000-0000EA000000}"/>
-    <cellStyle name="20% - Énfasis3 17" xfId="261" xr:uid="{00000000-0005-0000-0000-0000EB000000}"/>
-    <cellStyle name="20% - Énfasis3 17 2" xfId="556" xr:uid="{00000000-0005-0000-0000-0000EC000000}"/>
-    <cellStyle name="20% - Énfasis3 17 2 2" xfId="739" xr:uid="{00000000-0005-0000-0000-0000ED000000}"/>
-    <cellStyle name="20% - Énfasis3 17 3" xfId="738" xr:uid="{00000000-0005-0000-0000-0000EE000000}"/>
-    <cellStyle name="20% - Énfasis3 18" xfId="275" xr:uid="{00000000-0005-0000-0000-0000EF000000}"/>
-    <cellStyle name="20% - Énfasis3 18 2" xfId="570" xr:uid="{00000000-0005-0000-0000-0000F0000000}"/>
-    <cellStyle name="20% - Énfasis3 18 2 2" xfId="741" xr:uid="{00000000-0005-0000-0000-0000F1000000}"/>
-    <cellStyle name="20% - Énfasis3 18 3" xfId="740" xr:uid="{00000000-0005-0000-0000-0000F2000000}"/>
-    <cellStyle name="20% - Énfasis3 19" xfId="289" xr:uid="{00000000-0005-0000-0000-0000F3000000}"/>
-    <cellStyle name="20% - Énfasis3 19 2" xfId="584" xr:uid="{00000000-0005-0000-0000-0000F4000000}"/>
-    <cellStyle name="20% - Énfasis3 19 2 2" xfId="743" xr:uid="{00000000-0005-0000-0000-0000F5000000}"/>
-    <cellStyle name="20% - Énfasis3 19 3" xfId="742" xr:uid="{00000000-0005-0000-0000-0000F6000000}"/>
-    <cellStyle name="20% - Énfasis3 2" xfId="51" xr:uid="{00000000-0005-0000-0000-0000F7000000}"/>
-    <cellStyle name="20% - Énfasis3 2 2" xfId="346" xr:uid="{00000000-0005-0000-0000-0000F8000000}"/>
-    <cellStyle name="20% - Énfasis3 2 2 2" xfId="745" xr:uid="{00000000-0005-0000-0000-0000F9000000}"/>
-    <cellStyle name="20% - Énfasis3 2 3" xfId="744" xr:uid="{00000000-0005-0000-0000-0000FA000000}"/>
-    <cellStyle name="20% - Énfasis3 20" xfId="303" xr:uid="{00000000-0005-0000-0000-0000FB000000}"/>
-    <cellStyle name="20% - Énfasis3 20 2" xfId="598" xr:uid="{00000000-0005-0000-0000-0000FC000000}"/>
-    <cellStyle name="20% - Énfasis3 20 2 2" xfId="747" xr:uid="{00000000-0005-0000-0000-0000FD000000}"/>
-    <cellStyle name="20% - Énfasis3 20 3" xfId="746" xr:uid="{00000000-0005-0000-0000-0000FE000000}"/>
-    <cellStyle name="20% - Énfasis3 21" xfId="317" xr:uid="{00000000-0005-0000-0000-0000FF000000}"/>
-    <cellStyle name="20% - Énfasis3 21 2" xfId="612" xr:uid="{00000000-0005-0000-0000-000000010000}"/>
-    <cellStyle name="20% - Énfasis3 21 2 2" xfId="749" xr:uid="{00000000-0005-0000-0000-000001010000}"/>
-    <cellStyle name="20% - Énfasis3 21 3" xfId="748" xr:uid="{00000000-0005-0000-0000-000002010000}"/>
-    <cellStyle name="20% - Énfasis3 22" xfId="626" xr:uid="{00000000-0005-0000-0000-000003010000}"/>
-    <cellStyle name="20% - Énfasis3 22 2" xfId="751" xr:uid="{00000000-0005-0000-0000-000004010000}"/>
-    <cellStyle name="20% - Énfasis3 22 3" xfId="750" xr:uid="{00000000-0005-0000-0000-000005010000}"/>
-    <cellStyle name="20% - Énfasis3 23" xfId="330" xr:uid="{00000000-0005-0000-0000-000006010000}"/>
-    <cellStyle name="20% - Énfasis3 23 2" xfId="752" xr:uid="{00000000-0005-0000-0000-000007010000}"/>
-    <cellStyle name="20% - Énfasis3 24" xfId="723" xr:uid="{00000000-0005-0000-0000-000008010000}"/>
-    <cellStyle name="20% - Énfasis3 25" xfId="1270" xr:uid="{00000000-0005-0000-0000-000009010000}"/>
-    <cellStyle name="20% - Énfasis3 26" xfId="1284" xr:uid="{00000000-0005-0000-0000-00000A010000}"/>
-    <cellStyle name="20% - Énfasis3 27" xfId="1298" xr:uid="{00000000-0005-0000-0000-00000B010000}"/>
-    <cellStyle name="20% - Énfasis3 28" xfId="1312" xr:uid="{00000000-0005-0000-0000-00000C010000}"/>
-    <cellStyle name="20% - Énfasis3 29" xfId="1326" xr:uid="{00000000-0005-0000-0000-00000D010000}"/>
-    <cellStyle name="20% - Énfasis3 3" xfId="65" xr:uid="{00000000-0005-0000-0000-00000E010000}"/>
-    <cellStyle name="20% - Énfasis3 3 2" xfId="360" xr:uid="{00000000-0005-0000-0000-00000F010000}"/>
-    <cellStyle name="20% - Énfasis3 3 2 2" xfId="754" xr:uid="{00000000-0005-0000-0000-000010010000}"/>
-    <cellStyle name="20% - Énfasis3 3 3" xfId="753" xr:uid="{00000000-0005-0000-0000-000011010000}"/>
-    <cellStyle name="20% - Énfasis3 30" xfId="1340" xr:uid="{00000000-0005-0000-0000-000012010000}"/>
-    <cellStyle name="20% - Énfasis3 31" xfId="1354" xr:uid="{00000000-0005-0000-0000-000013010000}"/>
-    <cellStyle name="20% - Énfasis3 32" xfId="1368" xr:uid="{00000000-0005-0000-0000-000014010000}"/>
-    <cellStyle name="20% - Énfasis3 33" xfId="1382" xr:uid="{00000000-0005-0000-0000-000015010000}"/>
-    <cellStyle name="20% - Énfasis3 34" xfId="1396" xr:uid="{00000000-0005-0000-0000-000016010000}"/>
-    <cellStyle name="20% - Énfasis3 35" xfId="1410" xr:uid="{00000000-0005-0000-0000-000017010000}"/>
-    <cellStyle name="20% - Énfasis3 36" xfId="1424" xr:uid="{00000000-0005-0000-0000-000018010000}"/>
-    <cellStyle name="20% - Énfasis3 37" xfId="1438" xr:uid="{00000000-0005-0000-0000-000019010000}"/>
-    <cellStyle name="20% - Énfasis3 38" xfId="1452" xr:uid="{00000000-0005-0000-0000-00001A010000}"/>
-    <cellStyle name="20% - Énfasis3 39" xfId="1466" xr:uid="{00000000-0005-0000-0000-00001B010000}"/>
-    <cellStyle name="20% - Énfasis3 4" xfId="79" xr:uid="{00000000-0005-0000-0000-00001C010000}"/>
-    <cellStyle name="20% - Énfasis3 4 2" xfId="374" xr:uid="{00000000-0005-0000-0000-00001D010000}"/>
-    <cellStyle name="20% - Énfasis3 4 2 2" xfId="756" xr:uid="{00000000-0005-0000-0000-00001E010000}"/>
-    <cellStyle name="20% - Énfasis3 4 3" xfId="755" xr:uid="{00000000-0005-0000-0000-00001F010000}"/>
-    <cellStyle name="20% - Énfasis3 40" xfId="1481" xr:uid="{00000000-0005-0000-0000-000020010000}"/>
-    <cellStyle name="20% - Énfasis3 5" xfId="93" xr:uid="{00000000-0005-0000-0000-000021010000}"/>
-    <cellStyle name="20% - Énfasis3 5 2" xfId="388" xr:uid="{00000000-0005-0000-0000-000022010000}"/>
-    <cellStyle name="20% - Énfasis3 5 2 2" xfId="758" xr:uid="{00000000-0005-0000-0000-000023010000}"/>
-    <cellStyle name="20% - Énfasis3 5 3" xfId="757" xr:uid="{00000000-0005-0000-0000-000024010000}"/>
-    <cellStyle name="20% - Énfasis3 6" xfId="107" xr:uid="{00000000-0005-0000-0000-000025010000}"/>
-    <cellStyle name="20% - Énfasis3 6 2" xfId="402" xr:uid="{00000000-0005-0000-0000-000026010000}"/>
-    <cellStyle name="20% - Énfasis3 6 2 2" xfId="760" xr:uid="{00000000-0005-0000-0000-000027010000}"/>
-    <cellStyle name="20% - Énfasis3 6 3" xfId="759" xr:uid="{00000000-0005-0000-0000-000028010000}"/>
-    <cellStyle name="20% - Énfasis3 7" xfId="121" xr:uid="{00000000-0005-0000-0000-000029010000}"/>
-    <cellStyle name="20% - Énfasis3 7 2" xfId="416" xr:uid="{00000000-0005-0000-0000-00002A010000}"/>
-    <cellStyle name="20% - Énfasis3 7 2 2" xfId="762" xr:uid="{00000000-0005-0000-0000-00002B010000}"/>
-    <cellStyle name="20% - Énfasis3 7 3" xfId="761" xr:uid="{00000000-0005-0000-0000-00002C010000}"/>
-    <cellStyle name="20% - Énfasis3 8" xfId="135" xr:uid="{00000000-0005-0000-0000-00002D010000}"/>
-    <cellStyle name="20% - Énfasis3 8 2" xfId="430" xr:uid="{00000000-0005-0000-0000-00002E010000}"/>
-    <cellStyle name="20% - Énfasis3 8 2 2" xfId="764" xr:uid="{00000000-0005-0000-0000-00002F010000}"/>
-    <cellStyle name="20% - Énfasis3 8 3" xfId="763" xr:uid="{00000000-0005-0000-0000-000030010000}"/>
-    <cellStyle name="20% - Énfasis3 9" xfId="149" xr:uid="{00000000-0005-0000-0000-000031010000}"/>
-    <cellStyle name="20% - Énfasis3 9 2" xfId="444" xr:uid="{00000000-0005-0000-0000-000032010000}"/>
-    <cellStyle name="20% - Énfasis3 9 2 2" xfId="766" xr:uid="{00000000-0005-0000-0000-000033010000}"/>
-    <cellStyle name="20% - Énfasis3 9 3" xfId="765" xr:uid="{00000000-0005-0000-0000-000034010000}"/>
+    <cellStyle name="20% - Énfasis3 10" xfId="163"/>
+    <cellStyle name="20% - Énfasis3 10 2" xfId="458"/>
+    <cellStyle name="20% - Énfasis3 10 2 2" xfId="725"/>
+    <cellStyle name="20% - Énfasis3 10 3" xfId="724"/>
+    <cellStyle name="20% - Énfasis3 11" xfId="177"/>
+    <cellStyle name="20% - Énfasis3 11 2" xfId="472"/>
+    <cellStyle name="20% - Énfasis3 11 2 2" xfId="727"/>
+    <cellStyle name="20% - Énfasis3 11 3" xfId="726"/>
+    <cellStyle name="20% - Énfasis3 12" xfId="191"/>
+    <cellStyle name="20% - Énfasis3 12 2" xfId="486"/>
+    <cellStyle name="20% - Énfasis3 12 2 2" xfId="729"/>
+    <cellStyle name="20% - Énfasis3 12 3" xfId="728"/>
+    <cellStyle name="20% - Énfasis3 13" xfId="205"/>
+    <cellStyle name="20% - Énfasis3 13 2" xfId="500"/>
+    <cellStyle name="20% - Énfasis3 13 2 2" xfId="731"/>
+    <cellStyle name="20% - Énfasis3 13 3" xfId="730"/>
+    <cellStyle name="20% - Énfasis3 14" xfId="219"/>
+    <cellStyle name="20% - Énfasis3 14 2" xfId="514"/>
+    <cellStyle name="20% - Énfasis3 14 2 2" xfId="733"/>
+    <cellStyle name="20% - Énfasis3 14 3" xfId="732"/>
+    <cellStyle name="20% - Énfasis3 15" xfId="233"/>
+    <cellStyle name="20% - Énfasis3 15 2" xfId="528"/>
+    <cellStyle name="20% - Énfasis3 15 2 2" xfId="735"/>
+    <cellStyle name="20% - Énfasis3 15 3" xfId="734"/>
+    <cellStyle name="20% - Énfasis3 16" xfId="247"/>
+    <cellStyle name="20% - Énfasis3 16 2" xfId="542"/>
+    <cellStyle name="20% - Énfasis3 16 2 2" xfId="737"/>
+    <cellStyle name="20% - Énfasis3 16 3" xfId="736"/>
+    <cellStyle name="20% - Énfasis3 17" xfId="261"/>
+    <cellStyle name="20% - Énfasis3 17 2" xfId="556"/>
+    <cellStyle name="20% - Énfasis3 17 2 2" xfId="739"/>
+    <cellStyle name="20% - Énfasis3 17 3" xfId="738"/>
+    <cellStyle name="20% - Énfasis3 18" xfId="275"/>
+    <cellStyle name="20% - Énfasis3 18 2" xfId="570"/>
+    <cellStyle name="20% - Énfasis3 18 2 2" xfId="741"/>
+    <cellStyle name="20% - Énfasis3 18 3" xfId="740"/>
+    <cellStyle name="20% - Énfasis3 19" xfId="289"/>
+    <cellStyle name="20% - Énfasis3 19 2" xfId="584"/>
+    <cellStyle name="20% - Énfasis3 19 2 2" xfId="743"/>
+    <cellStyle name="20% - Énfasis3 19 3" xfId="742"/>
+    <cellStyle name="20% - Énfasis3 2" xfId="51"/>
+    <cellStyle name="20% - Énfasis3 2 2" xfId="346"/>
+    <cellStyle name="20% - Énfasis3 2 2 2" xfId="745"/>
+    <cellStyle name="20% - Énfasis3 2 3" xfId="744"/>
+    <cellStyle name="20% - Énfasis3 20" xfId="303"/>
+    <cellStyle name="20% - Énfasis3 20 2" xfId="598"/>
+    <cellStyle name="20% - Énfasis3 20 2 2" xfId="747"/>
+    <cellStyle name="20% - Énfasis3 20 3" xfId="746"/>
+    <cellStyle name="20% - Énfasis3 21" xfId="317"/>
+    <cellStyle name="20% - Énfasis3 21 2" xfId="612"/>
+    <cellStyle name="20% - Énfasis3 21 2 2" xfId="749"/>
+    <cellStyle name="20% - Énfasis3 21 3" xfId="748"/>
+    <cellStyle name="20% - Énfasis3 22" xfId="626"/>
+    <cellStyle name="20% - Énfasis3 22 2" xfId="751"/>
+    <cellStyle name="20% - Énfasis3 22 3" xfId="750"/>
+    <cellStyle name="20% - Énfasis3 23" xfId="330"/>
+    <cellStyle name="20% - Énfasis3 23 2" xfId="752"/>
+    <cellStyle name="20% - Énfasis3 24" xfId="723"/>
+    <cellStyle name="20% - Énfasis3 25" xfId="1270"/>
+    <cellStyle name="20% - Énfasis3 26" xfId="1284"/>
+    <cellStyle name="20% - Énfasis3 27" xfId="1298"/>
+    <cellStyle name="20% - Énfasis3 28" xfId="1312"/>
+    <cellStyle name="20% - Énfasis3 29" xfId="1326"/>
+    <cellStyle name="20% - Énfasis3 3" xfId="65"/>
+    <cellStyle name="20% - Énfasis3 3 2" xfId="360"/>
+    <cellStyle name="20% - Énfasis3 3 2 2" xfId="754"/>
+    <cellStyle name="20% - Énfasis3 3 3" xfId="753"/>
+    <cellStyle name="20% - Énfasis3 30" xfId="1340"/>
+    <cellStyle name="20% - Énfasis3 31" xfId="1354"/>
+    <cellStyle name="20% - Énfasis3 32" xfId="1368"/>
+    <cellStyle name="20% - Énfasis3 33" xfId="1382"/>
+    <cellStyle name="20% - Énfasis3 34" xfId="1396"/>
+    <cellStyle name="20% - Énfasis3 35" xfId="1410"/>
+    <cellStyle name="20% - Énfasis3 36" xfId="1424"/>
+    <cellStyle name="20% - Énfasis3 37" xfId="1438"/>
+    <cellStyle name="20% - Énfasis3 38" xfId="1452"/>
+    <cellStyle name="20% - Énfasis3 39" xfId="1466"/>
+    <cellStyle name="20% - Énfasis3 4" xfId="79"/>
+    <cellStyle name="20% - Énfasis3 4 2" xfId="374"/>
+    <cellStyle name="20% - Énfasis3 4 2 2" xfId="756"/>
+    <cellStyle name="20% - Énfasis3 4 3" xfId="755"/>
+    <cellStyle name="20% - Énfasis3 40" xfId="1481"/>
+    <cellStyle name="20% - Énfasis3 5" xfId="93"/>
+    <cellStyle name="20% - Énfasis3 5 2" xfId="388"/>
+    <cellStyle name="20% - Énfasis3 5 2 2" xfId="758"/>
+    <cellStyle name="20% - Énfasis3 5 3" xfId="757"/>
+    <cellStyle name="20% - Énfasis3 6" xfId="107"/>
+    <cellStyle name="20% - Énfasis3 6 2" xfId="402"/>
+    <cellStyle name="20% - Énfasis3 6 2 2" xfId="760"/>
+    <cellStyle name="20% - Énfasis3 6 3" xfId="759"/>
+    <cellStyle name="20% - Énfasis3 7" xfId="121"/>
+    <cellStyle name="20% - Énfasis3 7 2" xfId="416"/>
+    <cellStyle name="20% - Énfasis3 7 2 2" xfId="762"/>
+    <cellStyle name="20% - Énfasis3 7 3" xfId="761"/>
+    <cellStyle name="20% - Énfasis3 8" xfId="135"/>
+    <cellStyle name="20% - Énfasis3 8 2" xfId="430"/>
+    <cellStyle name="20% - Énfasis3 8 2 2" xfId="764"/>
+    <cellStyle name="20% - Énfasis3 8 3" xfId="763"/>
+    <cellStyle name="20% - Énfasis3 9" xfId="149"/>
+    <cellStyle name="20% - Énfasis3 9 2" xfId="444"/>
+    <cellStyle name="20% - Énfasis3 9 2 2" xfId="766"/>
+    <cellStyle name="20% - Énfasis3 9 3" xfId="765"/>
     <cellStyle name="20% - Énfasis4" xfId="32" builtinId="42" customBuiltin="1"/>
-    <cellStyle name="20% - Énfasis4 10" xfId="165" xr:uid="{00000000-0005-0000-0000-000036010000}"/>
-    <cellStyle name="20% - Énfasis4 10 2" xfId="460" xr:uid="{00000000-0005-0000-0000-000037010000}"/>
-    <cellStyle name="20% - Énfasis4 10 2 2" xfId="769" xr:uid="{00000000-0005-0000-0000-000038010000}"/>
-    <cellStyle name="20% - Énfasis4 10 3" xfId="768" xr:uid="{00000000-0005-0000-0000-000039010000}"/>
-    <cellStyle name="20% - Énfasis4 11" xfId="179" xr:uid="{00000000-0005-0000-0000-00003A010000}"/>
-    <cellStyle name="20% - Énfasis4 11 2" xfId="474" xr:uid="{00000000-0005-0000-0000-00003B010000}"/>
-    <cellStyle name="20% - Énfasis4 11 2 2" xfId="771" xr:uid="{00000000-0005-0000-0000-00003C010000}"/>
-    <cellStyle name="20% - Énfasis4 11 3" xfId="770" xr:uid="{00000000-0005-0000-0000-00003D010000}"/>
-    <cellStyle name="20% - Énfasis4 12" xfId="193" xr:uid="{00000000-0005-0000-0000-00003E010000}"/>
-    <cellStyle name="20% - Énfasis4 12 2" xfId="488" xr:uid="{00000000-0005-0000-0000-00003F010000}"/>
-    <cellStyle name="20% - Énfasis4 12 2 2" xfId="773" xr:uid="{00000000-0005-0000-0000-000040010000}"/>
-    <cellStyle name="20% - Énfasis4 12 3" xfId="772" xr:uid="{00000000-0005-0000-0000-000041010000}"/>
-    <cellStyle name="20% - Énfasis4 13" xfId="207" xr:uid="{00000000-0005-0000-0000-000042010000}"/>
-    <cellStyle name="20% - Énfasis4 13 2" xfId="502" xr:uid="{00000000-0005-0000-0000-000043010000}"/>
-    <cellStyle name="20% - Énfasis4 13 2 2" xfId="775" xr:uid="{00000000-0005-0000-0000-000044010000}"/>
-    <cellStyle name="20% - Énfasis4 13 3" xfId="774" xr:uid="{00000000-0005-0000-0000-000045010000}"/>
-    <cellStyle name="20% - Énfasis4 14" xfId="221" xr:uid="{00000000-0005-0000-0000-000046010000}"/>
-    <cellStyle name="20% - Énfasis4 14 2" xfId="516" xr:uid="{00000000-0005-0000-0000-000047010000}"/>
-    <cellStyle name="20% - Énfasis4 14 2 2" xfId="777" xr:uid="{00000000-0005-0000-0000-000048010000}"/>
-    <cellStyle name="20% - Énfasis4 14 3" xfId="776" xr:uid="{00000000-0005-0000-0000-000049010000}"/>
-    <cellStyle name="20% - Énfasis4 15" xfId="235" xr:uid="{00000000-0005-0000-0000-00004A010000}"/>
-    <cellStyle name="20% - Énfasis4 15 2" xfId="530" xr:uid="{00000000-0005-0000-0000-00004B010000}"/>
-    <cellStyle name="20% - Énfasis4 15 2 2" xfId="779" xr:uid="{00000000-0005-0000-0000-00004C010000}"/>
-    <cellStyle name="20% - Énfasis4 15 3" xfId="778" xr:uid="{00000000-0005-0000-0000-00004D010000}"/>
-    <cellStyle name="20% - Énfasis4 16" xfId="249" xr:uid="{00000000-0005-0000-0000-00004E010000}"/>
-    <cellStyle name="20% - Énfasis4 16 2" xfId="544" xr:uid="{00000000-0005-0000-0000-00004F010000}"/>
-    <cellStyle name="20% - Énfasis4 16 2 2" xfId="781" xr:uid="{00000000-0005-0000-0000-000050010000}"/>
-    <cellStyle name="20% - Énfasis4 16 3" xfId="780" xr:uid="{00000000-0005-0000-0000-000051010000}"/>
-    <cellStyle name="20% - Énfasis4 17" xfId="263" xr:uid="{00000000-0005-0000-0000-000052010000}"/>
-    <cellStyle name="20% - Énfasis4 17 2" xfId="558" xr:uid="{00000000-0005-0000-0000-000053010000}"/>
-    <cellStyle name="20% - Énfasis4 17 2 2" xfId="783" xr:uid="{00000000-0005-0000-0000-000054010000}"/>
-    <cellStyle name="20% - Énfasis4 17 3" xfId="782" xr:uid="{00000000-0005-0000-0000-000055010000}"/>
-    <cellStyle name="20% - Énfasis4 18" xfId="277" xr:uid="{00000000-0005-0000-0000-000056010000}"/>
-    <cellStyle name="20% - Énfasis4 18 2" xfId="572" xr:uid="{00000000-0005-0000-0000-000057010000}"/>
-    <cellStyle name="20% - Énfasis4 18 2 2" xfId="785" xr:uid="{00000000-0005-0000-0000-000058010000}"/>
-    <cellStyle name="20% - Énfasis4 18 3" xfId="784" xr:uid="{00000000-0005-0000-0000-000059010000}"/>
-    <cellStyle name="20% - Énfasis4 19" xfId="291" xr:uid="{00000000-0005-0000-0000-00005A010000}"/>
-    <cellStyle name="20% - Énfasis4 19 2" xfId="586" xr:uid="{00000000-0005-0000-0000-00005B010000}"/>
-    <cellStyle name="20% - Énfasis4 19 2 2" xfId="787" xr:uid="{00000000-0005-0000-0000-00005C010000}"/>
-    <cellStyle name="20% - Énfasis4 19 3" xfId="786" xr:uid="{00000000-0005-0000-0000-00005D010000}"/>
-    <cellStyle name="20% - Énfasis4 2" xfId="53" xr:uid="{00000000-0005-0000-0000-00005E010000}"/>
-    <cellStyle name="20% - Énfasis4 2 2" xfId="348" xr:uid="{00000000-0005-0000-0000-00005F010000}"/>
-    <cellStyle name="20% - Énfasis4 2 2 2" xfId="789" xr:uid="{00000000-0005-0000-0000-000060010000}"/>
-    <cellStyle name="20% - Énfasis4 2 3" xfId="788" xr:uid="{00000000-0005-0000-0000-000061010000}"/>
-    <cellStyle name="20% - Énfasis4 20" xfId="305" xr:uid="{00000000-0005-0000-0000-000062010000}"/>
-    <cellStyle name="20% - Énfasis4 20 2" xfId="600" xr:uid="{00000000-0005-0000-0000-000063010000}"/>
-    <cellStyle name="20% - Énfasis4 20 2 2" xfId="791" xr:uid="{00000000-0005-0000-0000-000064010000}"/>
-    <cellStyle name="20% - Énfasis4 20 3" xfId="790" xr:uid="{00000000-0005-0000-0000-000065010000}"/>
-    <cellStyle name="20% - Énfasis4 21" xfId="319" xr:uid="{00000000-0005-0000-0000-000066010000}"/>
-    <cellStyle name="20% - Énfasis4 21 2" xfId="614" xr:uid="{00000000-0005-0000-0000-000067010000}"/>
-    <cellStyle name="20% - Énfasis4 21 2 2" xfId="793" xr:uid="{00000000-0005-0000-0000-000068010000}"/>
-    <cellStyle name="20% - Énfasis4 21 3" xfId="792" xr:uid="{00000000-0005-0000-0000-000069010000}"/>
-    <cellStyle name="20% - Énfasis4 22" xfId="628" xr:uid="{00000000-0005-0000-0000-00006A010000}"/>
-    <cellStyle name="20% - Énfasis4 22 2" xfId="795" xr:uid="{00000000-0005-0000-0000-00006B010000}"/>
-    <cellStyle name="20% - Énfasis4 22 3" xfId="794" xr:uid="{00000000-0005-0000-0000-00006C010000}"/>
-    <cellStyle name="20% - Énfasis4 23" xfId="332" xr:uid="{00000000-0005-0000-0000-00006D010000}"/>
-    <cellStyle name="20% - Énfasis4 23 2" xfId="796" xr:uid="{00000000-0005-0000-0000-00006E010000}"/>
-    <cellStyle name="20% - Énfasis4 24" xfId="767" xr:uid="{00000000-0005-0000-0000-00006F010000}"/>
-    <cellStyle name="20% - Énfasis4 25" xfId="1272" xr:uid="{00000000-0005-0000-0000-000070010000}"/>
-    <cellStyle name="20% - Énfasis4 26" xfId="1286" xr:uid="{00000000-0005-0000-0000-000071010000}"/>
-    <cellStyle name="20% - Énfasis4 27" xfId="1300" xr:uid="{00000000-0005-0000-0000-000072010000}"/>
-    <cellStyle name="20% - Énfasis4 28" xfId="1314" xr:uid="{00000000-0005-0000-0000-000073010000}"/>
-    <cellStyle name="20% - Énfasis4 29" xfId="1328" xr:uid="{00000000-0005-0000-0000-000074010000}"/>
-    <cellStyle name="20% - Énfasis4 3" xfId="67" xr:uid="{00000000-0005-0000-0000-000075010000}"/>
-    <cellStyle name="20% - Énfasis4 3 2" xfId="362" xr:uid="{00000000-0005-0000-0000-000076010000}"/>
-    <cellStyle name="20% - Énfasis4 3 2 2" xfId="798" xr:uid="{00000000-0005-0000-0000-000077010000}"/>
-    <cellStyle name="20% - Énfasis4 3 3" xfId="797" xr:uid="{00000000-0005-0000-0000-000078010000}"/>
-    <cellStyle name="20% - Énfasis4 30" xfId="1342" xr:uid="{00000000-0005-0000-0000-000079010000}"/>
-    <cellStyle name="20% - Énfasis4 31" xfId="1356" xr:uid="{00000000-0005-0000-0000-00007A010000}"/>
-    <cellStyle name="20% - Énfasis4 32" xfId="1370" xr:uid="{00000000-0005-0000-0000-00007B010000}"/>
-    <cellStyle name="20% - Énfasis4 33" xfId="1384" xr:uid="{00000000-0005-0000-0000-00007C010000}"/>
-    <cellStyle name="20% - Énfasis4 34" xfId="1398" xr:uid="{00000000-0005-0000-0000-00007D010000}"/>
-    <cellStyle name="20% - Énfasis4 35" xfId="1412" xr:uid="{00000000-0005-0000-0000-00007E010000}"/>
-    <cellStyle name="20% - Énfasis4 36" xfId="1426" xr:uid="{00000000-0005-0000-0000-00007F010000}"/>
-    <cellStyle name="20% - Énfasis4 37" xfId="1440" xr:uid="{00000000-0005-0000-0000-000080010000}"/>
-    <cellStyle name="20% - Énfasis4 38" xfId="1454" xr:uid="{00000000-0005-0000-0000-000081010000}"/>
-    <cellStyle name="20% - Énfasis4 39" xfId="1468" xr:uid="{00000000-0005-0000-0000-000082010000}"/>
-    <cellStyle name="20% - Énfasis4 4" xfId="81" xr:uid="{00000000-0005-0000-0000-000083010000}"/>
-    <cellStyle name="20% - Énfasis4 4 2" xfId="376" xr:uid="{00000000-0005-0000-0000-000084010000}"/>
-    <cellStyle name="20% - Énfasis4 4 2 2" xfId="800" xr:uid="{00000000-0005-0000-0000-000085010000}"/>
-    <cellStyle name="20% - Énfasis4 4 3" xfId="799" xr:uid="{00000000-0005-0000-0000-000086010000}"/>
-    <cellStyle name="20% - Énfasis4 40" xfId="1483" xr:uid="{00000000-0005-0000-0000-000087010000}"/>
-    <cellStyle name="20% - Énfasis4 5" xfId="95" xr:uid="{00000000-0005-0000-0000-000088010000}"/>
-    <cellStyle name="20% - Énfasis4 5 2" xfId="390" xr:uid="{00000000-0005-0000-0000-000089010000}"/>
-    <cellStyle name="20% - Énfasis4 5 2 2" xfId="802" xr:uid="{00000000-0005-0000-0000-00008A010000}"/>
-    <cellStyle name="20% - Énfasis4 5 3" xfId="801" xr:uid="{00000000-0005-0000-0000-00008B010000}"/>
-    <cellStyle name="20% - Énfasis4 6" xfId="109" xr:uid="{00000000-0005-0000-0000-00008C010000}"/>
-    <cellStyle name="20% - Énfasis4 6 2" xfId="404" xr:uid="{00000000-0005-0000-0000-00008D010000}"/>
-    <cellStyle name="20% - Énfasis4 6 2 2" xfId="804" xr:uid="{00000000-0005-0000-0000-00008E010000}"/>
-    <cellStyle name="20% - Énfasis4 6 3" xfId="803" xr:uid="{00000000-0005-0000-0000-00008F010000}"/>
-    <cellStyle name="20% - Énfasis4 7" xfId="123" xr:uid="{00000000-0005-0000-0000-000090010000}"/>
-    <cellStyle name="20% - Énfasis4 7 2" xfId="418" xr:uid="{00000000-0005-0000-0000-000091010000}"/>
-    <cellStyle name="20% - Énfasis4 7 2 2" xfId="806" xr:uid="{00000000-0005-0000-0000-000092010000}"/>
-    <cellStyle name="20% - Énfasis4 7 3" xfId="805" xr:uid="{00000000-0005-0000-0000-000093010000}"/>
-    <cellStyle name="20% - Énfasis4 8" xfId="137" xr:uid="{00000000-0005-0000-0000-000094010000}"/>
-    <cellStyle name="20% - Énfasis4 8 2" xfId="432" xr:uid="{00000000-0005-0000-0000-000095010000}"/>
-    <cellStyle name="20% - Énfasis4 8 2 2" xfId="808" xr:uid="{00000000-0005-0000-0000-000096010000}"/>
-    <cellStyle name="20% - Énfasis4 8 3" xfId="807" xr:uid="{00000000-0005-0000-0000-000097010000}"/>
-    <cellStyle name="20% - Énfasis4 9" xfId="151" xr:uid="{00000000-0005-0000-0000-000098010000}"/>
-    <cellStyle name="20% - Énfasis4 9 2" xfId="446" xr:uid="{00000000-0005-0000-0000-000099010000}"/>
-    <cellStyle name="20% - Énfasis4 9 2 2" xfId="810" xr:uid="{00000000-0005-0000-0000-00009A010000}"/>
-    <cellStyle name="20% - Énfasis4 9 3" xfId="809" xr:uid="{00000000-0005-0000-0000-00009B010000}"/>
+    <cellStyle name="20% - Énfasis4 10" xfId="165"/>
+    <cellStyle name="20% - Énfasis4 10 2" xfId="460"/>
+    <cellStyle name="20% - Énfasis4 10 2 2" xfId="769"/>
+    <cellStyle name="20% - Énfasis4 10 3" xfId="768"/>
+    <cellStyle name="20% - Énfasis4 11" xfId="179"/>
+    <cellStyle name="20% - Énfasis4 11 2" xfId="474"/>
+    <cellStyle name="20% - Énfasis4 11 2 2" xfId="771"/>
+    <cellStyle name="20% - Énfasis4 11 3" xfId="770"/>
+    <cellStyle name="20% - Énfasis4 12" xfId="193"/>
+    <cellStyle name="20% - Énfasis4 12 2" xfId="488"/>
+    <cellStyle name="20% - Énfasis4 12 2 2" xfId="773"/>
+    <cellStyle name="20% - Énfasis4 12 3" xfId="772"/>
+    <cellStyle name="20% - Énfasis4 13" xfId="207"/>
+    <cellStyle name="20% - Énfasis4 13 2" xfId="502"/>
+    <cellStyle name="20% - Énfasis4 13 2 2" xfId="775"/>
+    <cellStyle name="20% - Énfasis4 13 3" xfId="774"/>
+    <cellStyle name="20% - Énfasis4 14" xfId="221"/>
+    <cellStyle name="20% - Énfasis4 14 2" xfId="516"/>
+    <cellStyle name="20% - Énfasis4 14 2 2" xfId="777"/>
+    <cellStyle name="20% - Énfasis4 14 3" xfId="776"/>
+    <cellStyle name="20% - Énfasis4 15" xfId="235"/>
+    <cellStyle name="20% - Énfasis4 15 2" xfId="530"/>
+    <cellStyle name="20% - Énfasis4 15 2 2" xfId="779"/>
+    <cellStyle name="20% - Énfasis4 15 3" xfId="778"/>
+    <cellStyle name="20% - Énfasis4 16" xfId="249"/>
+    <cellStyle name="20% - Énfasis4 16 2" xfId="544"/>
+    <cellStyle name="20% - Énfasis4 16 2 2" xfId="781"/>
+    <cellStyle name="20% - Énfasis4 16 3" xfId="780"/>
+    <cellStyle name="20% - Énfasis4 17" xfId="263"/>
+    <cellStyle name="20% - Énfasis4 17 2" xfId="558"/>
+    <cellStyle name="20% - Énfasis4 17 2 2" xfId="783"/>
+    <cellStyle name="20% - Énfasis4 17 3" xfId="782"/>
+    <cellStyle name="20% - Énfasis4 18" xfId="277"/>
+    <cellStyle name="20% - Énfasis4 18 2" xfId="572"/>
+    <cellStyle name="20% - Énfasis4 18 2 2" xfId="785"/>
+    <cellStyle name="20% - Énfasis4 18 3" xfId="784"/>
+    <cellStyle name="20% - Énfasis4 19" xfId="291"/>
+    <cellStyle name="20% - Énfasis4 19 2" xfId="586"/>
+    <cellStyle name="20% - Énfasis4 19 2 2" xfId="787"/>
+    <cellStyle name="20% - Énfasis4 19 3" xfId="786"/>
+    <cellStyle name="20% - Énfasis4 2" xfId="53"/>
+    <cellStyle name="20% - Énfasis4 2 2" xfId="348"/>
+    <cellStyle name="20% - Énfasis4 2 2 2" xfId="789"/>
+    <cellStyle name="20% - Énfasis4 2 3" xfId="788"/>
+    <cellStyle name="20% - Énfasis4 20" xfId="305"/>
+    <cellStyle name="20% - Énfasis4 20 2" xfId="600"/>
+    <cellStyle name="20% - Énfasis4 20 2 2" xfId="791"/>
+    <cellStyle name="20% - Énfasis4 20 3" xfId="790"/>
+    <cellStyle name="20% - Énfasis4 21" xfId="319"/>
+    <cellStyle name="20% - Énfasis4 21 2" xfId="614"/>
+    <cellStyle name="20% - Énfasis4 21 2 2" xfId="793"/>
+    <cellStyle name="20% - Énfasis4 21 3" xfId="792"/>
+    <cellStyle name="20% - Énfasis4 22" xfId="628"/>
+    <cellStyle name="20% - Énfasis4 22 2" xfId="795"/>
+    <cellStyle name="20% - Énfasis4 22 3" xfId="794"/>
+    <cellStyle name="20% - Énfasis4 23" xfId="332"/>
+    <cellStyle name="20% - Énfasis4 23 2" xfId="796"/>
+    <cellStyle name="20% - Énfasis4 24" xfId="767"/>
+    <cellStyle name="20% - Énfasis4 25" xfId="1272"/>
+    <cellStyle name="20% - Énfasis4 26" xfId="1286"/>
+    <cellStyle name="20% - Énfasis4 27" xfId="1300"/>
+    <cellStyle name="20% - Énfasis4 28" xfId="1314"/>
+    <cellStyle name="20% - Énfasis4 29" xfId="1328"/>
+    <cellStyle name="20% - Énfasis4 3" xfId="67"/>
+    <cellStyle name="20% - Énfasis4 3 2" xfId="362"/>
+    <cellStyle name="20% - Énfasis4 3 2 2" xfId="798"/>
+    <cellStyle name="20% - Énfasis4 3 3" xfId="797"/>
+    <cellStyle name="20% - Énfasis4 30" xfId="1342"/>
+    <cellStyle name="20% - Énfasis4 31" xfId="1356"/>
+    <cellStyle name="20% - Énfasis4 32" xfId="1370"/>
+    <cellStyle name="20% - Énfasis4 33" xfId="1384"/>
+    <cellStyle name="20% - Énfasis4 34" xfId="1398"/>
+    <cellStyle name="20% - Énfasis4 35" xfId="1412"/>
+    <cellStyle name="20% - Énfasis4 36" xfId="1426"/>
+    <cellStyle name="20% - Énfasis4 37" xfId="1440"/>
+    <cellStyle name="20% - Énfasis4 38" xfId="1454"/>
+    <cellStyle name="20% - Énfasis4 39" xfId="1468"/>
+    <cellStyle name="20% - Énfasis4 4" xfId="81"/>
+    <cellStyle name="20% - Énfasis4 4 2" xfId="376"/>
+    <cellStyle name="20% - Énfasis4 4 2 2" xfId="800"/>
+    <cellStyle name="20% - Énfasis4 4 3" xfId="799"/>
+    <cellStyle name="20% - Énfasis4 40" xfId="1483"/>
+    <cellStyle name="20% - Énfasis4 5" xfId="95"/>
+    <cellStyle name="20% - Énfasis4 5 2" xfId="390"/>
+    <cellStyle name="20% - Énfasis4 5 2 2" xfId="802"/>
+    <cellStyle name="20% - Énfasis4 5 3" xfId="801"/>
+    <cellStyle name="20% - Énfasis4 6" xfId="109"/>
+    <cellStyle name="20% - Énfasis4 6 2" xfId="404"/>
+    <cellStyle name="20% - Énfasis4 6 2 2" xfId="804"/>
+    <cellStyle name="20% - Énfasis4 6 3" xfId="803"/>
+    <cellStyle name="20% - Énfasis4 7" xfId="123"/>
+    <cellStyle name="20% - Énfasis4 7 2" xfId="418"/>
+    <cellStyle name="20% - Énfasis4 7 2 2" xfId="806"/>
+    <cellStyle name="20% - Énfasis4 7 3" xfId="805"/>
+    <cellStyle name="20% - Énfasis4 8" xfId="137"/>
+    <cellStyle name="20% - Énfasis4 8 2" xfId="432"/>
+    <cellStyle name="20% - Énfasis4 8 2 2" xfId="808"/>
+    <cellStyle name="20% - Énfasis4 8 3" xfId="807"/>
+    <cellStyle name="20% - Énfasis4 9" xfId="151"/>
+    <cellStyle name="20% - Énfasis4 9 2" xfId="446"/>
+    <cellStyle name="20% - Énfasis4 9 2 2" xfId="810"/>
+    <cellStyle name="20% - Énfasis4 9 3" xfId="809"/>
     <cellStyle name="20% - Énfasis5" xfId="36" builtinId="46" customBuiltin="1"/>
-    <cellStyle name="20% - Énfasis5 10" xfId="167" xr:uid="{00000000-0005-0000-0000-00009D010000}"/>
-    <cellStyle name="20% - Énfasis5 10 2" xfId="462" xr:uid="{00000000-0005-0000-0000-00009E010000}"/>
-    <cellStyle name="20% - Énfasis5 10 2 2" xfId="813" xr:uid="{00000000-0005-0000-0000-00009F010000}"/>
-    <cellStyle name="20% - Énfasis5 10 3" xfId="812" xr:uid="{00000000-0005-0000-0000-0000A0010000}"/>
-    <cellStyle name="20% - Énfasis5 11" xfId="181" xr:uid="{00000000-0005-0000-0000-0000A1010000}"/>
-    <cellStyle name="20% - Énfasis5 11 2" xfId="476" xr:uid="{00000000-0005-0000-0000-0000A2010000}"/>
-    <cellStyle name="20% - Énfasis5 11 2 2" xfId="815" xr:uid="{00000000-0005-0000-0000-0000A3010000}"/>
-    <cellStyle name="20% - Énfasis5 11 3" xfId="814" xr:uid="{00000000-0005-0000-0000-0000A4010000}"/>
-    <cellStyle name="20% - Énfasis5 12" xfId="195" xr:uid="{00000000-0005-0000-0000-0000A5010000}"/>
-    <cellStyle name="20% - Énfasis5 12 2" xfId="490" xr:uid="{00000000-0005-0000-0000-0000A6010000}"/>
-    <cellStyle name="20% - Énfasis5 12 2 2" xfId="817" xr:uid="{00000000-0005-0000-0000-0000A7010000}"/>
-    <cellStyle name="20% - Énfasis5 12 3" xfId="816" xr:uid="{00000000-0005-0000-0000-0000A8010000}"/>
-    <cellStyle name="20% - Énfasis5 13" xfId="209" xr:uid="{00000000-0005-0000-0000-0000A9010000}"/>
-    <cellStyle name="20% - Énfasis5 13 2" xfId="504" xr:uid="{00000000-0005-0000-0000-0000AA010000}"/>
-    <cellStyle name="20% - Énfasis5 13 2 2" xfId="819" xr:uid="{00000000-0005-0000-0000-0000AB010000}"/>
-    <cellStyle name="20% - Énfasis5 13 3" xfId="818" xr:uid="{00000000-0005-0000-0000-0000AC010000}"/>
-    <cellStyle name="20% - Énfasis5 14" xfId="223" xr:uid="{00000000-0005-0000-0000-0000AD010000}"/>
-    <cellStyle name="20% - Énfasis5 14 2" xfId="518" xr:uid="{00000000-0005-0000-0000-0000AE010000}"/>
-    <cellStyle name="20% - Énfasis5 14 2 2" xfId="821" xr:uid="{00000000-0005-0000-0000-0000AF010000}"/>
-    <cellStyle name="20% - Énfasis5 14 3" xfId="820" xr:uid="{00000000-0005-0000-0000-0000B0010000}"/>
-    <cellStyle name="20% - Énfasis5 15" xfId="237" xr:uid="{00000000-0005-0000-0000-0000B1010000}"/>
-    <cellStyle name="20% - Énfasis5 15 2" xfId="532" xr:uid="{00000000-0005-0000-0000-0000B2010000}"/>
-    <cellStyle name="20% - Énfasis5 15 2 2" xfId="823" xr:uid="{00000000-0005-0000-0000-0000B3010000}"/>
-    <cellStyle name="20% - Énfasis5 15 3" xfId="822" xr:uid="{00000000-0005-0000-0000-0000B4010000}"/>
-    <cellStyle name="20% - Énfasis5 16" xfId="251" xr:uid="{00000000-0005-0000-0000-0000B5010000}"/>
-    <cellStyle name="20% - Énfasis5 16 2" xfId="546" xr:uid="{00000000-0005-0000-0000-0000B6010000}"/>
-    <cellStyle name="20% - Énfasis5 16 2 2" xfId="825" xr:uid="{00000000-0005-0000-0000-0000B7010000}"/>
-    <cellStyle name="20% - Énfasis5 16 3" xfId="824" xr:uid="{00000000-0005-0000-0000-0000B8010000}"/>
-    <cellStyle name="20% - Énfasis5 17" xfId="265" xr:uid="{00000000-0005-0000-0000-0000B9010000}"/>
-    <cellStyle name="20% - Énfasis5 17 2" xfId="560" xr:uid="{00000000-0005-0000-0000-0000BA010000}"/>
-    <cellStyle name="20% - Énfasis5 17 2 2" xfId="827" xr:uid="{00000000-0005-0000-0000-0000BB010000}"/>
-    <cellStyle name="20% - Énfasis5 17 3" xfId="826" xr:uid="{00000000-0005-0000-0000-0000BC010000}"/>
-    <cellStyle name="20% - Énfasis5 18" xfId="279" xr:uid="{00000000-0005-0000-0000-0000BD010000}"/>
-    <cellStyle name="20% - Énfasis5 18 2" xfId="574" xr:uid="{00000000-0005-0000-0000-0000BE010000}"/>
-    <cellStyle name="20% - Énfasis5 18 2 2" xfId="829" xr:uid="{00000000-0005-0000-0000-0000BF010000}"/>
-    <cellStyle name="20% - Énfasis5 18 3" xfId="828" xr:uid="{00000000-0005-0000-0000-0000C0010000}"/>
-    <cellStyle name="20% - Énfasis5 19" xfId="293" xr:uid="{00000000-0005-0000-0000-0000C1010000}"/>
-    <cellStyle name="20% - Énfasis5 19 2" xfId="588" xr:uid="{00000000-0005-0000-0000-0000C2010000}"/>
-    <cellStyle name="20% - Énfasis5 19 2 2" xfId="831" xr:uid="{00000000-0005-0000-0000-0000C3010000}"/>
-    <cellStyle name="20% - Énfasis5 19 3" xfId="830" xr:uid="{00000000-0005-0000-0000-0000C4010000}"/>
-    <cellStyle name="20% - Énfasis5 2" xfId="55" xr:uid="{00000000-0005-0000-0000-0000C5010000}"/>
-    <cellStyle name="20% - Énfasis5 2 2" xfId="350" xr:uid="{00000000-0005-0000-0000-0000C6010000}"/>
-    <cellStyle name="20% - Énfasis5 2 2 2" xfId="833" xr:uid="{00000000-0005-0000-0000-0000C7010000}"/>
-    <cellStyle name="20% - Énfasis5 2 3" xfId="832" xr:uid="{00000000-0005-0000-0000-0000C8010000}"/>
-    <cellStyle name="20% - Énfasis5 20" xfId="307" xr:uid="{00000000-0005-0000-0000-0000C9010000}"/>
-    <cellStyle name="20% - Énfasis5 20 2" xfId="602" xr:uid="{00000000-0005-0000-0000-0000CA010000}"/>
-    <cellStyle name="20% - Énfasis5 20 2 2" xfId="835" xr:uid="{00000000-0005-0000-0000-0000CB010000}"/>
-    <cellStyle name="20% - Énfasis5 20 3" xfId="834" xr:uid="{00000000-0005-0000-0000-0000CC010000}"/>
-    <cellStyle name="20% - Énfasis5 21" xfId="321" xr:uid="{00000000-0005-0000-0000-0000CD010000}"/>
-    <cellStyle name="20% - Énfasis5 21 2" xfId="616" xr:uid="{00000000-0005-0000-0000-0000CE010000}"/>
-    <cellStyle name="20% - Énfasis5 21 2 2" xfId="837" xr:uid="{00000000-0005-0000-0000-0000CF010000}"/>
-    <cellStyle name="20% - Énfasis5 21 3" xfId="836" xr:uid="{00000000-0005-0000-0000-0000D0010000}"/>
-    <cellStyle name="20% - Énfasis5 22" xfId="630" xr:uid="{00000000-0005-0000-0000-0000D1010000}"/>
-    <cellStyle name="20% - Énfasis5 22 2" xfId="839" xr:uid="{00000000-0005-0000-0000-0000D2010000}"/>
-    <cellStyle name="20% - Énfasis5 22 3" xfId="838" xr:uid="{00000000-0005-0000-0000-0000D3010000}"/>
-    <cellStyle name="20% - Énfasis5 23" xfId="334" xr:uid="{00000000-0005-0000-0000-0000D4010000}"/>
-    <cellStyle name="20% - Énfasis5 23 2" xfId="840" xr:uid="{00000000-0005-0000-0000-0000D5010000}"/>
-    <cellStyle name="20% - Énfasis5 24" xfId="811" xr:uid="{00000000-0005-0000-0000-0000D6010000}"/>
-    <cellStyle name="20% - Énfasis5 25" xfId="1274" xr:uid="{00000000-0005-0000-0000-0000D7010000}"/>
-    <cellStyle name="20% - Énfasis5 26" xfId="1288" xr:uid="{00000000-0005-0000-0000-0000D8010000}"/>
-    <cellStyle name="20% - Énfasis5 27" xfId="1302" xr:uid="{00000000-0005-0000-0000-0000D9010000}"/>
-    <cellStyle name="20% - Énfasis5 28" xfId="1316" xr:uid="{00000000-0005-0000-0000-0000DA010000}"/>
-    <cellStyle name="20% - Énfasis5 29" xfId="1330" xr:uid="{00000000-0005-0000-0000-0000DB010000}"/>
-    <cellStyle name="20% - Énfasis5 3" xfId="69" xr:uid="{00000000-0005-0000-0000-0000DC010000}"/>
-    <cellStyle name="20% - Énfasis5 3 2" xfId="364" xr:uid="{00000000-0005-0000-0000-0000DD010000}"/>
-    <cellStyle name="20% - Énfasis5 3 2 2" xfId="842" xr:uid="{00000000-0005-0000-0000-0000DE010000}"/>
-    <cellStyle name="20% - Énfasis5 3 3" xfId="841" xr:uid="{00000000-0005-0000-0000-0000DF010000}"/>
-    <cellStyle name="20% - Énfasis5 30" xfId="1344" xr:uid="{00000000-0005-0000-0000-0000E0010000}"/>
-    <cellStyle name="20% - Énfasis5 31" xfId="1358" xr:uid="{00000000-0005-0000-0000-0000E1010000}"/>
-    <cellStyle name="20% - Énfasis5 32" xfId="1372" xr:uid="{00000000-0005-0000-0000-0000E2010000}"/>
-    <cellStyle name="20% - Énfasis5 33" xfId="1386" xr:uid="{00000000-0005-0000-0000-0000E3010000}"/>
-    <cellStyle name="20% - Énfasis5 34" xfId="1400" xr:uid="{00000000-0005-0000-0000-0000E4010000}"/>
-    <cellStyle name="20% - Énfasis5 35" xfId="1414" xr:uid="{00000000-0005-0000-0000-0000E5010000}"/>
-    <cellStyle name="20% - Énfasis5 36" xfId="1428" xr:uid="{00000000-0005-0000-0000-0000E6010000}"/>
-    <cellStyle name="20% - Énfasis5 37" xfId="1442" xr:uid="{00000000-0005-0000-0000-0000E7010000}"/>
-    <cellStyle name="20% - Énfasis5 38" xfId="1456" xr:uid="{00000000-0005-0000-0000-0000E8010000}"/>
-    <cellStyle name="20% - Énfasis5 39" xfId="1470" xr:uid="{00000000-0005-0000-0000-0000E9010000}"/>
-    <cellStyle name="20% - Énfasis5 4" xfId="83" xr:uid="{00000000-0005-0000-0000-0000EA010000}"/>
-    <cellStyle name="20% - Énfasis5 4 2" xfId="378" xr:uid="{00000000-0005-0000-0000-0000EB010000}"/>
-    <cellStyle name="20% - Énfasis5 4 2 2" xfId="844" xr:uid="{00000000-0005-0000-0000-0000EC010000}"/>
-    <cellStyle name="20% - Énfasis5 4 3" xfId="843" xr:uid="{00000000-0005-0000-0000-0000ED010000}"/>
-    <cellStyle name="20% - Énfasis5 40" xfId="1485" xr:uid="{00000000-0005-0000-0000-0000EE010000}"/>
-    <cellStyle name="20% - Énfasis5 5" xfId="97" xr:uid="{00000000-0005-0000-0000-0000EF010000}"/>
-    <cellStyle name="20% - Énfasis5 5 2" xfId="392" xr:uid="{00000000-0005-0000-0000-0000F0010000}"/>
-    <cellStyle name="20% - Énfasis5 5 2 2" xfId="846" xr:uid="{00000000-0005-0000-0000-0000F1010000}"/>
-    <cellStyle name="20% - Énfasis5 5 3" xfId="845" xr:uid="{00000000-0005-0000-0000-0000F2010000}"/>
-    <cellStyle name="20% - Énfasis5 6" xfId="111" xr:uid="{00000000-0005-0000-0000-0000F3010000}"/>
-    <cellStyle name="20% - Énfasis5 6 2" xfId="406" xr:uid="{00000000-0005-0000-0000-0000F4010000}"/>
-    <cellStyle name="20% - Énfasis5 6 2 2" xfId="848" xr:uid="{00000000-0005-0000-0000-0000F5010000}"/>
-    <cellStyle name="20% - Énfasis5 6 3" xfId="847" xr:uid="{00000000-0005-0000-0000-0000F6010000}"/>
-    <cellStyle name="20% - Énfasis5 7" xfId="125" xr:uid="{00000000-0005-0000-0000-0000F7010000}"/>
-    <cellStyle name="20% - Énfasis5 7 2" xfId="420" xr:uid="{00000000-0005-0000-0000-0000F8010000}"/>
-    <cellStyle name="20% - Énfasis5 7 2 2" xfId="850" xr:uid="{00000000-0005-0000-0000-0000F9010000}"/>
-    <cellStyle name="20% - Énfasis5 7 3" xfId="849" xr:uid="{00000000-0005-0000-0000-0000FA010000}"/>
-    <cellStyle name="20% - Énfasis5 8" xfId="139" xr:uid="{00000000-0005-0000-0000-0000FB010000}"/>
-    <cellStyle name="20% - Énfasis5 8 2" xfId="434" xr:uid="{00000000-0005-0000-0000-0000FC010000}"/>
-    <cellStyle name="20% - Énfasis5 8 2 2" xfId="852" xr:uid="{00000000-0005-0000-0000-0000FD010000}"/>
-    <cellStyle name="20% - Énfasis5 8 3" xfId="851" xr:uid="{00000000-0005-0000-0000-0000FE010000}"/>
-    <cellStyle name="20% - Énfasis5 9" xfId="153" xr:uid="{00000000-0005-0000-0000-0000FF010000}"/>
-    <cellStyle name="20% - Énfasis5 9 2" xfId="448" xr:uid="{00000000-0005-0000-0000-000000020000}"/>
-    <cellStyle name="20% - Énfasis5 9 2 2" xfId="854" xr:uid="{00000000-0005-0000-0000-000001020000}"/>
-    <cellStyle name="20% - Énfasis5 9 3" xfId="853" xr:uid="{00000000-0005-0000-0000-000002020000}"/>
+    <cellStyle name="20% - Énfasis5 10" xfId="167"/>
+    <cellStyle name="20% - Énfasis5 10 2" xfId="462"/>
+    <cellStyle name="20% - Énfasis5 10 2 2" xfId="813"/>
+    <cellStyle name="20% - Énfasis5 10 3" xfId="812"/>
+    <cellStyle name="20% - Énfasis5 11" xfId="181"/>
+    <cellStyle name="20% - Énfasis5 11 2" xfId="476"/>
+    <cellStyle name="20% - Énfasis5 11 2 2" xfId="815"/>
+    <cellStyle name="20% - Énfasis5 11 3" xfId="814"/>
+    <cellStyle name="20% - Énfasis5 12" xfId="195"/>
+    <cellStyle name="20% - Énfasis5 12 2" xfId="490"/>
+    <cellStyle name="20% - Énfasis5 12 2 2" xfId="817"/>
+    <cellStyle name="20% - Énfasis5 12 3" xfId="816"/>
+    <cellStyle name="20% - Énfasis5 13" xfId="209"/>
+    <cellStyle name="20% - Énfasis5 13 2" xfId="504"/>
+    <cellStyle name="20% - Énfasis5 13 2 2" xfId="819"/>
+    <cellStyle name="20% - Énfasis5 13 3" xfId="818"/>
+    <cellStyle name="20% - Énfasis5 14" xfId="223"/>
+    <cellStyle name="20% - Énfasis5 14 2" xfId="518"/>
+    <cellStyle name="20% - Énfasis5 14 2 2" xfId="821"/>
+    <cellStyle name="20% - Énfasis5 14 3" xfId="820"/>
+    <cellStyle name="20% - Énfasis5 15" xfId="237"/>
+    <cellStyle name="20% - Énfasis5 15 2" xfId="532"/>
+    <cellStyle name="20% - Énfasis5 15 2 2" xfId="823"/>
+    <cellStyle name="20% - Énfasis5 15 3" xfId="822"/>
+    <cellStyle name="20% - Énfasis5 16" xfId="251"/>
+    <cellStyle name="20% - Énfasis5 16 2" xfId="546"/>
+    <cellStyle name="20% - Énfasis5 16 2 2" xfId="825"/>
+    <cellStyle name="20% - Énfasis5 16 3" xfId="824"/>
+    <cellStyle name="20% - Énfasis5 17" xfId="265"/>
+    <cellStyle name="20% - Énfasis5 17 2" xfId="560"/>
+    <cellStyle name="20% - Énfasis5 17 2 2" xfId="827"/>
+    <cellStyle name="20% - Énfasis5 17 3" xfId="826"/>
+    <cellStyle name="20% - Énfasis5 18" xfId="279"/>
+    <cellStyle name="20% - Énfasis5 18 2" xfId="574"/>
+    <cellStyle name="20% - Énfasis5 18 2 2" xfId="829"/>
+    <cellStyle name="20% - Énfasis5 18 3" xfId="828"/>
+    <cellStyle name="20% - Énfasis5 19" xfId="293"/>
+    <cellStyle name="20% - Énfasis5 19 2" xfId="588"/>
+    <cellStyle name="20% - Énfasis5 19 2 2" xfId="831"/>
+    <cellStyle name="20% - Énfasis5 19 3" xfId="830"/>
+    <cellStyle name="20% - Énfasis5 2" xfId="55"/>
+    <cellStyle name="20% - Énfasis5 2 2" xfId="350"/>
+    <cellStyle name="20% - Énfasis5 2 2 2" xfId="833"/>
+    <cellStyle name="20% - Énfasis5 2 3" xfId="832"/>
+    <cellStyle name="20% - Énfasis5 20" xfId="307"/>
+    <cellStyle name="20% - Énfasis5 20 2" xfId="602"/>
+    <cellStyle name="20% - Énfasis5 20 2 2" xfId="835"/>
+    <cellStyle name="20% - Énfasis5 20 3" xfId="834"/>
+    <cellStyle name="20% - Énfasis5 21" xfId="321"/>
+    <cellStyle name="20% - Énfasis5 21 2" xfId="616"/>
+    <cellStyle name="20% - Énfasis5 21 2 2" xfId="837"/>
+    <cellStyle name="20% - Énfasis5 21 3" xfId="836"/>
+    <cellStyle name="20% - Énfasis5 22" xfId="630"/>
+    <cellStyle name="20% - Énfasis5 22 2" xfId="839"/>
+    <cellStyle name="20% - Énfasis5 22 3" xfId="838"/>
+    <cellStyle name="20% - Énfasis5 23" xfId="334"/>
+    <cellStyle name="20% - Énfasis5 23 2" xfId="840"/>
+    <cellStyle name="20% - Énfasis5 24" xfId="811"/>
+    <cellStyle name="20% - Énfasis5 25" xfId="1274"/>
+    <cellStyle name="20% - Énfasis5 26" xfId="1288"/>
+    <cellStyle name="20% - Énfasis5 27" xfId="1302"/>
+    <cellStyle name="20% - Énfasis5 28" xfId="1316"/>
+    <cellStyle name="20% - Énfasis5 29" xfId="1330"/>
+    <cellStyle name="20% - Énfasis5 3" xfId="69"/>
+    <cellStyle name="20% - Énfasis5 3 2" xfId="364"/>
+    <cellStyle name="20% - Énfasis5 3 2 2" xfId="842"/>
+    <cellStyle name="20% - Énfasis5 3 3" xfId="841"/>
+    <cellStyle name="20% - Énfasis5 30" xfId="1344"/>
+    <cellStyle name="20% - Énfasis5 31" xfId="1358"/>
+    <cellStyle name="20% - Énfasis5 32" xfId="1372"/>
+    <cellStyle name="20% - Énfasis5 33" xfId="1386"/>
+    <cellStyle name="20% - Énfasis5 34" xfId="1400"/>
+    <cellStyle name="20% - Énfasis5 35" xfId="1414"/>
+    <cellStyle name="20% - Énfasis5 36" xfId="1428"/>
+    <cellStyle name="20% - Énfasis5 37" xfId="1442"/>
+    <cellStyle name="20% - Énfasis5 38" xfId="1456"/>
+    <cellStyle name="20% - Énfasis5 39" xfId="1470"/>
+    <cellStyle name="20% - Énfasis5 4" xfId="83"/>
+    <cellStyle name="20% - Énfasis5 4 2" xfId="378"/>
+    <cellStyle name="20% - Énfasis5 4 2 2" xfId="844"/>
+    <cellStyle name="20% - Énfasis5 4 3" xfId="843"/>
+    <cellStyle name="20% - Énfasis5 40" xfId="1485"/>
+    <cellStyle name="20% - Énfasis5 5" xfId="97"/>
+    <cellStyle name="20% - Énfasis5 5 2" xfId="392"/>
+    <cellStyle name="20% - Énfasis5 5 2 2" xfId="846"/>
+    <cellStyle name="20% - Énfasis5 5 3" xfId="845"/>
+    <cellStyle name="20% - Énfasis5 6" xfId="111"/>
+    <cellStyle name="20% - Énfasis5 6 2" xfId="406"/>
+    <cellStyle name="20% - Énfasis5 6 2 2" xfId="848"/>
+    <cellStyle name="20% - Énfasis5 6 3" xfId="847"/>
+    <cellStyle name="20% - Énfasis5 7" xfId="125"/>
+    <cellStyle name="20% - Énfasis5 7 2" xfId="420"/>
+    <cellStyle name="20% - Énfasis5 7 2 2" xfId="850"/>
+    <cellStyle name="20% - Énfasis5 7 3" xfId="849"/>
+    <cellStyle name="20% - Énfasis5 8" xfId="139"/>
+    <cellStyle name="20% - Énfasis5 8 2" xfId="434"/>
+    <cellStyle name="20% - Énfasis5 8 2 2" xfId="852"/>
+    <cellStyle name="20% - Énfasis5 8 3" xfId="851"/>
+    <cellStyle name="20% - Énfasis5 9" xfId="153"/>
+    <cellStyle name="20% - Énfasis5 9 2" xfId="448"/>
+    <cellStyle name="20% - Énfasis5 9 2 2" xfId="854"/>
+    <cellStyle name="20% - Énfasis5 9 3" xfId="853"/>
     <cellStyle name="20% - Énfasis6" xfId="40" builtinId="50" customBuiltin="1"/>
-    <cellStyle name="20% - Énfasis6 10" xfId="169" xr:uid="{00000000-0005-0000-0000-000004020000}"/>
-    <cellStyle name="20% - Énfasis6 10 2" xfId="464" xr:uid="{00000000-0005-0000-0000-000005020000}"/>
-    <cellStyle name="20% - Énfasis6 10 2 2" xfId="857" xr:uid="{00000000-0005-0000-0000-000006020000}"/>
-    <cellStyle name="20% - Énfasis6 10 3" xfId="856" xr:uid="{00000000-0005-0000-0000-000007020000}"/>
-    <cellStyle name="20% - Énfasis6 11" xfId="183" xr:uid="{00000000-0005-0000-0000-000008020000}"/>
-    <cellStyle name="20% - Énfasis6 11 2" xfId="478" xr:uid="{00000000-0005-0000-0000-000009020000}"/>
-    <cellStyle name="20% - Énfasis6 11 2 2" xfId="859" xr:uid="{00000000-0005-0000-0000-00000A020000}"/>
-    <cellStyle name="20% - Énfasis6 11 3" xfId="858" xr:uid="{00000000-0005-0000-0000-00000B020000}"/>
-    <cellStyle name="20% - Énfasis6 12" xfId="197" xr:uid="{00000000-0005-0000-0000-00000C020000}"/>
-    <cellStyle name="20% - Énfasis6 12 2" xfId="492" xr:uid="{00000000-0005-0000-0000-00000D020000}"/>
-    <cellStyle name="20% - Énfasis6 12 2 2" xfId="861" xr:uid="{00000000-0005-0000-0000-00000E020000}"/>
-    <cellStyle name="20% - Énfasis6 12 3" xfId="860" xr:uid="{00000000-0005-0000-0000-00000F020000}"/>
-    <cellStyle name="20% - Énfasis6 13" xfId="211" xr:uid="{00000000-0005-0000-0000-000010020000}"/>
-    <cellStyle name="20% - Énfasis6 13 2" xfId="506" xr:uid="{00000000-0005-0000-0000-000011020000}"/>
-    <cellStyle name="20% - Énfasis6 13 2 2" xfId="863" xr:uid="{00000000-0005-0000-0000-000012020000}"/>
-    <cellStyle name="20% - Énfasis6 13 3" xfId="862" xr:uid="{00000000-0005-0000-0000-000013020000}"/>
-    <cellStyle name="20% - Énfasis6 14" xfId="225" xr:uid="{00000000-0005-0000-0000-000014020000}"/>
-    <cellStyle name="20% - Énfasis6 14 2" xfId="520" xr:uid="{00000000-0005-0000-0000-000015020000}"/>
-    <cellStyle name="20% - Énfasis6 14 2 2" xfId="865" xr:uid="{00000000-0005-0000-0000-000016020000}"/>
-    <cellStyle name="20% - Énfasis6 14 3" xfId="864" xr:uid="{00000000-0005-0000-0000-000017020000}"/>
-    <cellStyle name="20% - Énfasis6 15" xfId="239" xr:uid="{00000000-0005-0000-0000-000018020000}"/>
-    <cellStyle name="20% - Énfasis6 15 2" xfId="534" xr:uid="{00000000-0005-0000-0000-000019020000}"/>
-    <cellStyle name="20% - Énfasis6 15 2 2" xfId="867" xr:uid="{00000000-0005-0000-0000-00001A020000}"/>
-    <cellStyle name="20% - Énfasis6 15 3" xfId="866" xr:uid="{00000000-0005-0000-0000-00001B020000}"/>
-    <cellStyle name="20% - Énfasis6 16" xfId="253" xr:uid="{00000000-0005-0000-0000-00001C020000}"/>
-    <cellStyle name="20% - Énfasis6 16 2" xfId="548" xr:uid="{00000000-0005-0000-0000-00001D020000}"/>
-    <cellStyle name="20% - Énfasis6 16 2 2" xfId="869" xr:uid="{00000000-0005-0000-0000-00001E020000}"/>
-    <cellStyle name="20% - Énfasis6 16 3" xfId="868" xr:uid="{00000000-0005-0000-0000-00001F020000}"/>
-    <cellStyle name="20% - Énfasis6 17" xfId="267" xr:uid="{00000000-0005-0000-0000-000020020000}"/>
-    <cellStyle name="20% - Énfasis6 17 2" xfId="562" xr:uid="{00000000-0005-0000-0000-000021020000}"/>
-    <cellStyle name="20% - Énfasis6 17 2 2" xfId="871" xr:uid="{00000000-0005-0000-0000-000022020000}"/>
-    <cellStyle name="20% - Énfasis6 17 3" xfId="870" xr:uid="{00000000-0005-0000-0000-000023020000}"/>
-    <cellStyle name="20% - Énfasis6 18" xfId="281" xr:uid="{00000000-0005-0000-0000-000024020000}"/>
-    <cellStyle name="20% - Énfasis6 18 2" xfId="576" xr:uid="{00000000-0005-0000-0000-000025020000}"/>
-    <cellStyle name="20% - Énfasis6 18 2 2" xfId="873" xr:uid="{00000000-0005-0000-0000-000026020000}"/>
-    <cellStyle name="20% - Énfasis6 18 3" xfId="872" xr:uid="{00000000-0005-0000-0000-000027020000}"/>
-    <cellStyle name="20% - Énfasis6 19" xfId="295" xr:uid="{00000000-0005-0000-0000-000028020000}"/>
-    <cellStyle name="20% - Énfasis6 19 2" xfId="590" xr:uid="{00000000-0005-0000-0000-000029020000}"/>
-    <cellStyle name="20% - Énfasis6 19 2 2" xfId="875" xr:uid="{00000000-0005-0000-0000-00002A020000}"/>
-    <cellStyle name="20% - Énfasis6 19 3" xfId="874" xr:uid="{00000000-0005-0000-0000-00002B020000}"/>
-    <cellStyle name="20% - Énfasis6 2" xfId="57" xr:uid="{00000000-0005-0000-0000-00002C020000}"/>
-    <cellStyle name="20% - Énfasis6 2 2" xfId="352" xr:uid="{00000000-0005-0000-0000-00002D020000}"/>
-    <cellStyle name="20% - Énfasis6 2 2 2" xfId="877" xr:uid="{00000000-0005-0000-0000-00002E020000}"/>
-    <cellStyle name="20% - Énfasis6 2 3" xfId="876" xr:uid="{00000000-0005-0000-0000-00002F020000}"/>
-    <cellStyle name="20% - Énfasis6 20" xfId="309" xr:uid="{00000000-0005-0000-0000-000030020000}"/>
-    <cellStyle name="20% - Énfasis6 20 2" xfId="604" xr:uid="{00000000-0005-0000-0000-000031020000}"/>
-    <cellStyle name="20% - Énfasis6 20 2 2" xfId="879" xr:uid="{00000000-0005-0000-0000-000032020000}"/>
-    <cellStyle name="20% - Énfasis6 20 3" xfId="878" xr:uid="{00000000-0005-0000-0000-000033020000}"/>
-    <cellStyle name="20% - Énfasis6 21" xfId="323" xr:uid="{00000000-0005-0000-0000-000034020000}"/>
-    <cellStyle name="20% - Énfasis6 21 2" xfId="618" xr:uid="{00000000-0005-0000-0000-000035020000}"/>
-    <cellStyle name="20% - Énfasis6 21 2 2" xfId="881" xr:uid="{00000000-0005-0000-0000-000036020000}"/>
-    <cellStyle name="20% - Énfasis6 21 3" xfId="880" xr:uid="{00000000-0005-0000-0000-000037020000}"/>
-    <cellStyle name="20% - Énfasis6 22" xfId="632" xr:uid="{00000000-0005-0000-0000-000038020000}"/>
-    <cellStyle name="20% - Énfasis6 22 2" xfId="883" xr:uid="{00000000-0005-0000-0000-000039020000}"/>
-    <cellStyle name="20% - Énfasis6 22 3" xfId="882" xr:uid="{00000000-0005-0000-0000-00003A020000}"/>
-    <cellStyle name="20% - Énfasis6 23" xfId="336" xr:uid="{00000000-0005-0000-0000-00003B020000}"/>
-    <cellStyle name="20% - Énfasis6 23 2" xfId="884" xr:uid="{00000000-0005-0000-0000-00003C020000}"/>
-    <cellStyle name="20% - Énfasis6 24" xfId="855" xr:uid="{00000000-0005-0000-0000-00003D020000}"/>
-    <cellStyle name="20% - Énfasis6 25" xfId="1276" xr:uid="{00000000-0005-0000-0000-00003E020000}"/>
-    <cellStyle name="20% - Énfasis6 26" xfId="1290" xr:uid="{00000000-0005-0000-0000-00003F020000}"/>
-    <cellStyle name="20% - Énfasis6 27" xfId="1304" xr:uid="{00000000-0005-0000-0000-000040020000}"/>
-    <cellStyle name="20% - Énfasis6 28" xfId="1318" xr:uid="{00000000-0005-0000-0000-000041020000}"/>
-    <cellStyle name="20% - Énfasis6 29" xfId="1332" xr:uid="{00000000-0005-0000-0000-000042020000}"/>
-    <cellStyle name="20% - Énfasis6 3" xfId="71" xr:uid="{00000000-0005-0000-0000-000043020000}"/>
-    <cellStyle name="20% - Énfasis6 3 2" xfId="366" xr:uid="{00000000-0005-0000-0000-000044020000}"/>
-    <cellStyle name="20% - Énfasis6 3 2 2" xfId="886" xr:uid="{00000000-0005-0000-0000-000045020000}"/>
-    <cellStyle name="20% - Énfasis6 3 3" xfId="885" xr:uid="{00000000-0005-0000-0000-000046020000}"/>
-    <cellStyle name="20% - Énfasis6 30" xfId="1346" xr:uid="{00000000-0005-0000-0000-000047020000}"/>
-    <cellStyle name="20% - Énfasis6 31" xfId="1360" xr:uid="{00000000-0005-0000-0000-000048020000}"/>
-    <cellStyle name="20% - Énfasis6 32" xfId="1374" xr:uid="{00000000-0005-0000-0000-000049020000}"/>
-    <cellStyle name="20% - Énfasis6 33" xfId="1388" xr:uid="{00000000-0005-0000-0000-00004A020000}"/>
-    <cellStyle name="20% - Énfasis6 34" xfId="1402" xr:uid="{00000000-0005-0000-0000-00004B020000}"/>
-    <cellStyle name="20% - Énfasis6 35" xfId="1416" xr:uid="{00000000-0005-0000-0000-00004C020000}"/>
-    <cellStyle name="20% - Énfasis6 36" xfId="1430" xr:uid="{00000000-0005-0000-0000-00004D020000}"/>
-    <cellStyle name="20% - Énfasis6 37" xfId="1444" xr:uid="{00000000-0005-0000-0000-00004E020000}"/>
-    <cellStyle name="20% - Énfasis6 38" xfId="1458" xr:uid="{00000000-0005-0000-0000-00004F020000}"/>
-    <cellStyle name="20% - Énfasis6 39" xfId="1472" xr:uid="{00000000-0005-0000-0000-000050020000}"/>
-    <cellStyle name="20% - Énfasis6 4" xfId="85" xr:uid="{00000000-0005-0000-0000-000051020000}"/>
-    <cellStyle name="20% - Énfasis6 4 2" xfId="380" xr:uid="{00000000-0005-0000-0000-000052020000}"/>
-    <cellStyle name="20% - Énfasis6 4 2 2" xfId="888" xr:uid="{00000000-0005-0000-0000-000053020000}"/>
-    <cellStyle name="20% - Énfasis6 4 3" xfId="887" xr:uid="{00000000-0005-0000-0000-000054020000}"/>
-    <cellStyle name="20% - Énfasis6 40" xfId="1487" xr:uid="{00000000-0005-0000-0000-000055020000}"/>
-    <cellStyle name="20% - Énfasis6 5" xfId="99" xr:uid="{00000000-0005-0000-0000-000056020000}"/>
-    <cellStyle name="20% - Énfasis6 5 2" xfId="394" xr:uid="{00000000-0005-0000-0000-000057020000}"/>
-    <cellStyle name="20% - Énfasis6 5 2 2" xfId="890" xr:uid="{00000000-0005-0000-0000-000058020000}"/>
-    <cellStyle name="20% - Énfasis6 5 3" xfId="889" xr:uid="{00000000-0005-0000-0000-000059020000}"/>
-    <cellStyle name="20% - Énfasis6 6" xfId="113" xr:uid="{00000000-0005-0000-0000-00005A020000}"/>
-    <cellStyle name="20% - Énfasis6 6 2" xfId="408" xr:uid="{00000000-0005-0000-0000-00005B020000}"/>
-    <cellStyle name="20% - Énfasis6 6 2 2" xfId="892" xr:uid="{00000000-0005-0000-0000-00005C020000}"/>
-    <cellStyle name="20% - Énfasis6 6 3" xfId="891" xr:uid="{00000000-0005-0000-0000-00005D020000}"/>
-    <cellStyle name="20% - Énfasis6 7" xfId="127" xr:uid="{00000000-0005-0000-0000-00005E020000}"/>
-    <cellStyle name="20% - Énfasis6 7 2" xfId="422" xr:uid="{00000000-0005-0000-0000-00005F020000}"/>
-    <cellStyle name="20% - Énfasis6 7 2 2" xfId="894" xr:uid="{00000000-0005-0000-0000-000060020000}"/>
-    <cellStyle name="20% - Énfasis6 7 3" xfId="893" xr:uid="{00000000-0005-0000-0000-000061020000}"/>
-    <cellStyle name="20% - Énfasis6 8" xfId="141" xr:uid="{00000000-0005-0000-0000-000062020000}"/>
-    <cellStyle name="20% - Énfasis6 8 2" xfId="436" xr:uid="{00000000-0005-0000-0000-000063020000}"/>
-    <cellStyle name="20% - Énfasis6 8 2 2" xfId="896" xr:uid="{00000000-0005-0000-0000-000064020000}"/>
-    <cellStyle name="20% - Énfasis6 8 3" xfId="895" xr:uid="{00000000-0005-0000-0000-000065020000}"/>
-    <cellStyle name="20% - Énfasis6 9" xfId="155" xr:uid="{00000000-0005-0000-0000-000066020000}"/>
-    <cellStyle name="20% - Énfasis6 9 2" xfId="450" xr:uid="{00000000-0005-0000-0000-000067020000}"/>
-    <cellStyle name="20% - Énfasis6 9 2 2" xfId="898" xr:uid="{00000000-0005-0000-0000-000068020000}"/>
-    <cellStyle name="20% - Énfasis6 9 3" xfId="897" xr:uid="{00000000-0005-0000-0000-000069020000}"/>
+    <cellStyle name="20% - Énfasis6 10" xfId="169"/>
+    <cellStyle name="20% - Énfasis6 10 2" xfId="464"/>
+    <cellStyle name="20% - Énfasis6 10 2 2" xfId="857"/>
+    <cellStyle name="20% - Énfasis6 10 3" xfId="856"/>
+    <cellStyle name="20% - Énfasis6 11" xfId="183"/>
+    <cellStyle name="20% - Énfasis6 11 2" xfId="478"/>
+    <cellStyle name="20% - Énfasis6 11 2 2" xfId="859"/>
+    <cellStyle name="20% - Énfasis6 11 3" xfId="858"/>
+    <cellStyle name="20% - Énfasis6 12" xfId="197"/>
+    <cellStyle name="20% - Énfasis6 12 2" xfId="492"/>
+    <cellStyle name="20% - Énfasis6 12 2 2" xfId="861"/>
+    <cellStyle name="20% - Énfasis6 12 3" xfId="860"/>
+    <cellStyle name="20% - Énfasis6 13" xfId="211"/>
+    <cellStyle name="20% - Énfasis6 13 2" xfId="506"/>
+    <cellStyle name="20% - Énfasis6 13 2 2" xfId="863"/>
+    <cellStyle name="20% - Énfasis6 13 3" xfId="862"/>
+    <cellStyle name="20% - Énfasis6 14" xfId="225"/>
+    <cellStyle name="20% - Énfasis6 14 2" xfId="520"/>
+    <cellStyle name="20% - Énfasis6 14 2 2" xfId="865"/>
+    <cellStyle name="20% - Énfasis6 14 3" xfId="864"/>
+    <cellStyle name="20% - Énfasis6 15" xfId="239"/>
+    <cellStyle name="20% - Énfasis6 15 2" xfId="534"/>
+    <cellStyle name="20% - Énfasis6 15 2 2" xfId="867"/>
+    <cellStyle name="20% - Énfasis6 15 3" xfId="866"/>
+    <cellStyle name="20% - Énfasis6 16" xfId="253"/>
+    <cellStyle name="20% - Énfasis6 16 2" xfId="548"/>
+    <cellStyle name="20% - Énfasis6 16 2 2" xfId="869"/>
+    <cellStyle name="20% - Énfasis6 16 3" xfId="868"/>
+    <cellStyle name="20% - Énfasis6 17" xfId="267"/>
+    <cellStyle name="20% - Énfasis6 17 2" xfId="562"/>
+    <cellStyle name="20% - Énfasis6 17 2 2" xfId="871"/>
+    <cellStyle name="20% - Énfasis6 17 3" xfId="870"/>
+    <cellStyle name="20% - Énfasis6 18" xfId="281"/>
+    <cellStyle name="20% - Énfasis6 18 2" xfId="576"/>
+    <cellStyle name="20% - Énfasis6 18 2 2" xfId="873"/>
+    <cellStyle name="20% - Énfasis6 18 3" xfId="872"/>
+    <cellStyle name="20% - Énfasis6 19" xfId="295"/>
+    <cellStyle name="20% - Énfasis6 19 2" xfId="590"/>
+    <cellStyle name="20% - Énfasis6 19 2 2" xfId="875"/>
+    <cellStyle name="20% - Énfasis6 19 3" xfId="874"/>
+    <cellStyle name="20% - Énfasis6 2" xfId="57"/>
+    <cellStyle name="20% - Énfasis6 2 2" xfId="352"/>
+    <cellStyle name="20% - Énfasis6 2 2 2" xfId="877"/>
+    <cellStyle name="20% - Énfasis6 2 3" xfId="876"/>
+    <cellStyle name="20% - Énfasis6 20" xfId="309"/>
+    <cellStyle name="20% - Énfasis6 20 2" xfId="604"/>
+    <cellStyle name="20% - Énfasis6 20 2 2" xfId="879"/>
+    <cellStyle name="20% - Énfasis6 20 3" xfId="878"/>
+    <cellStyle name="20% - Énfasis6 21" xfId="323"/>
+    <cellStyle name="20% - Énfasis6 21 2" xfId="618"/>
+    <cellStyle name="20% - Énfasis6 21 2 2" xfId="881"/>
+    <cellStyle name="20% - Énfasis6 21 3" xfId="880"/>
+    <cellStyle name="20% - Énfasis6 22" xfId="632"/>
+    <cellStyle name="20% - Énfasis6 22 2" xfId="883"/>
+    <cellStyle name="20% - Énfasis6 22 3" xfId="882"/>
+    <cellStyle name="20% - Énfasis6 23" xfId="336"/>
+    <cellStyle name="20% - Énfasis6 23 2" xfId="884"/>
+    <cellStyle name="20% - Énfasis6 24" xfId="855"/>
+    <cellStyle name="20% - Énfasis6 25" xfId="1276"/>
+    <cellStyle name="20% - Énfasis6 26" xfId="1290"/>
+    <cellStyle name="20% - Énfasis6 27" xfId="1304"/>
+    <cellStyle name="20% - Énfasis6 28" xfId="1318"/>
+    <cellStyle name="20% - Énfasis6 29" xfId="1332"/>
+    <cellStyle name="20% - Énfasis6 3" xfId="71"/>
+    <cellStyle name="20% - Énfasis6 3 2" xfId="366"/>
+    <cellStyle name="20% - Énfasis6 3 2 2" xfId="886"/>
+    <cellStyle name="20% - Énfasis6 3 3" xfId="885"/>
+    <cellStyle name="20% - Énfasis6 30" xfId="1346"/>
+    <cellStyle name="20% - Énfasis6 31" xfId="1360"/>
+    <cellStyle name="20% - Énfasis6 32" xfId="1374"/>
+    <cellStyle name="20% - Énfasis6 33" xfId="1388"/>
+    <cellStyle name="20% - Énfasis6 34" xfId="1402"/>
+    <cellStyle name="20% - Énfasis6 35" xfId="1416"/>
+    <cellStyle name="20% - Énfasis6 36" xfId="1430"/>
+    <cellStyle name="20% - Énfasis6 37" xfId="1444"/>
+    <cellStyle name="20% - Énfasis6 38" xfId="1458"/>
+    <cellStyle name="20% - Énfasis6 39" xfId="1472"/>
+    <cellStyle name="20% - Énfasis6 4" xfId="85"/>
+    <cellStyle name="20% - Énfasis6 4 2" xfId="380"/>
+    <cellStyle name="20% - Énfasis6 4 2 2" xfId="888"/>
+    <cellStyle name="20% - Énfasis6 4 3" xfId="887"/>
+    <cellStyle name="20% - Énfasis6 40" xfId="1487"/>
+    <cellStyle name="20% - Énfasis6 5" xfId="99"/>
+    <cellStyle name="20% - Énfasis6 5 2" xfId="394"/>
+    <cellStyle name="20% - Énfasis6 5 2 2" xfId="890"/>
+    <cellStyle name="20% - Énfasis6 5 3" xfId="889"/>
+    <cellStyle name="20% - Énfasis6 6" xfId="113"/>
+    <cellStyle name="20% - Énfasis6 6 2" xfId="408"/>
+    <cellStyle name="20% - Énfasis6 6 2 2" xfId="892"/>
+    <cellStyle name="20% - Énfasis6 6 3" xfId="891"/>
+    <cellStyle name="20% - Énfasis6 7" xfId="127"/>
+    <cellStyle name="20% - Énfasis6 7 2" xfId="422"/>
+    <cellStyle name="20% - Énfasis6 7 2 2" xfId="894"/>
+    <cellStyle name="20% - Énfasis6 7 3" xfId="893"/>
+    <cellStyle name="20% - Énfasis6 8" xfId="141"/>
+    <cellStyle name="20% - Énfasis6 8 2" xfId="436"/>
+    <cellStyle name="20% - Énfasis6 8 2 2" xfId="896"/>
+    <cellStyle name="20% - Énfasis6 8 3" xfId="895"/>
+    <cellStyle name="20% - Énfasis6 9" xfId="155"/>
+    <cellStyle name="20% - Énfasis6 9 2" xfId="450"/>
+    <cellStyle name="20% - Énfasis6 9 2 2" xfId="898"/>
+    <cellStyle name="20% - Énfasis6 9 3" xfId="897"/>
     <cellStyle name="40% - Énfasis1" xfId="21" builtinId="31" customBuiltin="1"/>
-    <cellStyle name="40% - Énfasis1 10" xfId="160" xr:uid="{00000000-0005-0000-0000-00006B020000}"/>
-    <cellStyle name="40% - Énfasis1 10 2" xfId="455" xr:uid="{00000000-0005-0000-0000-00006C020000}"/>
-    <cellStyle name="40% - Énfasis1 10 2 2" xfId="901" xr:uid="{00000000-0005-0000-0000-00006D020000}"/>
-    <cellStyle name="40% - Énfasis1 10 3" xfId="900" xr:uid="{00000000-0005-0000-0000-00006E020000}"/>
-    <cellStyle name="40% - Énfasis1 11" xfId="174" xr:uid="{00000000-0005-0000-0000-00006F020000}"/>
-    <cellStyle name="40% - Énfasis1 11 2" xfId="469" xr:uid="{00000000-0005-0000-0000-000070020000}"/>
-    <cellStyle name="40% - Énfasis1 11 2 2" xfId="903" xr:uid="{00000000-0005-0000-0000-000071020000}"/>
-    <cellStyle name="40% - Énfasis1 11 3" xfId="902" xr:uid="{00000000-0005-0000-0000-000072020000}"/>
-    <cellStyle name="40% - Énfasis1 12" xfId="188" xr:uid="{00000000-0005-0000-0000-000073020000}"/>
-    <cellStyle name="40% - Énfasis1 12 2" xfId="483" xr:uid="{00000000-0005-0000-0000-000074020000}"/>
-    <cellStyle name="40% - Énfasis1 12 2 2" xfId="905" xr:uid="{00000000-0005-0000-0000-000075020000}"/>
-    <cellStyle name="40% - Énfasis1 12 3" xfId="904" xr:uid="{00000000-0005-0000-0000-000076020000}"/>
-    <cellStyle name="40% - Énfasis1 13" xfId="202" xr:uid="{00000000-0005-0000-0000-000077020000}"/>
-    <cellStyle name="40% - Énfasis1 13 2" xfId="497" xr:uid="{00000000-0005-0000-0000-000078020000}"/>
-    <cellStyle name="40% - Énfasis1 13 2 2" xfId="907" xr:uid="{00000000-0005-0000-0000-000079020000}"/>
-    <cellStyle name="40% - Énfasis1 13 3" xfId="906" xr:uid="{00000000-0005-0000-0000-00007A020000}"/>
-    <cellStyle name="40% - Énfasis1 14" xfId="216" xr:uid="{00000000-0005-0000-0000-00007B020000}"/>
-    <cellStyle name="40% - Énfasis1 14 2" xfId="511" xr:uid="{00000000-0005-0000-0000-00007C020000}"/>
-    <cellStyle name="40% - Énfasis1 14 2 2" xfId="909" xr:uid="{00000000-0005-0000-0000-00007D020000}"/>
-    <cellStyle name="40% - Énfasis1 14 3" xfId="908" xr:uid="{00000000-0005-0000-0000-00007E020000}"/>
-    <cellStyle name="40% - Énfasis1 15" xfId="230" xr:uid="{00000000-0005-0000-0000-00007F020000}"/>
-    <cellStyle name="40% - Énfasis1 15 2" xfId="525" xr:uid="{00000000-0005-0000-0000-000080020000}"/>
-    <cellStyle name="40% - Énfasis1 15 2 2" xfId="911" xr:uid="{00000000-0005-0000-0000-000081020000}"/>
-    <cellStyle name="40% - Énfasis1 15 3" xfId="910" xr:uid="{00000000-0005-0000-0000-000082020000}"/>
-    <cellStyle name="40% - Énfasis1 16" xfId="244" xr:uid="{00000000-0005-0000-0000-000083020000}"/>
-    <cellStyle name="40% - Énfasis1 16 2" xfId="539" xr:uid="{00000000-0005-0000-0000-000084020000}"/>
-    <cellStyle name="40% - Énfasis1 16 2 2" xfId="913" xr:uid="{00000000-0005-0000-0000-000085020000}"/>
-    <cellStyle name="40% - Énfasis1 16 3" xfId="912" xr:uid="{00000000-0005-0000-0000-000086020000}"/>
-    <cellStyle name="40% - Énfasis1 17" xfId="258" xr:uid="{00000000-0005-0000-0000-000087020000}"/>
-    <cellStyle name="40% - Énfasis1 17 2" xfId="553" xr:uid="{00000000-0005-0000-0000-000088020000}"/>
-    <cellStyle name="40% - Énfasis1 17 2 2" xfId="915" xr:uid="{00000000-0005-0000-0000-000089020000}"/>
-    <cellStyle name="40% - Énfasis1 17 3" xfId="914" xr:uid="{00000000-0005-0000-0000-00008A020000}"/>
-    <cellStyle name="40% - Énfasis1 18" xfId="272" xr:uid="{00000000-0005-0000-0000-00008B020000}"/>
-    <cellStyle name="40% - Énfasis1 18 2" xfId="567" xr:uid="{00000000-0005-0000-0000-00008C020000}"/>
-    <cellStyle name="40% - Énfasis1 18 2 2" xfId="917" xr:uid="{00000000-0005-0000-0000-00008D020000}"/>
-    <cellStyle name="40% - Énfasis1 18 3" xfId="916" xr:uid="{00000000-0005-0000-0000-00008E020000}"/>
-    <cellStyle name="40% - Énfasis1 19" xfId="286" xr:uid="{00000000-0005-0000-0000-00008F020000}"/>
-    <cellStyle name="40% - Énfasis1 19 2" xfId="581" xr:uid="{00000000-0005-0000-0000-000090020000}"/>
-    <cellStyle name="40% - Énfasis1 19 2 2" xfId="919" xr:uid="{00000000-0005-0000-0000-000091020000}"/>
-    <cellStyle name="40% - Énfasis1 19 3" xfId="918" xr:uid="{00000000-0005-0000-0000-000092020000}"/>
-    <cellStyle name="40% - Énfasis1 2" xfId="48" xr:uid="{00000000-0005-0000-0000-000093020000}"/>
-    <cellStyle name="40% - Énfasis1 2 2" xfId="343" xr:uid="{00000000-0005-0000-0000-000094020000}"/>
-    <cellStyle name="40% - Énfasis1 2 2 2" xfId="921" xr:uid="{00000000-0005-0000-0000-000095020000}"/>
-    <cellStyle name="40% - Énfasis1 2 3" xfId="920" xr:uid="{00000000-0005-0000-0000-000096020000}"/>
-    <cellStyle name="40% - Énfasis1 20" xfId="300" xr:uid="{00000000-0005-0000-0000-000097020000}"/>
-    <cellStyle name="40% - Énfasis1 20 2" xfId="595" xr:uid="{00000000-0005-0000-0000-000098020000}"/>
-    <cellStyle name="40% - Énfasis1 20 2 2" xfId="923" xr:uid="{00000000-0005-0000-0000-000099020000}"/>
-    <cellStyle name="40% - Énfasis1 20 3" xfId="922" xr:uid="{00000000-0005-0000-0000-00009A020000}"/>
-    <cellStyle name="40% - Énfasis1 21" xfId="314" xr:uid="{00000000-0005-0000-0000-00009B020000}"/>
-    <cellStyle name="40% - Énfasis1 21 2" xfId="609" xr:uid="{00000000-0005-0000-0000-00009C020000}"/>
-    <cellStyle name="40% - Énfasis1 21 2 2" xfId="925" xr:uid="{00000000-0005-0000-0000-00009D020000}"/>
-    <cellStyle name="40% - Énfasis1 21 3" xfId="924" xr:uid="{00000000-0005-0000-0000-00009E020000}"/>
-    <cellStyle name="40% - Énfasis1 22" xfId="623" xr:uid="{00000000-0005-0000-0000-00009F020000}"/>
-    <cellStyle name="40% - Énfasis1 22 2" xfId="927" xr:uid="{00000000-0005-0000-0000-0000A0020000}"/>
-    <cellStyle name="40% - Énfasis1 22 3" xfId="926" xr:uid="{00000000-0005-0000-0000-0000A1020000}"/>
-    <cellStyle name="40% - Énfasis1 23" xfId="327" xr:uid="{00000000-0005-0000-0000-0000A2020000}"/>
-    <cellStyle name="40% - Énfasis1 23 2" xfId="928" xr:uid="{00000000-0005-0000-0000-0000A3020000}"/>
-    <cellStyle name="40% - Énfasis1 24" xfId="899" xr:uid="{00000000-0005-0000-0000-0000A4020000}"/>
-    <cellStyle name="40% - Énfasis1 25" xfId="1267" xr:uid="{00000000-0005-0000-0000-0000A5020000}"/>
-    <cellStyle name="40% - Énfasis1 26" xfId="1281" xr:uid="{00000000-0005-0000-0000-0000A6020000}"/>
-    <cellStyle name="40% - Énfasis1 27" xfId="1295" xr:uid="{00000000-0005-0000-0000-0000A7020000}"/>
-    <cellStyle name="40% - Énfasis1 28" xfId="1309" xr:uid="{00000000-0005-0000-0000-0000A8020000}"/>
-    <cellStyle name="40% - Énfasis1 29" xfId="1323" xr:uid="{00000000-0005-0000-0000-0000A9020000}"/>
-    <cellStyle name="40% - Énfasis1 3" xfId="62" xr:uid="{00000000-0005-0000-0000-0000AA020000}"/>
-    <cellStyle name="40% - Énfasis1 3 2" xfId="357" xr:uid="{00000000-0005-0000-0000-0000AB020000}"/>
-    <cellStyle name="40% - Énfasis1 3 2 2" xfId="930" xr:uid="{00000000-0005-0000-0000-0000AC020000}"/>
-    <cellStyle name="40% - Énfasis1 3 3" xfId="929" xr:uid="{00000000-0005-0000-0000-0000AD020000}"/>
-    <cellStyle name="40% - Énfasis1 30" xfId="1337" xr:uid="{00000000-0005-0000-0000-0000AE020000}"/>
-    <cellStyle name="40% - Énfasis1 31" xfId="1351" xr:uid="{00000000-0005-0000-0000-0000AF020000}"/>
-    <cellStyle name="40% - Énfasis1 32" xfId="1365" xr:uid="{00000000-0005-0000-0000-0000B0020000}"/>
-    <cellStyle name="40% - Énfasis1 33" xfId="1379" xr:uid="{00000000-0005-0000-0000-0000B1020000}"/>
-    <cellStyle name="40% - Énfasis1 34" xfId="1393" xr:uid="{00000000-0005-0000-0000-0000B2020000}"/>
-    <cellStyle name="40% - Énfasis1 35" xfId="1407" xr:uid="{00000000-0005-0000-0000-0000B3020000}"/>
-    <cellStyle name="40% - Énfasis1 36" xfId="1421" xr:uid="{00000000-0005-0000-0000-0000B4020000}"/>
-    <cellStyle name="40% - Énfasis1 37" xfId="1435" xr:uid="{00000000-0005-0000-0000-0000B5020000}"/>
-    <cellStyle name="40% - Énfasis1 38" xfId="1449" xr:uid="{00000000-0005-0000-0000-0000B6020000}"/>
-    <cellStyle name="40% - Énfasis1 39" xfId="1463" xr:uid="{00000000-0005-0000-0000-0000B7020000}"/>
-    <cellStyle name="40% - Énfasis1 4" xfId="76" xr:uid="{00000000-0005-0000-0000-0000B8020000}"/>
-    <cellStyle name="40% - Énfasis1 4 2" xfId="371" xr:uid="{00000000-0005-0000-0000-0000B9020000}"/>
-    <cellStyle name="40% - Énfasis1 4 2 2" xfId="932" xr:uid="{00000000-0005-0000-0000-0000BA020000}"/>
-    <cellStyle name="40% - Énfasis1 4 3" xfId="931" xr:uid="{00000000-0005-0000-0000-0000BB020000}"/>
-    <cellStyle name="40% - Énfasis1 40" xfId="1478" xr:uid="{00000000-0005-0000-0000-0000BC020000}"/>
-    <cellStyle name="40% - Énfasis1 5" xfId="90" xr:uid="{00000000-0005-0000-0000-0000BD020000}"/>
-    <cellStyle name="40% - Énfasis1 5 2" xfId="385" xr:uid="{00000000-0005-0000-0000-0000BE020000}"/>
-    <cellStyle name="40% - Énfasis1 5 2 2" xfId="934" xr:uid="{00000000-0005-0000-0000-0000BF020000}"/>
-    <cellStyle name="40% - Énfasis1 5 3" xfId="933" xr:uid="{00000000-0005-0000-0000-0000C0020000}"/>
-    <cellStyle name="40% - Énfasis1 6" xfId="104" xr:uid="{00000000-0005-0000-0000-0000C1020000}"/>
-    <cellStyle name="40% - Énfasis1 6 2" xfId="399" xr:uid="{00000000-0005-0000-0000-0000C2020000}"/>
-    <cellStyle name="40% - Énfasis1 6 2 2" xfId="936" xr:uid="{00000000-0005-0000-0000-0000C3020000}"/>
-    <cellStyle name="40% - Énfasis1 6 3" xfId="935" xr:uid="{00000000-0005-0000-0000-0000C4020000}"/>
-    <cellStyle name="40% - Énfasis1 7" xfId="118" xr:uid="{00000000-0005-0000-0000-0000C5020000}"/>
-    <cellStyle name="40% - Énfasis1 7 2" xfId="413" xr:uid="{00000000-0005-0000-0000-0000C6020000}"/>
-    <cellStyle name="40% - Énfasis1 7 2 2" xfId="938" xr:uid="{00000000-0005-0000-0000-0000C7020000}"/>
-    <cellStyle name="40% - Énfasis1 7 3" xfId="937" xr:uid="{00000000-0005-0000-0000-0000C8020000}"/>
-    <cellStyle name="40% - Énfasis1 8" xfId="132" xr:uid="{00000000-0005-0000-0000-0000C9020000}"/>
-    <cellStyle name="40% - Énfasis1 8 2" xfId="427" xr:uid="{00000000-0005-0000-0000-0000CA020000}"/>
-    <cellStyle name="40% - Énfasis1 8 2 2" xfId="940" xr:uid="{00000000-0005-0000-0000-0000CB020000}"/>
-    <cellStyle name="40% - Énfasis1 8 3" xfId="939" xr:uid="{00000000-0005-0000-0000-0000CC020000}"/>
-    <cellStyle name="40% - Énfasis1 9" xfId="146" xr:uid="{00000000-0005-0000-0000-0000CD020000}"/>
-    <cellStyle name="40% - Énfasis1 9 2" xfId="441" xr:uid="{00000000-0005-0000-0000-0000CE020000}"/>
-    <cellStyle name="40% - Énfasis1 9 2 2" xfId="942" xr:uid="{00000000-0005-0000-0000-0000CF020000}"/>
-    <cellStyle name="40% - Énfasis1 9 3" xfId="941" xr:uid="{00000000-0005-0000-0000-0000D0020000}"/>
+    <cellStyle name="40% - Énfasis1 10" xfId="160"/>
+    <cellStyle name="40% - Énfasis1 10 2" xfId="455"/>
+    <cellStyle name="40% - Énfasis1 10 2 2" xfId="901"/>
+    <cellStyle name="40% - Énfasis1 10 3" xfId="900"/>
+    <cellStyle name="40% - Énfasis1 11" xfId="174"/>
+    <cellStyle name="40% - Énfasis1 11 2" xfId="469"/>
+    <cellStyle name="40% - Énfasis1 11 2 2" xfId="903"/>
+    <cellStyle name="40% - Énfasis1 11 3" xfId="902"/>
+    <cellStyle name="40% - Énfasis1 12" xfId="188"/>
+    <cellStyle name="40% - Énfasis1 12 2" xfId="483"/>
+    <cellStyle name="40% - Énfasis1 12 2 2" xfId="905"/>
+    <cellStyle name="40% - Énfasis1 12 3" xfId="904"/>
+    <cellStyle name="40% - Énfasis1 13" xfId="202"/>
+    <cellStyle name="40% - Énfasis1 13 2" xfId="497"/>
+    <cellStyle name="40% - Énfasis1 13 2 2" xfId="907"/>
+    <cellStyle name="40% - Énfasis1 13 3" xfId="906"/>
+    <cellStyle name="40% - Énfasis1 14" xfId="216"/>
+    <cellStyle name="40% - Énfasis1 14 2" xfId="511"/>
+    <cellStyle name="40% - Énfasis1 14 2 2" xfId="909"/>
+    <cellStyle name="40% - Énfasis1 14 3" xfId="908"/>
+    <cellStyle name="40% - Énfasis1 15" xfId="230"/>
+    <cellStyle name="40% - Énfasis1 15 2" xfId="525"/>
+    <cellStyle name="40% - Énfasis1 15 2 2" xfId="911"/>
+    <cellStyle name="40% - Énfasis1 15 3" xfId="910"/>
+    <cellStyle name="40% - Énfasis1 16" xfId="244"/>
+    <cellStyle name="40% - Énfasis1 16 2" xfId="539"/>
+    <cellStyle name="40% - Énfasis1 16 2 2" xfId="913"/>
+    <cellStyle name="40% - Énfasis1 16 3" xfId="912"/>
+    <cellStyle name="40% - Énfasis1 17" xfId="258"/>
+    <cellStyle name="40% - Énfasis1 17 2" xfId="553"/>
+    <cellStyle name="40% - Énfasis1 17 2 2" xfId="915"/>
+    <cellStyle name="40% - Énfasis1 17 3" xfId="914"/>
+    <cellStyle name="40% - Énfasis1 18" xfId="272"/>
+    <cellStyle name="40% - Énfasis1 18 2" xfId="567"/>
+    <cellStyle name="40% - Énfasis1 18 2 2" xfId="917"/>
+    <cellStyle name="40% - Énfasis1 18 3" xfId="916"/>
+    <cellStyle name="40% - Énfasis1 19" xfId="286"/>
+    <cellStyle name="40% - Énfasis1 19 2" xfId="581"/>
+    <cellStyle name="40% - Énfasis1 19 2 2" xfId="919"/>
+    <cellStyle name="40% - Énfasis1 19 3" xfId="918"/>
+    <cellStyle name="40% - Énfasis1 2" xfId="48"/>
+    <cellStyle name="40% - Énfasis1 2 2" xfId="343"/>
+    <cellStyle name="40% - Énfasis1 2 2 2" xfId="921"/>
+    <cellStyle name="40% - Énfasis1 2 3" xfId="920"/>
+    <cellStyle name="40% - Énfasis1 20" xfId="300"/>
+    <cellStyle name="40% - Énfasis1 20 2" xfId="595"/>
+    <cellStyle name="40% - Énfasis1 20 2 2" xfId="923"/>
+    <cellStyle name="40% - Énfasis1 20 3" xfId="922"/>
+    <cellStyle name="40% - Énfasis1 21" xfId="314"/>
+    <cellStyle name="40% - Énfasis1 21 2" xfId="609"/>
+    <cellStyle name="40% - Énfasis1 21 2 2" xfId="925"/>
+    <cellStyle name="40% - Énfasis1 21 3" xfId="924"/>
+    <cellStyle name="40% - Énfasis1 22" xfId="623"/>
+    <cellStyle name="40% - Énfasis1 22 2" xfId="927"/>
+    <cellStyle name="40% - Énfasis1 22 3" xfId="926"/>
+    <cellStyle name="40% - Énfasis1 23" xfId="327"/>
+    <cellStyle name="40% - Énfasis1 23 2" xfId="928"/>
+    <cellStyle name="40% - Énfasis1 24" xfId="899"/>
+    <cellStyle name="40% - Énfasis1 25" xfId="1267"/>
+    <cellStyle name="40% - Énfasis1 26" xfId="1281"/>
+    <cellStyle name="40% - Énfasis1 27" xfId="1295"/>
+    <cellStyle name="40% - Énfasis1 28" xfId="1309"/>
+    <cellStyle name="40% - Énfasis1 29" xfId="1323"/>
+    <cellStyle name="40% - Énfasis1 3" xfId="62"/>
+    <cellStyle name="40% - Énfasis1 3 2" xfId="357"/>
+    <cellStyle name="40% - Énfasis1 3 2 2" xfId="930"/>
+    <cellStyle name="40% - Énfasis1 3 3" xfId="929"/>
+    <cellStyle name="40% - Énfasis1 30" xfId="1337"/>
+    <cellStyle name="40% - Énfasis1 31" xfId="1351"/>
+    <cellStyle name="40% - Énfasis1 32" xfId="1365"/>
+    <cellStyle name="40% - Énfasis1 33" xfId="1379"/>
+    <cellStyle name="40% - Énfasis1 34" xfId="1393"/>
+    <cellStyle name="40% - Énfasis1 35" xfId="1407"/>
+    <cellStyle name="40% - Énfasis1 36" xfId="1421"/>
+    <cellStyle name="40% - Énfasis1 37" xfId="1435"/>
+    <cellStyle name="40% - Énfasis1 38" xfId="1449"/>
+    <cellStyle name="40% - Énfasis1 39" xfId="1463"/>
+    <cellStyle name="40% - Énfasis1 4" xfId="76"/>
+    <cellStyle name="40% - Énfasis1 4 2" xfId="371"/>
+    <cellStyle name="40% - Énfasis1 4 2 2" xfId="932"/>
+    <cellStyle name="40% - Énfasis1 4 3" xfId="931"/>
+    <cellStyle name="40% - Énfasis1 40" xfId="1478"/>
+    <cellStyle name="40% - Énfasis1 5" xfId="90"/>
+    <cellStyle name="40% - Énfasis1 5 2" xfId="385"/>
+    <cellStyle name="40% - Énfasis1 5 2 2" xfId="934"/>
+    <cellStyle name="40% - Énfasis1 5 3" xfId="933"/>
+    <cellStyle name="40% - Énfasis1 6" xfId="104"/>
+    <cellStyle name="40% - Énfasis1 6 2" xfId="399"/>
+    <cellStyle name="40% - Énfasis1 6 2 2" xfId="936"/>
+    <cellStyle name="40% - Énfasis1 6 3" xfId="935"/>
+    <cellStyle name="40% - Énfasis1 7" xfId="118"/>
+    <cellStyle name="40% - Énfasis1 7 2" xfId="413"/>
+    <cellStyle name="40% - Énfasis1 7 2 2" xfId="938"/>
+    <cellStyle name="40% - Énfasis1 7 3" xfId="937"/>
+    <cellStyle name="40% - Énfasis1 8" xfId="132"/>
+    <cellStyle name="40% - Énfasis1 8 2" xfId="427"/>
+    <cellStyle name="40% - Énfasis1 8 2 2" xfId="940"/>
+    <cellStyle name="40% - Énfasis1 8 3" xfId="939"/>
+    <cellStyle name="40% - Énfasis1 9" xfId="146"/>
+    <cellStyle name="40% - Énfasis1 9 2" xfId="441"/>
+    <cellStyle name="40% - Énfasis1 9 2 2" xfId="942"/>
+    <cellStyle name="40% - Énfasis1 9 3" xfId="941"/>
     <cellStyle name="40% - Énfasis2" xfId="25" builtinId="35" customBuiltin="1"/>
-    <cellStyle name="40% - Énfasis2 10" xfId="162" xr:uid="{00000000-0005-0000-0000-0000D2020000}"/>
-    <cellStyle name="40% - Énfasis2 10 2" xfId="457" xr:uid="{00000000-0005-0000-0000-0000D3020000}"/>
-    <cellStyle name="40% - Énfasis2 10 2 2" xfId="945" xr:uid="{00000000-0005-0000-0000-0000D4020000}"/>
-    <cellStyle name="40% - Énfasis2 10 3" xfId="944" xr:uid="{00000000-0005-0000-0000-0000D5020000}"/>
-    <cellStyle name="40% - Énfasis2 11" xfId="176" xr:uid="{00000000-0005-0000-0000-0000D6020000}"/>
-    <cellStyle name="40% - Énfasis2 11 2" xfId="471" xr:uid="{00000000-0005-0000-0000-0000D7020000}"/>
-    <cellStyle name="40% - Énfasis2 11 2 2" xfId="947" xr:uid="{00000000-0005-0000-0000-0000D8020000}"/>
-    <cellStyle name="40% - Énfasis2 11 3" xfId="946" xr:uid="{00000000-0005-0000-0000-0000D9020000}"/>
-    <cellStyle name="40% - Énfasis2 12" xfId="190" xr:uid="{00000000-0005-0000-0000-0000DA020000}"/>
-    <cellStyle name="40% - Énfasis2 12 2" xfId="485" xr:uid="{00000000-0005-0000-0000-0000DB020000}"/>
-    <cellStyle name="40% - Énfasis2 12 2 2" xfId="949" xr:uid="{00000000-0005-0000-0000-0000DC020000}"/>
-    <cellStyle name="40% - Énfasis2 12 3" xfId="948" xr:uid="{00000000-0005-0000-0000-0000DD020000}"/>
-    <cellStyle name="40% - Énfasis2 13" xfId="204" xr:uid="{00000000-0005-0000-0000-0000DE020000}"/>
-    <cellStyle name="40% - Énfasis2 13 2" xfId="499" xr:uid="{00000000-0005-0000-0000-0000DF020000}"/>
-    <cellStyle name="40% - Énfasis2 13 2 2" xfId="951" xr:uid="{00000000-0005-0000-0000-0000E0020000}"/>
-    <cellStyle name="40% - Énfasis2 13 3" xfId="950" xr:uid="{00000000-0005-0000-0000-0000E1020000}"/>
-    <cellStyle name="40% - Énfasis2 14" xfId="218" xr:uid="{00000000-0005-0000-0000-0000E2020000}"/>
-    <cellStyle name="40% - Énfasis2 14 2" xfId="513" xr:uid="{00000000-0005-0000-0000-0000E3020000}"/>
-    <cellStyle name="40% - Énfasis2 14 2 2" xfId="953" xr:uid="{00000000-0005-0000-0000-0000E4020000}"/>
-    <cellStyle name="40% - Énfasis2 14 3" xfId="952" xr:uid="{00000000-0005-0000-0000-0000E5020000}"/>
-    <cellStyle name="40% - Énfasis2 15" xfId="232" xr:uid="{00000000-0005-0000-0000-0000E6020000}"/>
-    <cellStyle name="40% - Énfasis2 15 2" xfId="527" xr:uid="{00000000-0005-0000-0000-0000E7020000}"/>
-    <cellStyle name="40% - Énfasis2 15 2 2" xfId="955" xr:uid="{00000000-0005-0000-0000-0000E8020000}"/>
-    <cellStyle name="40% - Énfasis2 15 3" xfId="954" xr:uid="{00000000-0005-0000-0000-0000E9020000}"/>
-    <cellStyle name="40% - Énfasis2 16" xfId="246" xr:uid="{00000000-0005-0000-0000-0000EA020000}"/>
-    <cellStyle name="40% - Énfasis2 16 2" xfId="541" xr:uid="{00000000-0005-0000-0000-0000EB020000}"/>
-    <cellStyle name="40% - Énfasis2 16 2 2" xfId="957" xr:uid="{00000000-0005-0000-0000-0000EC020000}"/>
-    <cellStyle name="40% - Énfasis2 16 3" xfId="956" xr:uid="{00000000-0005-0000-0000-0000ED020000}"/>
-    <cellStyle name="40% - Énfasis2 17" xfId="260" xr:uid="{00000000-0005-0000-0000-0000EE020000}"/>
-    <cellStyle name="40% - Énfasis2 17 2" xfId="555" xr:uid="{00000000-0005-0000-0000-0000EF020000}"/>
-    <cellStyle name="40% - Énfasis2 17 2 2" xfId="959" xr:uid="{00000000-0005-0000-0000-0000F0020000}"/>
-    <cellStyle name="40% - Énfasis2 17 3" xfId="958" xr:uid="{00000000-0005-0000-0000-0000F1020000}"/>
-    <cellStyle name="40% - Énfasis2 18" xfId="274" xr:uid="{00000000-0005-0000-0000-0000F2020000}"/>
-    <cellStyle name="40% - Énfasis2 18 2" xfId="569" xr:uid="{00000000-0005-0000-0000-0000F3020000}"/>
-    <cellStyle name="40% - Énfasis2 18 2 2" xfId="961" xr:uid="{00000000-0005-0000-0000-0000F4020000}"/>
-    <cellStyle name="40% - Énfasis2 18 3" xfId="960" xr:uid="{00000000-0005-0000-0000-0000F5020000}"/>
-    <cellStyle name="40% - Énfasis2 19" xfId="288" xr:uid="{00000000-0005-0000-0000-0000F6020000}"/>
-    <cellStyle name="40% - Énfasis2 19 2" xfId="583" xr:uid="{00000000-0005-0000-0000-0000F7020000}"/>
-    <cellStyle name="40% - Énfasis2 19 2 2" xfId="963" xr:uid="{00000000-0005-0000-0000-0000F8020000}"/>
-    <cellStyle name="40% - Énfasis2 19 3" xfId="962" xr:uid="{00000000-0005-0000-0000-0000F9020000}"/>
-    <cellStyle name="40% - Énfasis2 2" xfId="50" xr:uid="{00000000-0005-0000-0000-0000FA020000}"/>
-    <cellStyle name="40% - Énfasis2 2 2" xfId="345" xr:uid="{00000000-0005-0000-0000-0000FB020000}"/>
-    <cellStyle name="40% - Énfasis2 2 2 2" xfId="965" xr:uid="{00000000-0005-0000-0000-0000FC020000}"/>
-    <cellStyle name="40% - Énfasis2 2 3" xfId="964" xr:uid="{00000000-0005-0000-0000-0000FD020000}"/>
-    <cellStyle name="40% - Énfasis2 20" xfId="302" xr:uid="{00000000-0005-0000-0000-0000FE020000}"/>
-    <cellStyle name="40% - Énfasis2 20 2" xfId="597" xr:uid="{00000000-0005-0000-0000-0000FF020000}"/>
-    <cellStyle name="40% - Énfasis2 20 2 2" xfId="967" xr:uid="{00000000-0005-0000-0000-000000030000}"/>
-    <cellStyle name="40% - Énfasis2 20 3" xfId="966" xr:uid="{00000000-0005-0000-0000-000001030000}"/>
-    <cellStyle name="40% - Énfasis2 21" xfId="316" xr:uid="{00000000-0005-0000-0000-000002030000}"/>
-    <cellStyle name="40% - Énfasis2 21 2" xfId="611" xr:uid="{00000000-0005-0000-0000-000003030000}"/>
-    <cellStyle name="40% - Énfasis2 21 2 2" xfId="969" xr:uid="{00000000-0005-0000-0000-000004030000}"/>
-    <cellStyle name="40% - Énfasis2 21 3" xfId="968" xr:uid="{00000000-0005-0000-0000-000005030000}"/>
-    <cellStyle name="40% - Énfasis2 22" xfId="625" xr:uid="{00000000-0005-0000-0000-000006030000}"/>
-    <cellStyle name="40% - Énfasis2 22 2" xfId="971" xr:uid="{00000000-0005-0000-0000-000007030000}"/>
-    <cellStyle name="40% - Énfasis2 22 3" xfId="970" xr:uid="{00000000-0005-0000-0000-000008030000}"/>
-    <cellStyle name="40% - Énfasis2 23" xfId="329" xr:uid="{00000000-0005-0000-0000-000009030000}"/>
-    <cellStyle name="40% - Énfasis2 23 2" xfId="972" xr:uid="{00000000-0005-0000-0000-00000A030000}"/>
-    <cellStyle name="40% - Énfasis2 24" xfId="943" xr:uid="{00000000-0005-0000-0000-00000B030000}"/>
-    <cellStyle name="40% - Énfasis2 25" xfId="1269" xr:uid="{00000000-0005-0000-0000-00000C030000}"/>
-    <cellStyle name="40% - Énfasis2 26" xfId="1283" xr:uid="{00000000-0005-0000-0000-00000D030000}"/>
-    <cellStyle name="40% - Énfasis2 27" xfId="1297" xr:uid="{00000000-0005-0000-0000-00000E030000}"/>
-    <cellStyle name="40% - Énfasis2 28" xfId="1311" xr:uid="{00000000-0005-0000-0000-00000F030000}"/>
-    <cellStyle name="40% - Énfasis2 29" xfId="1325" xr:uid="{00000000-0005-0000-0000-000010030000}"/>
-    <cellStyle name="40% - Énfasis2 3" xfId="64" xr:uid="{00000000-0005-0000-0000-000011030000}"/>
-    <cellStyle name="40% - Énfasis2 3 2" xfId="359" xr:uid="{00000000-0005-0000-0000-000012030000}"/>
-    <cellStyle name="40% - Énfasis2 3 2 2" xfId="974" xr:uid="{00000000-0005-0000-0000-000013030000}"/>
-    <cellStyle name="40% - Énfasis2 3 3" xfId="973" xr:uid="{00000000-0005-0000-0000-000014030000}"/>
-    <cellStyle name="40% - Énfasis2 30" xfId="1339" xr:uid="{00000000-0005-0000-0000-000015030000}"/>
-    <cellStyle name="40% - Énfasis2 31" xfId="1353" xr:uid="{00000000-0005-0000-0000-000016030000}"/>
-    <cellStyle name="40% - Énfasis2 32" xfId="1367" xr:uid="{00000000-0005-0000-0000-000017030000}"/>
-    <cellStyle name="40% - Énfasis2 33" xfId="1381" xr:uid="{00000000-0005-0000-0000-000018030000}"/>
-    <cellStyle name="40% - Énfasis2 34" xfId="1395" xr:uid="{00000000-0005-0000-0000-000019030000}"/>
-    <cellStyle name="40% - Énfasis2 35" xfId="1409" xr:uid="{00000000-0005-0000-0000-00001A030000}"/>
-    <cellStyle name="40% - Énfasis2 36" xfId="1423" xr:uid="{00000000-0005-0000-0000-00001B030000}"/>
-    <cellStyle name="40% - Énfasis2 37" xfId="1437" xr:uid="{00000000-0005-0000-0000-00001C030000}"/>
-    <cellStyle name="40% - Énfasis2 38" xfId="1451" xr:uid="{00000000-0005-0000-0000-00001D030000}"/>
-    <cellStyle name="40% - Énfasis2 39" xfId="1465" xr:uid="{00000000-0005-0000-0000-00001E030000}"/>
-    <cellStyle name="40% - Énfasis2 4" xfId="78" xr:uid="{00000000-0005-0000-0000-00001F030000}"/>
-    <cellStyle name="40% - Énfasis2 4 2" xfId="373" xr:uid="{00000000-0005-0000-0000-000020030000}"/>
-    <cellStyle name="40% - Énfasis2 4 2 2" xfId="976" xr:uid="{00000000-0005-0000-0000-000021030000}"/>
-    <cellStyle name="40% - Énfasis2 4 3" xfId="975" xr:uid="{00000000-0005-0000-0000-000022030000}"/>
-    <cellStyle name="40% - Énfasis2 40" xfId="1480" xr:uid="{00000000-0005-0000-0000-000023030000}"/>
-    <cellStyle name="40% - Énfasis2 5" xfId="92" xr:uid="{00000000-0005-0000-0000-000024030000}"/>
-    <cellStyle name="40% - Énfasis2 5 2" xfId="387" xr:uid="{00000000-0005-0000-0000-000025030000}"/>
-    <cellStyle name="40% - Énfasis2 5 2 2" xfId="978" xr:uid="{00000000-0005-0000-0000-000026030000}"/>
-    <cellStyle name="40% - Énfasis2 5 3" xfId="977" xr:uid="{00000000-0005-0000-0000-000027030000}"/>
-    <cellStyle name="40% - Énfasis2 6" xfId="106" xr:uid="{00000000-0005-0000-0000-000028030000}"/>
-    <cellStyle name="40% - Énfasis2 6 2" xfId="401" xr:uid="{00000000-0005-0000-0000-000029030000}"/>
-    <cellStyle name="40% - Énfasis2 6 2 2" xfId="980" xr:uid="{00000000-0005-0000-0000-00002A030000}"/>
-    <cellStyle name="40% - Énfasis2 6 3" xfId="979" xr:uid="{00000000-0005-0000-0000-00002B030000}"/>
-    <cellStyle name="40% - Énfasis2 7" xfId="120" xr:uid="{00000000-0005-0000-0000-00002C030000}"/>
-    <cellStyle name="40% - Énfasis2 7 2" xfId="415" xr:uid="{00000000-0005-0000-0000-00002D030000}"/>
-    <cellStyle name="40% - Énfasis2 7 2 2" xfId="982" xr:uid="{00000000-0005-0000-0000-00002E030000}"/>
-    <cellStyle name="40% - Énfasis2 7 3" xfId="981" xr:uid="{00000000-0005-0000-0000-00002F030000}"/>
-    <cellStyle name="40% - Énfasis2 8" xfId="134" xr:uid="{00000000-0005-0000-0000-000030030000}"/>
-    <cellStyle name="40% - Énfasis2 8 2" xfId="429" xr:uid="{00000000-0005-0000-0000-000031030000}"/>
-    <cellStyle name="40% - Énfasis2 8 2 2" xfId="984" xr:uid="{00000000-0005-0000-0000-000032030000}"/>
-    <cellStyle name="40% - Énfasis2 8 3" xfId="983" xr:uid="{00000000-0005-0000-0000-000033030000}"/>
-    <cellStyle name="40% - Énfasis2 9" xfId="148" xr:uid="{00000000-0005-0000-0000-000034030000}"/>
-    <cellStyle name="40% - Énfasis2 9 2" xfId="443" xr:uid="{00000000-0005-0000-0000-000035030000}"/>
-    <cellStyle name="40% - Énfasis2 9 2 2" xfId="986" xr:uid="{00000000-0005-0000-0000-000036030000}"/>
-    <cellStyle name="40% - Énfasis2 9 3" xfId="985" xr:uid="{00000000-0005-0000-0000-000037030000}"/>
+    <cellStyle name="40% - Énfasis2 10" xfId="162"/>
+    <cellStyle name="40% - Énfasis2 10 2" xfId="457"/>
+    <cellStyle name="40% - Énfasis2 10 2 2" xfId="945"/>
+    <cellStyle name="40% - Énfasis2 10 3" xfId="944"/>
+    <cellStyle name="40% - Énfasis2 11" xfId="176"/>
+    <cellStyle name="40% - Énfasis2 11 2" xfId="471"/>
+    <cellStyle name="40% - Énfasis2 11 2 2" xfId="947"/>
+    <cellStyle name="40% - Énfasis2 11 3" xfId="946"/>
+    <cellStyle name="40% - Énfasis2 12" xfId="190"/>
+    <cellStyle name="40% - Énfasis2 12 2" xfId="485"/>
+    <cellStyle name="40% - Énfasis2 12 2 2" xfId="949"/>
+    <cellStyle name="40% - Énfasis2 12 3" xfId="948"/>
+    <cellStyle name="40% - Énfasis2 13" xfId="204"/>
+    <cellStyle name="40% - Énfasis2 13 2" xfId="499"/>
+    <cellStyle name="40% - Énfasis2 13 2 2" xfId="951"/>
+    <cellStyle name="40% - Énfasis2 13 3" xfId="950"/>
+    <cellStyle name="40% - Énfasis2 14" xfId="218"/>
+    <cellStyle name="40% - Énfasis2 14 2" xfId="513"/>
+    <cellStyle name="40% - Énfasis2 14 2 2" xfId="953"/>
+    <cellStyle name="40% - Énfasis2 14 3" xfId="952"/>
+    <cellStyle name="40% - Énfasis2 15" xfId="232"/>
+    <cellStyle name="40% - Énfasis2 15 2" xfId="527"/>
+    <cellStyle name="40% - Énfasis2 15 2 2" xfId="955"/>
+    <cellStyle name="40% - Énfasis2 15 3" xfId="954"/>
+    <cellStyle name="40% - Énfasis2 16" xfId="246"/>
+    <cellStyle name="40% - Énfasis2 16 2" xfId="541"/>
+    <cellStyle name="40% - Énfasis2 16 2 2" xfId="957"/>
+    <cellStyle name="40% - Énfasis2 16 3" xfId="956"/>
+    <cellStyle name="40% - Énfasis2 17" xfId="260"/>
+    <cellStyle name="40% - Énfasis2 17 2" xfId="555"/>
+    <cellStyle name="40% - Énfasis2 17 2 2" xfId="959"/>
+    <cellStyle name="40% - Énfasis2 17 3" xfId="958"/>
+    <cellStyle name="40% - Énfasis2 18" xfId="274"/>
+    <cellStyle name="40% - Énfasis2 18 2" xfId="569"/>
+    <cellStyle name="40% - Énfasis2 18 2 2" xfId="961"/>
+    <cellStyle name="40% - Énfasis2 18 3" xfId="960"/>
+    <cellStyle name="40% - Énfasis2 19" xfId="288"/>
+    <cellStyle name="40% - Énfasis2 19 2" xfId="583"/>
+    <cellStyle name="40% - Énfasis2 19 2 2" xfId="963"/>
+    <cellStyle name="40% - Énfasis2 19 3" xfId="962"/>
+    <cellStyle name="40% - Énfasis2 2" xfId="50"/>
+    <cellStyle name="40% - Énfasis2 2 2" xfId="345"/>
+    <cellStyle name="40% - Énfasis2 2 2 2" xfId="965"/>
+    <cellStyle name="40% - Énfasis2 2 3" xfId="964"/>
+    <cellStyle name="40% - Énfasis2 20" xfId="302"/>
+    <cellStyle name="40% - Énfasis2 20 2" xfId="597"/>
+    <cellStyle name="40% - Énfasis2 20 2 2" xfId="967"/>
+    <cellStyle name="40% - Énfasis2 20 3" xfId="966"/>
+    <cellStyle name="40% - Énfasis2 21" xfId="316"/>
+    <cellStyle name="40% - Énfasis2 21 2" xfId="611"/>
+    <cellStyle name="40% - Énfasis2 21 2 2" xfId="969"/>
+    <cellStyle name="40% - Énfasis2 21 3" xfId="968"/>
+    <cellStyle name="40% - Énfasis2 22" xfId="625"/>
+    <cellStyle name="40% - Énfasis2 22 2" xfId="971"/>
+    <cellStyle name="40% - Énfasis2 22 3" xfId="970"/>
+    <cellStyle name="40% - Énfasis2 23" xfId="329"/>
+    <cellStyle name="40% - Énfasis2 23 2" xfId="972"/>
+    <cellStyle name="40% - Énfasis2 24" xfId="943"/>
+    <cellStyle name="40% - Énfasis2 25" xfId="1269"/>
+    <cellStyle name="40% - Énfasis2 26" xfId="1283"/>
+    <cellStyle name="40% - Énfasis2 27" xfId="1297"/>
+    <cellStyle name="40% - Énfasis2 28" xfId="1311"/>
+    <cellStyle name="40% - Énfasis2 29" xfId="1325"/>
+    <cellStyle name="40% - Énfasis2 3" xfId="64"/>
+    <cellStyle name="40% - Énfasis2 3 2" xfId="359"/>
+    <cellStyle name="40% - Énfasis2 3 2 2" xfId="974"/>
+    <cellStyle name="40% - Énfasis2 3 3" xfId="973"/>
+    <cellStyle name="40% - Énfasis2 30" xfId="1339"/>
+    <cellStyle name="40% - Énfasis2 31" xfId="1353"/>
+    <cellStyle name="40% - Énfasis2 32" xfId="1367"/>
+    <cellStyle name="40% - Énfasis2 33" xfId="1381"/>
+    <cellStyle name="40% - Énfasis2 34" xfId="1395"/>
+    <cellStyle name="40% - Énfasis2 35" xfId="1409"/>
+    <cellStyle name="40% - Énfasis2 36" xfId="1423"/>
+    <cellStyle name="40% - Énfasis2 37" xfId="1437"/>
+    <cellStyle name="40% - Énfasis2 38" xfId="1451"/>
+    <cellStyle name="40% - Énfasis2 39" xfId="1465"/>
+    <cellStyle name="40% - Énfasis2 4" xfId="78"/>
+    <cellStyle name="40% - Énfasis2 4 2" xfId="373"/>
+    <cellStyle name="40% - Énfasis2 4 2 2" xfId="976"/>
+    <cellStyle name="40% - Énfasis2 4 3" xfId="975"/>
+    <cellStyle name="40% - Énfasis2 40" xfId="1480"/>
+    <cellStyle name="40% - Énfasis2 5" xfId="92"/>
+    <cellStyle name="40% - Énfasis2 5 2" xfId="387"/>
+    <cellStyle name="40% - Énfasis2 5 2 2" xfId="978"/>
+    <cellStyle name="40% - Énfasis2 5 3" xfId="977"/>
+    <cellStyle name="40% - Énfasis2 6" xfId="106"/>
+    <cellStyle name="40% - Énfasis2 6 2" xfId="401"/>
+    <cellStyle name="40% - Énfasis2 6 2 2" xfId="980"/>
+    <cellStyle name="40% - Énfasis2 6 3" xfId="979"/>
+    <cellStyle name="40% - Énfasis2 7" xfId="120"/>
+    <cellStyle name="40% - Énfasis2 7 2" xfId="415"/>
+    <cellStyle name="40% - Énfasis2 7 2 2" xfId="982"/>
+    <cellStyle name="40% - Énfasis2 7 3" xfId="981"/>
+    <cellStyle name="40% - Énfasis2 8" xfId="134"/>
+    <cellStyle name="40% - Énfasis2 8 2" xfId="429"/>
+    <cellStyle name="40% - Énfasis2 8 2 2" xfId="984"/>
+    <cellStyle name="40% - Énfasis2 8 3" xfId="983"/>
+    <cellStyle name="40% - Énfasis2 9" xfId="148"/>
+    <cellStyle name="40% - Énfasis2 9 2" xfId="443"/>
+    <cellStyle name="40% - Énfasis2 9 2 2" xfId="986"/>
+    <cellStyle name="40% - Énfasis2 9 3" xfId="985"/>
     <cellStyle name="40% - Énfasis3" xfId="29" builtinId="39" customBuiltin="1"/>
-    <cellStyle name="40% - Énfasis3 10" xfId="164" xr:uid="{00000000-0005-0000-0000-000039030000}"/>
-    <cellStyle name="40% - Énfasis3 10 2" xfId="459" xr:uid="{00000000-0005-0000-0000-00003A030000}"/>
-    <cellStyle name="40% - Énfasis3 10 2 2" xfId="989" xr:uid="{00000000-0005-0000-0000-00003B030000}"/>
-    <cellStyle name="40% - Énfasis3 10 3" xfId="988" xr:uid="{00000000-0005-0000-0000-00003C030000}"/>
-    <cellStyle name="40% - Énfasis3 11" xfId="178" xr:uid="{00000000-0005-0000-0000-00003D030000}"/>
-    <cellStyle name="40% - Énfasis3 11 2" xfId="473" xr:uid="{00000000-0005-0000-0000-00003E030000}"/>
-    <cellStyle name="40% - Énfasis3 11 2 2" xfId="991" xr:uid="{00000000-0005-0000-0000-00003F030000}"/>
-    <cellStyle name="40% - Énfasis3 11 3" xfId="990" xr:uid="{00000000-0005-0000-0000-000040030000}"/>
-    <cellStyle name="40% - Énfasis3 12" xfId="192" xr:uid="{00000000-0005-0000-0000-000041030000}"/>
-    <cellStyle name="40% - Énfasis3 12 2" xfId="487" xr:uid="{00000000-0005-0000-0000-000042030000}"/>
-    <cellStyle name="40% - Énfasis3 12 2 2" xfId="993" xr:uid="{00000000-0005-0000-0000-000043030000}"/>
-    <cellStyle name="40% - Énfasis3 12 3" xfId="992" xr:uid="{00000000-0005-0000-0000-000044030000}"/>
-    <cellStyle name="40% - Énfasis3 13" xfId="206" xr:uid="{00000000-0005-0000-0000-000045030000}"/>
-    <cellStyle name="40% - Énfasis3 13 2" xfId="501" xr:uid="{00000000-0005-0000-0000-000046030000}"/>
-    <cellStyle name="40% - Énfasis3 13 2 2" xfId="995" xr:uid="{00000000-0005-0000-0000-000047030000}"/>
-    <cellStyle name="40% - Énfasis3 13 3" xfId="994" xr:uid="{00000000-0005-0000-0000-000048030000}"/>
-    <cellStyle name="40% - Énfasis3 14" xfId="220" xr:uid="{00000000-0005-0000-0000-000049030000}"/>
-    <cellStyle name="40% - Énfasis3 14 2" xfId="515" xr:uid="{00000000-0005-0000-0000-00004A030000}"/>
-    <cellStyle name="40% - Énfasis3 14 2 2" xfId="997" xr:uid="{00000000-0005-0000-0000-00004B030000}"/>
-    <cellStyle name="40% - Énfasis3 14 3" xfId="996" xr:uid="{00000000-0005-0000-0000-00004C030000}"/>
-    <cellStyle name="40% - Énfasis3 15" xfId="234" xr:uid="{00000000-0005-0000-0000-00004D030000}"/>
-    <cellStyle name="40% - Énfasis3 15 2" xfId="529" xr:uid="{00000000-0005-0000-0000-00004E030000}"/>
-    <cellStyle name="40% - Énfasis3 15 2 2" xfId="999" xr:uid="{00000000-0005-0000-0000-00004F030000}"/>
-    <cellStyle name="40% - Énfasis3 15 3" xfId="998" xr:uid="{00000000-0005-0000-0000-000050030000}"/>
-    <cellStyle name="40% - Énfasis3 16" xfId="248" xr:uid="{00000000-0005-0000-0000-000051030000}"/>
-    <cellStyle name="40% - Énfasis3 16 2" xfId="543" xr:uid="{00000000-0005-0000-0000-000052030000}"/>
-    <cellStyle name="40% - Énfasis3 16 2 2" xfId="1001" xr:uid="{00000000-0005-0000-0000-000053030000}"/>
-    <cellStyle name="40% - Énfasis3 16 3" xfId="1000" xr:uid="{00000000-0005-0000-0000-000054030000}"/>
-    <cellStyle name="40% - Énfasis3 17" xfId="262" xr:uid="{00000000-0005-0000-0000-000055030000}"/>
-    <cellStyle name="40% - Énfasis3 17 2" xfId="557" xr:uid="{00000000-0005-0000-0000-000056030000}"/>
-    <cellStyle name="40% - Énfasis3 17 2 2" xfId="1003" xr:uid="{00000000-0005-0000-0000-000057030000}"/>
-    <cellStyle name="40% - Énfasis3 17 3" xfId="1002" xr:uid="{00000000-0005-0000-0000-000058030000}"/>
-    <cellStyle name="40% - Énfasis3 18" xfId="276" xr:uid="{00000000-0005-0000-0000-000059030000}"/>
-    <cellStyle name="40% - Énfasis3 18 2" xfId="571" xr:uid="{00000000-0005-0000-0000-00005A030000}"/>
-    <cellStyle name="40% - Énfasis3 18 2 2" xfId="1005" xr:uid="{00000000-0005-0000-0000-00005B030000}"/>
-    <cellStyle name="40% - Énfasis3 18 3" xfId="1004" xr:uid="{00000000-0005-0000-0000-00005C030000}"/>
-    <cellStyle name="40% - Énfasis3 19" xfId="290" xr:uid="{00000000-0005-0000-0000-00005D030000}"/>
-    <cellStyle name="40% - Énfasis3 19 2" xfId="585" xr:uid="{00000000-0005-0000-0000-00005E030000}"/>
-    <cellStyle name="40% - Énfasis3 19 2 2" xfId="1007" xr:uid="{00000000-0005-0000-0000-00005F030000}"/>
-    <cellStyle name="40% - Énfasis3 19 3" xfId="1006" xr:uid="{00000000-0005-0000-0000-000060030000}"/>
-    <cellStyle name="40% - Énfasis3 2" xfId="52" xr:uid="{00000000-0005-0000-0000-000061030000}"/>
-    <cellStyle name="40% - Énfasis3 2 2" xfId="347" xr:uid="{00000000-0005-0000-0000-000062030000}"/>
-    <cellStyle name="40% - Énfasis3 2 2 2" xfId="1009" xr:uid="{00000000-0005-0000-0000-000063030000}"/>
-    <cellStyle name="40% - Énfasis3 2 3" xfId="1008" xr:uid="{00000000-0005-0000-0000-000064030000}"/>
-    <cellStyle name="40% - Énfasis3 20" xfId="304" xr:uid="{00000000-0005-0000-0000-000065030000}"/>
-    <cellStyle name="40% - Énfasis3 20 2" xfId="599" xr:uid="{00000000-0005-0000-0000-000066030000}"/>
-    <cellStyle name="40% - Énfasis3 20 2 2" xfId="1011" xr:uid="{00000000-0005-0000-0000-000067030000}"/>
-    <cellStyle name="40% - Énfasis3 20 3" xfId="1010" xr:uid="{00000000-0005-0000-0000-000068030000}"/>
-    <cellStyle name="40% - Énfasis3 21" xfId="318" xr:uid="{00000000-0005-0000-0000-000069030000}"/>
-    <cellStyle name="40% - Énfasis3 21 2" xfId="613" xr:uid="{00000000-0005-0000-0000-00006A030000}"/>
-    <cellStyle name="40% - Énfasis3 21 2 2" xfId="1013" xr:uid="{00000000-0005-0000-0000-00006B030000}"/>
-    <cellStyle name="40% - Énfasis3 21 3" xfId="1012" xr:uid="{00000000-0005-0000-0000-00006C030000}"/>
-    <cellStyle name="40% - Énfasis3 22" xfId="627" xr:uid="{00000000-0005-0000-0000-00006D030000}"/>
-    <cellStyle name="40% - Énfasis3 22 2" xfId="1015" xr:uid="{00000000-0005-0000-0000-00006E030000}"/>
-    <cellStyle name="40% - Énfasis3 22 3" xfId="1014" xr:uid="{00000000-0005-0000-0000-00006F030000}"/>
-    <cellStyle name="40% - Énfasis3 23" xfId="331" xr:uid="{00000000-0005-0000-0000-000070030000}"/>
-    <cellStyle name="40% - Énfasis3 23 2" xfId="1016" xr:uid="{00000000-0005-0000-0000-000071030000}"/>
-    <cellStyle name="40% - Énfasis3 24" xfId="987" xr:uid="{00000000-0005-0000-0000-000072030000}"/>
-    <cellStyle name="40% - Énfasis3 25" xfId="1271" xr:uid="{00000000-0005-0000-0000-000073030000}"/>
-    <cellStyle name="40% - Énfasis3 26" xfId="1285" xr:uid="{00000000-0005-0000-0000-000074030000}"/>
-    <cellStyle name="40% - Énfasis3 27" xfId="1299" xr:uid="{00000000-0005-0000-0000-000075030000}"/>
-    <cellStyle name="40% - Énfasis3 28" xfId="1313" xr:uid="{00000000-0005-0000-0000-000076030000}"/>
-    <cellStyle name="40% - Énfasis3 29" xfId="1327" xr:uid="{00000000-0005-0000-0000-000077030000}"/>
-    <cellStyle name="40% - Énfasis3 3" xfId="66" xr:uid="{00000000-0005-0000-0000-000078030000}"/>
-    <cellStyle name="40% - Énfasis3 3 2" xfId="361" xr:uid="{00000000-0005-0000-0000-000079030000}"/>
-    <cellStyle name="40% - Énfasis3 3 2 2" xfId="1018" xr:uid="{00000000-0005-0000-0000-00007A030000}"/>
-    <cellStyle name="40% - Énfasis3 3 3" xfId="1017" xr:uid="{00000000-0005-0000-0000-00007B030000}"/>
-    <cellStyle name="40% - Énfasis3 30" xfId="1341" xr:uid="{00000000-0005-0000-0000-00007C030000}"/>
-    <cellStyle name="40% - Énfasis3 31" xfId="1355" xr:uid="{00000000-0005-0000-0000-00007D030000}"/>
-    <cellStyle name="40% - Énfasis3 32" xfId="1369" xr:uid="{00000000-0005-0000-0000-00007E030000}"/>
-    <cellStyle name="40% - Énfasis3 33" xfId="1383" xr:uid="{00000000-0005-0000-0000-00007F030000}"/>
-    <cellStyle name="40% - Énfasis3 34" xfId="1397" xr:uid="{00000000-0005-0000-0000-000080030000}"/>
-    <cellStyle name="40% - Énfasis3 35" xfId="1411" xr:uid="{00000000-0005-0000-0000-000081030000}"/>
-    <cellStyle name="40% - Énfasis3 36" xfId="1425" xr:uid="{00000000-0005-0000-0000-000082030000}"/>
-    <cellStyle name="40% - Énfasis3 37" xfId="1439" xr:uid="{00000000-0005-0000-0000-000083030000}"/>
-    <cellStyle name="40% - Énfasis3 38" xfId="1453" xr:uid="{00000000-0005-0000-0000-000084030000}"/>
-    <cellStyle name="40% - Énfasis3 39" xfId="1467" xr:uid="{00000000-0005-0000-0000-000085030000}"/>
-    <cellStyle name="40% - Énfasis3 4" xfId="80" xr:uid="{00000000-0005-0000-0000-000086030000}"/>
-    <cellStyle name="40% - Énfasis3 4 2" xfId="375" xr:uid="{00000000-0005-0000-0000-000087030000}"/>
-    <cellStyle name="40% - Énfasis3 4 2 2" xfId="1020" xr:uid="{00000000-0005-0000-0000-000088030000}"/>
-    <cellStyle name="40% - Énfasis3 4 3" xfId="1019" xr:uid="{00000000-0005-0000-0000-000089030000}"/>
-    <cellStyle name="40% - Énfasis3 40" xfId="1482" xr:uid="{00000000-0005-0000-0000-00008A030000}"/>
-    <cellStyle name="40% - Énfasis3 5" xfId="94" xr:uid="{00000000-0005-0000-0000-00008B030000}"/>
-    <cellStyle name="40% - Énfasis3 5 2" xfId="389" xr:uid="{00000000-0005-0000-0000-00008C030000}"/>
-    <cellStyle name="40% - Énfasis3 5 2 2" xfId="1022" xr:uid="{00000000-0005-0000-0000-00008D030000}"/>
-    <cellStyle name="40% - Énfasis3 5 3" xfId="1021" xr:uid="{00000000-0005-0000-0000-00008E030000}"/>
-    <cellStyle name="40% - Énfasis3 6" xfId="108" xr:uid="{00000000-0005-0000-0000-00008F030000}"/>
-    <cellStyle name="40% - Énfasis3 6 2" xfId="403" xr:uid="{00000000-0005-0000-0000-000090030000}"/>
-    <cellStyle name="40% - Énfasis3 6 2 2" xfId="1024" xr:uid="{00000000-0005-0000-0000-000091030000}"/>
-    <cellStyle name="40% - Énfasis3 6 3" xfId="1023" xr:uid="{00000000-0005-0000-0000-000092030000}"/>
-    <cellStyle name="40% - Énfasis3 7" xfId="122" xr:uid="{00000000-0005-0000-0000-000093030000}"/>
-    <cellStyle name="40% - Énfasis3 7 2" xfId="417" xr:uid="{00000000-0005-0000-0000-000094030000}"/>
-    <cellStyle name="40% - Énfasis3 7 2 2" xfId="1026" xr:uid="{00000000-0005-0000-0000-000095030000}"/>
-    <cellStyle name="40% - Énfasis3 7 3" xfId="1025" xr:uid="{00000000-0005-0000-0000-000096030000}"/>
-    <cellStyle name="40% - Énfasis3 8" xfId="136" xr:uid="{00000000-0005-0000-0000-000097030000}"/>
-    <cellStyle name="40% - Énfasis3 8 2" xfId="431" xr:uid="{00000000-0005-0000-0000-000098030000}"/>
-    <cellStyle name="40% - Énfasis3 8 2 2" xfId="1028" xr:uid="{00000000-0005-0000-0000-000099030000}"/>
-    <cellStyle name="40% - Énfasis3 8 3" xfId="1027" xr:uid="{00000000-0005-0000-0000-00009A030000}"/>
-    <cellStyle name="40% - Énfasis3 9" xfId="150" xr:uid="{00000000-0005-0000-0000-00009B030000}"/>
-    <cellStyle name="40% - Énfasis3 9 2" xfId="445" xr:uid="{00000000-0005-0000-0000-00009C030000}"/>
-    <cellStyle name="40% - Énfasis3 9 2 2" xfId="1030" xr:uid="{00000000-0005-0000-0000-00009D030000}"/>
-    <cellStyle name="40% - Énfasis3 9 3" xfId="1029" xr:uid="{00000000-0005-0000-0000-00009E030000}"/>
+    <cellStyle name="40% - Énfasis3 10" xfId="164"/>
+    <cellStyle name="40% - Énfasis3 10 2" xfId="459"/>
+    <cellStyle name="40% - Énfasis3 10 2 2" xfId="989"/>
+    <cellStyle name="40% - Énfasis3 10 3" xfId="988"/>
+    <cellStyle name="40% - Énfasis3 11" xfId="178"/>
+    <cellStyle name="40% - Énfasis3 11 2" xfId="473"/>
+    <cellStyle name="40% - Énfasis3 11 2 2" xfId="991"/>
+    <cellStyle name="40% - Énfasis3 11 3" xfId="990"/>
+    <cellStyle name="40% - Énfasis3 12" xfId="192"/>
+    <cellStyle name="40% - Énfasis3 12 2" xfId="487"/>
+    <cellStyle name="40% - Énfasis3 12 2 2" xfId="993"/>
+    <cellStyle name="40% - Énfasis3 12 3" xfId="992"/>
+    <cellStyle name="40% - Énfasis3 13" xfId="206"/>
+    <cellStyle name="40% - Énfasis3 13 2" xfId="501"/>
+    <cellStyle name="40% - Énfasis3 13 2 2" xfId="995"/>
+    <cellStyle name="40% - Énfasis3 13 3" xfId="994"/>
+    <cellStyle name="40% - Énfasis3 14" xfId="220"/>
+    <cellStyle name="40% - Énfasis3 14 2" xfId="515"/>
+    <cellStyle name="40% - Énfasis3 14 2 2" xfId="997"/>
+    <cellStyle name="40% - Énfasis3 14 3" xfId="996"/>
+    <cellStyle name="40% - Énfasis3 15" xfId="234"/>
+    <cellStyle name="40% - Énfasis3 15 2" xfId="529"/>
+    <cellStyle name="40% - Énfasis3 15 2 2" xfId="999"/>
+    <cellStyle name="40% - Énfasis3 15 3" xfId="998"/>
+    <cellStyle name="40% - Énfasis3 16" xfId="248"/>
+    <cellStyle name="40% - Énfasis3 16 2" xfId="543"/>
+    <cellStyle name="40% - Énfasis3 16 2 2" xfId="1001"/>
+    <cellStyle name="40% - Énfasis3 16 3" xfId="1000"/>
+    <cellStyle name="40% - Énfasis3 17" xfId="262"/>
+    <cellStyle name="40% - Énfasis3 17 2" xfId="557"/>
+    <cellStyle name="40% - Énfasis3 17 2 2" xfId="1003"/>
+    <cellStyle name="40% - Énfasis3 17 3" xfId="1002"/>
+    <cellStyle name="40% - Énfasis3 18" xfId="276"/>
+    <cellStyle name="40% - Énfasis3 18 2" xfId="571"/>
+    <cellStyle name="40% - Énfasis3 18 2 2" xfId="1005"/>
+    <cellStyle name="40% - Énfasis3 18 3" xfId="1004"/>
+    <cellStyle name="40% - Énfasis3 19" xfId="290"/>
+    <cellStyle name="40% - Énfasis3 19 2" xfId="585"/>
+    <cellStyle name="40% - Énfasis3 19 2 2" xfId="1007"/>
+    <cellStyle name="40% - Énfasis3 19 3" xfId="1006"/>
+    <cellStyle name="40% - Énfasis3 2" xfId="52"/>
+    <cellStyle name="40% - Énfasis3 2 2" xfId="347"/>
+    <cellStyle name="40% - Énfasis3 2 2 2" xfId="1009"/>
+    <cellStyle name="40% - Énfasis3 2 3" xfId="1008"/>
+    <cellStyle name="40% - Énfasis3 20" xfId="304"/>
+    <cellStyle name="40% - Énfasis3 20 2" xfId="599"/>
+    <cellStyle name="40% - Énfasis3 20 2 2" xfId="1011"/>
+    <cellStyle name="40% - Énfasis3 20 3" xfId="1010"/>
+    <cellStyle name="40% - Énfasis3 21" xfId="318"/>
+    <cellStyle name="40% - Énfasis3 21 2" xfId="613"/>
+    <cellStyle name="40% - Énfasis3 21 2 2" xfId="1013"/>
+    <cellStyle name="40% - Énfasis3 21 3" xfId="1012"/>
+    <cellStyle name="40% - Énfasis3 22" xfId="627"/>
+    <cellStyle name="40% - Énfasis3 22 2" xfId="1015"/>
+    <cellStyle name="40% - Énfasis3 22 3" xfId="1014"/>
+    <cellStyle name="40% - Énfasis3 23" xfId="331"/>
+    <cellStyle name="40% - Énfasis3 23 2" xfId="1016"/>
+    <cellStyle name="40% - Énfasis3 24" xfId="987"/>
+    <cellStyle name="40% - Énfasis3 25" xfId="1271"/>
+    <cellStyle name="40% - Énfasis3 26" xfId="1285"/>
+    <cellStyle name="40% - Énfasis3 27" xfId="1299"/>
+    <cellStyle name="40% - Énfasis3 28" xfId="1313"/>
+    <cellStyle name="40% - Énfasis3 29" xfId="1327"/>
+    <cellStyle name="40% - Énfasis3 3" xfId="66"/>
+    <cellStyle name="40% - Énfasis3 3 2" xfId="361"/>
+    <cellStyle name="40% - Énfasis3 3 2 2" xfId="1018"/>
+    <cellStyle name="40% - Énfasis3 3 3" xfId="1017"/>
+    <cellStyle name="40% - Énfasis3 30" xfId="1341"/>
+    <cellStyle name="40% - Énfasis3 31" xfId="1355"/>
+    <cellStyle name="40% - Énfasis3 32" xfId="1369"/>
+    <cellStyle name="40% - Énfasis3 33" xfId="1383"/>
+    <cellStyle name="40% - Énfasis3 34" xfId="1397"/>
+    <cellStyle name="40% - Énfasis3 35" xfId="1411"/>
+    <cellStyle name="40% - Énfasis3 36" xfId="1425"/>
+    <cellStyle name="40% - Énfasis3 37" xfId="1439"/>
+    <cellStyle name="40% - Énfasis3 38" xfId="1453"/>
+    <cellStyle name="40% - Énfasis3 39" xfId="1467"/>
+    <cellStyle name="40% - Énfasis3 4" xfId="80"/>
+    <cellStyle name="40% - Énfasis3 4 2" xfId="375"/>
+    <cellStyle name="40% - Énfasis3 4 2 2" xfId="1020"/>
+    <cellStyle name="40% - Énfasis3 4 3" xfId="1019"/>
+    <cellStyle name="40% - Énfasis3 40" xfId="1482"/>
+    <cellStyle name="40% - Énfasis3 5" xfId="94"/>
+    <cellStyle name="40% - Énfasis3 5 2" xfId="389"/>
+    <cellStyle name="40% - Énfasis3 5 2 2" xfId="1022"/>
+    <cellStyle name="40% - Énfasis3 5 3" xfId="1021"/>
+    <cellStyle name="40% - Énfasis3 6" xfId="108"/>
+    <cellStyle name="40% - Énfasis3 6 2" xfId="403"/>
+    <cellStyle name="40% - Énfasis3 6 2 2" xfId="1024"/>
+    <cellStyle name="40% - Énfasis3 6 3" xfId="1023"/>
+    <cellStyle name="40% - Énfasis3 7" xfId="122"/>
+    <cellStyle name="40% - Énfasis3 7 2" xfId="417"/>
+    <cellStyle name="40% - Énfasis3 7 2 2" xfId="1026"/>
+    <cellStyle name="40% - Énfasis3 7 3" xfId="1025"/>
+    <cellStyle name="40% - Énfasis3 8" xfId="136"/>
+    <cellStyle name="40% - Énfasis3 8 2" xfId="431"/>
+    <cellStyle name="40% - Énfasis3 8 2 2" xfId="1028"/>
+    <cellStyle name="40% - Énfasis3 8 3" xfId="1027"/>
+    <cellStyle name="40% - Énfasis3 9" xfId="150"/>
+    <cellStyle name="40% - Énfasis3 9 2" xfId="445"/>
+    <cellStyle name="40% - Énfasis3 9 2 2" xfId="1030"/>
+    <cellStyle name="40% - Énfasis3 9 3" xfId="1029"/>
     <cellStyle name="40% - Énfasis4" xfId="33" builtinId="43" customBuiltin="1"/>
-    <cellStyle name="40% - Énfasis4 10" xfId="166" xr:uid="{00000000-0005-0000-0000-0000A0030000}"/>
-    <cellStyle name="40% - Énfasis4 10 2" xfId="461" xr:uid="{00000000-0005-0000-0000-0000A1030000}"/>
-    <cellStyle name="40% - Énfasis4 10 2 2" xfId="1033" xr:uid="{00000000-0005-0000-0000-0000A2030000}"/>
-    <cellStyle name="40% - Énfasis4 10 3" xfId="1032" xr:uid="{00000000-0005-0000-0000-0000A3030000}"/>
-    <cellStyle name="40% - Énfasis4 11" xfId="180" xr:uid="{00000000-0005-0000-0000-0000A4030000}"/>
-    <cellStyle name="40% - Énfasis4 11 2" xfId="475" xr:uid="{00000000-0005-0000-0000-0000A5030000}"/>
-    <cellStyle name="40% - Énfasis4 11 2 2" xfId="1035" xr:uid="{00000000-0005-0000-0000-0000A6030000}"/>
-    <cellStyle name="40% - Énfasis4 11 3" xfId="1034" xr:uid="{00000000-0005-0000-0000-0000A7030000}"/>
-    <cellStyle name="40% - Énfasis4 12" xfId="194" xr:uid="{00000000-0005-0000-0000-0000A8030000}"/>
-    <cellStyle name="40% - Énfasis4 12 2" xfId="489" xr:uid="{00000000-0005-0000-0000-0000A9030000}"/>
-    <cellStyle name="40% - Énfasis4 12 2 2" xfId="1037" xr:uid="{00000000-0005-0000-0000-0000AA030000}"/>
-    <cellStyle name="40% - Énfasis4 12 3" xfId="1036" xr:uid="{00000000-0005-0000-0000-0000AB030000}"/>
-    <cellStyle name="40% - Énfasis4 13" xfId="208" xr:uid="{00000000-0005-0000-0000-0000AC030000}"/>
-    <cellStyle name="40% - Énfasis4 13 2" xfId="503" xr:uid="{00000000-0005-0000-0000-0000AD030000}"/>
-    <cellStyle name="40% - Énfasis4 13 2 2" xfId="1039" xr:uid="{00000000-0005-0000-0000-0000AE030000}"/>
-    <cellStyle name="40% - Énfasis4 13 3" xfId="1038" xr:uid="{00000000-0005-0000-0000-0000AF030000}"/>
-    <cellStyle name="40% - Énfasis4 14" xfId="222" xr:uid="{00000000-0005-0000-0000-0000B0030000}"/>
-    <cellStyle name="40% - Énfasis4 14 2" xfId="517" xr:uid="{00000000-0005-0000-0000-0000B1030000}"/>
-    <cellStyle name="40% - Énfasis4 14 2 2" xfId="1041" xr:uid="{00000000-0005-0000-0000-0000B2030000}"/>
-    <cellStyle name="40% - Énfasis4 14 3" xfId="1040" xr:uid="{00000000-0005-0000-0000-0000B3030000}"/>
-    <cellStyle name="40% - Énfasis4 15" xfId="236" xr:uid="{00000000-0005-0000-0000-0000B4030000}"/>
-    <cellStyle name="40% - Énfasis4 15 2" xfId="531" xr:uid="{00000000-0005-0000-0000-0000B5030000}"/>
-    <cellStyle name="40% - Énfasis4 15 2 2" xfId="1043" xr:uid="{00000000-0005-0000-0000-0000B6030000}"/>
-    <cellStyle name="40% - Énfasis4 15 3" xfId="1042" xr:uid="{00000000-0005-0000-0000-0000B7030000}"/>
-    <cellStyle name="40% - Énfasis4 16" xfId="250" xr:uid="{00000000-0005-0000-0000-0000B8030000}"/>
-    <cellStyle name="40% - Énfasis4 16 2" xfId="545" xr:uid="{00000000-0005-0000-0000-0000B9030000}"/>
-    <cellStyle name="40% - Énfasis4 16 2 2" xfId="1045" xr:uid="{00000000-0005-0000-0000-0000BA030000}"/>
-    <cellStyle name="40% - Énfasis4 16 3" xfId="1044" xr:uid="{00000000-0005-0000-0000-0000BB030000}"/>
-    <cellStyle name="40% - Énfasis4 17" xfId="264" xr:uid="{00000000-0005-0000-0000-0000BC030000}"/>
-    <cellStyle name="40% - Énfasis4 17 2" xfId="559" xr:uid="{00000000-0005-0000-0000-0000BD030000}"/>
-    <cellStyle name="40% - Énfasis4 17 2 2" xfId="1047" xr:uid="{00000000-0005-0000-0000-0000BE030000}"/>
-    <cellStyle name="40% - Énfasis4 17 3" xfId="1046" xr:uid="{00000000-0005-0000-0000-0000BF030000}"/>
-    <cellStyle name="40% - Énfasis4 18" xfId="278" xr:uid="{00000000-0005-0000-0000-0000C0030000}"/>
-    <cellStyle name="40% - Énfasis4 18 2" xfId="573" xr:uid="{00000000-0005-0000-0000-0000C1030000}"/>
-    <cellStyle name="40% - Énfasis4 18 2 2" xfId="1049" xr:uid="{00000000-0005-0000-0000-0000C2030000}"/>
-    <cellStyle name="40% - Énfasis4 18 3" xfId="1048" xr:uid="{00000000-0005-0000-0000-0000C3030000}"/>
-    <cellStyle name="40% - Énfasis4 19" xfId="292" xr:uid="{00000000-0005-0000-0000-0000C4030000}"/>
-    <cellStyle name="40% - Énfasis4 19 2" xfId="587" xr:uid="{00000000-0005-0000-0000-0000C5030000}"/>
-    <cellStyle name="40% - Énfasis4 19 2 2" xfId="1051" xr:uid="{00000000-0005-0000-0000-0000C6030000}"/>
-    <cellStyle name="40% - Énfasis4 19 3" xfId="1050" xr:uid="{00000000-0005-0000-0000-0000C7030000}"/>
-    <cellStyle name="40% - Énfasis4 2" xfId="54" xr:uid="{00000000-0005-0000-0000-0000C8030000}"/>
-    <cellStyle name="40% - Énfasis4 2 2" xfId="349" xr:uid="{00000000-0005-0000-0000-0000C9030000}"/>
-    <cellStyle name="40% - Énfasis4 2 2 2" xfId="1053" xr:uid="{00000000-0005-0000-0000-0000CA030000}"/>
-    <cellStyle name="40% - Énfasis4 2 3" xfId="1052" xr:uid="{00000000-0005-0000-0000-0000CB030000}"/>
-    <cellStyle name="40% - Énfasis4 20" xfId="306" xr:uid="{00000000-0005-0000-0000-0000CC030000}"/>
-    <cellStyle name="40% - Énfasis4 20 2" xfId="601" xr:uid="{00000000-0005-0000-0000-0000CD030000}"/>
-    <cellStyle name="40% - Énfasis4 20 2 2" xfId="1055" xr:uid="{00000000-0005-0000-0000-0000CE030000}"/>
-    <cellStyle name="40% - Énfasis4 20 3" xfId="1054" xr:uid="{00000000-0005-0000-0000-0000CF030000}"/>
-    <cellStyle name="40% - Énfasis4 21" xfId="320" xr:uid="{00000000-0005-0000-0000-0000D0030000}"/>
-    <cellStyle name="40% - Énfasis4 21 2" xfId="615" xr:uid="{00000000-0005-0000-0000-0000D1030000}"/>
-    <cellStyle name="40% - Énfasis4 21 2 2" xfId="1057" xr:uid="{00000000-0005-0000-0000-0000D2030000}"/>
-    <cellStyle name="40% - Énfasis4 21 3" xfId="1056" xr:uid="{00000000-0005-0000-0000-0000D3030000}"/>
-    <cellStyle name="40% - Énfasis4 22" xfId="629" xr:uid="{00000000-0005-0000-0000-0000D4030000}"/>
-    <cellStyle name="40% - Énfasis4 22 2" xfId="1059" xr:uid="{00000000-0005-0000-0000-0000D5030000}"/>
-    <cellStyle name="40% - Énfasis4 22 3" xfId="1058" xr:uid="{00000000-0005-0000-0000-0000D6030000}"/>
-    <cellStyle name="40% - Énfasis4 23" xfId="333" xr:uid="{00000000-0005-0000-0000-0000D7030000}"/>
-    <cellStyle name="40% - Énfasis4 23 2" xfId="1060" xr:uid="{00000000-0005-0000-0000-0000D8030000}"/>
-    <cellStyle name="40% - Énfasis4 24" xfId="1031" xr:uid="{00000000-0005-0000-0000-0000D9030000}"/>
-    <cellStyle name="40% - Énfasis4 25" xfId="1273" xr:uid="{00000000-0005-0000-0000-0000DA030000}"/>
-    <cellStyle name="40% - Énfasis4 26" xfId="1287" xr:uid="{00000000-0005-0000-0000-0000DB030000}"/>
-    <cellStyle name="40% - Énfasis4 27" xfId="1301" xr:uid="{00000000-0005-0000-0000-0000DC030000}"/>
-    <cellStyle name="40% - Énfasis4 28" xfId="1315" xr:uid="{00000000-0005-0000-0000-0000DD030000}"/>
-    <cellStyle name="40% - Énfasis4 29" xfId="1329" xr:uid="{00000000-0005-0000-0000-0000DE030000}"/>
-    <cellStyle name="40% - Énfasis4 3" xfId="68" xr:uid="{00000000-0005-0000-0000-0000DF030000}"/>
-    <cellStyle name="40% - Énfasis4 3 2" xfId="363" xr:uid="{00000000-0005-0000-0000-0000E0030000}"/>
-    <cellStyle name="40% - Énfasis4 3 2 2" xfId="1062" xr:uid="{00000000-0005-0000-0000-0000E1030000}"/>
-    <cellStyle name="40% - Énfasis4 3 3" xfId="1061" xr:uid="{00000000-0005-0000-0000-0000E2030000}"/>
-    <cellStyle name="40% - Énfasis4 30" xfId="1343" xr:uid="{00000000-0005-0000-0000-0000E3030000}"/>
-    <cellStyle name="40% - Énfasis4 31" xfId="1357" xr:uid="{00000000-0005-0000-0000-0000E4030000}"/>
-    <cellStyle name="40% - Énfasis4 32" xfId="1371" xr:uid="{00000000-0005-0000-0000-0000E5030000}"/>
-    <cellStyle name="40% - Énfasis4 33" xfId="1385" xr:uid="{00000000-0005-0000-0000-0000E6030000}"/>
-    <cellStyle name="40% - Énfasis4 34" xfId="1399" xr:uid="{00000000-0005-0000-0000-0000E7030000}"/>
-    <cellStyle name="40% - Énfasis4 35" xfId="1413" xr:uid="{00000000-0005-0000-0000-0000E8030000}"/>
-    <cellStyle name="40% - Énfasis4 36" xfId="1427" xr:uid="{00000000-0005-0000-0000-0000E9030000}"/>
-    <cellStyle name="40% - Énfasis4 37" xfId="1441" xr:uid="{00000000-0005-0000-0000-0000EA030000}"/>
-    <cellStyle name="40% - Énfasis4 38" xfId="1455" xr:uid="{00000000-0005-0000-0000-0000EB030000}"/>
-    <cellStyle name="40% - Énfasis4 39" xfId="1469" xr:uid="{00000000-0005-0000-0000-0000EC030000}"/>
-    <cellStyle name="40% - Énfasis4 4" xfId="82" xr:uid="{00000000-0005-0000-0000-0000ED030000}"/>
-    <cellStyle name="40% - Énfasis4 4 2" xfId="377" xr:uid="{00000000-0005-0000-0000-0000EE030000}"/>
-    <cellStyle name="40% - Énfasis4 4 2 2" xfId="1064" xr:uid="{00000000-0005-0000-0000-0000EF030000}"/>
-    <cellStyle name="40% - Énfasis4 4 3" xfId="1063" xr:uid="{00000000-0005-0000-0000-0000F0030000}"/>
-    <cellStyle name="40% - Énfasis4 40" xfId="1484" xr:uid="{00000000-0005-0000-0000-0000F1030000}"/>
-    <cellStyle name="40% - Énfasis4 5" xfId="96" xr:uid="{00000000-0005-0000-0000-0000F2030000}"/>
-    <cellStyle name="40% - Énfasis4 5 2" xfId="391" xr:uid="{00000000-0005-0000-0000-0000F3030000}"/>
-    <cellStyle name="40% - Énfasis4 5 2 2" xfId="1066" xr:uid="{00000000-0005-0000-0000-0000F4030000}"/>
-    <cellStyle name="40% - Énfasis4 5 3" xfId="1065" xr:uid="{00000000-0005-0000-0000-0000F5030000}"/>
-    <cellStyle name="40% - Énfasis4 6" xfId="110" xr:uid="{00000000-0005-0000-0000-0000F6030000}"/>
-    <cellStyle name="40% - Énfasis4 6 2" xfId="405" xr:uid="{00000000-0005-0000-0000-0000F7030000}"/>
-    <cellStyle name="40% - Énfasis4 6 2 2" xfId="1068" xr:uid="{00000000-0005-0000-0000-0000F8030000}"/>
-    <cellStyle name="40% - Énfasis4 6 3" xfId="1067" xr:uid="{00000000-0005-0000-0000-0000F9030000}"/>
-    <cellStyle name="40% - Énfasis4 7" xfId="124" xr:uid="{00000000-0005-0000-0000-0000FA030000}"/>
-    <cellStyle name="40% - Énfasis4 7 2" xfId="419" xr:uid="{00000000-0005-0000-0000-0000FB030000}"/>
-    <cellStyle name="40% - Énfasis4 7 2 2" xfId="1070" xr:uid="{00000000-0005-0000-0000-0000FC030000}"/>
-    <cellStyle name="40% - Énfasis4 7 3" xfId="1069" xr:uid="{00000000-0005-0000-0000-0000FD030000}"/>
-    <cellStyle name="40% - Énfasis4 8" xfId="138" xr:uid="{00000000-0005-0000-0000-0000FE030000}"/>
-    <cellStyle name="40% - Énfasis4 8 2" xfId="433" xr:uid="{00000000-0005-0000-0000-0000FF030000}"/>
-    <cellStyle name="40% - Énfasis4 8 2 2" xfId="1072" xr:uid="{00000000-0005-0000-0000-000000040000}"/>
-    <cellStyle name="40% - Énfasis4 8 3" xfId="1071" xr:uid="{00000000-0005-0000-0000-000001040000}"/>
-    <cellStyle name="40% - Énfasis4 9" xfId="152" xr:uid="{00000000-0005-0000-0000-000002040000}"/>
-    <cellStyle name="40% - Énfasis4 9 2" xfId="447" xr:uid="{00000000-0005-0000-0000-000003040000}"/>
-    <cellStyle name="40% - Énfasis4 9 2 2" xfId="1074" xr:uid="{00000000-0005-0000-0000-000004040000}"/>
-    <cellStyle name="40% - Énfasis4 9 3" xfId="1073" xr:uid="{00000000-0005-0000-0000-000005040000}"/>
+    <cellStyle name="40% - Énfasis4 10" xfId="166"/>
+    <cellStyle name="40% - Énfasis4 10 2" xfId="461"/>
+    <cellStyle name="40% - Énfasis4 10 2 2" xfId="1033"/>
+    <cellStyle name="40% - Énfasis4 10 3" xfId="1032"/>
+    <cellStyle name="40% - Énfasis4 11" xfId="180"/>
+    <cellStyle name="40% - Énfasis4 11 2" xfId="475"/>
+    <cellStyle name="40% - Énfasis4 11 2 2" xfId="1035"/>
+    <cellStyle name="40% - Énfasis4 11 3" xfId="1034"/>
+    <cellStyle name="40% - Énfasis4 12" xfId="194"/>
+    <cellStyle name="40% - Énfasis4 12 2" xfId="489"/>
+    <cellStyle name="40% - Énfasis4 12 2 2" xfId="1037"/>
+    <cellStyle name="40% - Énfasis4 12 3" xfId="1036"/>
+    <cellStyle name="40% - Énfasis4 13" xfId="208"/>
+    <cellStyle name="40% - Énfasis4 13 2" xfId="503"/>
+    <cellStyle name="40% - Énfasis4 13 2 2" xfId="1039"/>
+    <cellStyle name="40% - Énfasis4 13 3" xfId="1038"/>
+    <cellStyle name="40% - Énfasis4 14" xfId="222"/>
+    <cellStyle name="40% - Énfasis4 14 2" xfId="517"/>
+    <cellStyle name="40% - Énfasis4 14 2 2" xfId="1041"/>
+    <cellStyle name="40% - Énfasis4 14 3" xfId="1040"/>
+    <cellStyle name="40% - Énfasis4 15" xfId="236"/>
+    <cellStyle name="40% - Énfasis4 15 2" xfId="531"/>
+    <cellStyle name="40% - Énfasis4 15 2 2" xfId="1043"/>
+    <cellStyle name="40% - Énfasis4 15 3" xfId="1042"/>
+    <cellStyle name="40% - Énfasis4 16" xfId="250"/>
+    <cellStyle name="40% - Énfasis4 16 2" xfId="545"/>
+    <cellStyle name="40% - Énfasis4 16 2 2" xfId="1045"/>
+    <cellStyle name="40% - Énfasis4 16 3" xfId="1044"/>
+    <cellStyle name="40% - Énfasis4 17" xfId="264"/>
+    <cellStyle name="40% - Énfasis4 17 2" xfId="559"/>
+    <cellStyle name="40% - Énfasis4 17 2 2" xfId="1047"/>
+    <cellStyle name="40% - Énfasis4 17 3" xfId="1046"/>
+    <cellStyle name="40% - Énfasis4 18" xfId="278"/>
+    <cellStyle name="40% - Énfasis4 18 2" xfId="573"/>
+    <cellStyle name="40% - Énfasis4 18 2 2" xfId="1049"/>
+    <cellStyle name="40% - Énfasis4 18 3" xfId="1048"/>
+    <cellStyle name="40% - Énfasis4 19" xfId="292"/>
+    <cellStyle name="40% - Énfasis4 19 2" xfId="587"/>
+    <cellStyle name="40% - Énfasis4 19 2 2" xfId="1051"/>
+    <cellStyle name="40% - Énfasis4 19 3" xfId="1050"/>
+    <cellStyle name="40% - Énfasis4 2" xfId="54"/>
+    <cellStyle name="40% - Énfasis4 2 2" xfId="349"/>
+    <cellStyle name="40% - Énfasis4 2 2 2" xfId="1053"/>
+    <cellStyle name="40% - Énfasis4 2 3" xfId="1052"/>
+    <cellStyle name="40% - Énfasis4 20" xfId="306"/>
+    <cellStyle name="40% - Énfasis4 20 2" xfId="601"/>
+    <cellStyle name="40% - Énfasis4 20 2 2" xfId="1055"/>
+    <cellStyle name="40% - Énfasis4 20 3" xfId="1054"/>
+    <cellStyle name="40% - Énfasis4 21" xfId="320"/>
+    <cellStyle name="40% - Énfasis4 21 2" xfId="615"/>
+    <cellStyle name="40% - Énfasis4 21 2 2" xfId="1057"/>
+    <cellStyle name="40% - Énfasis4 21 3" xfId="1056"/>
+    <cellStyle name="40% - Énfasis4 22" xfId="629"/>
+    <cellStyle name="40% - Énfasis4 22 2" xfId="1059"/>
+    <cellStyle name="40% - Énfasis4 22 3" xfId="1058"/>
+    <cellStyle name="40% - Énfasis4 23" xfId="333"/>
+    <cellStyle name="40% - Énfasis4 23 2" xfId="1060"/>
+    <cellStyle name="40% - Énfasis4 24" xfId="1031"/>
+    <cellStyle name="40% - Énfasis4 25" xfId="1273"/>
+    <cellStyle name="40% - Énfasis4 26" xfId="1287"/>
+    <cellStyle name="40% - Énfasis4 27" xfId="1301"/>
+    <cellStyle name="40% - Énfasis4 28" xfId="1315"/>
+    <cellStyle name="40% - Énfasis4 29" xfId="1329"/>
+    <cellStyle name="40% - Énfasis4 3" xfId="68"/>
+    <cellStyle name="40% - Énfasis4 3 2" xfId="363"/>
+    <cellStyle name="40% - Énfasis4 3 2 2" xfId="1062"/>
+    <cellStyle name="40% - Énfasis4 3 3" xfId="1061"/>
+    <cellStyle name="40% - Énfasis4 30" xfId="1343"/>
+    <cellStyle name="40% - Énfasis4 31" xfId="1357"/>
+    <cellStyle name="40% - Énfasis4 32" xfId="1371"/>
+    <cellStyle name="40% - Énfasis4 33" xfId="1385"/>
+    <cellStyle name="40% - Énfasis4 34" xfId="1399"/>
+    <cellStyle name="40% - Énfasis4 35" xfId="1413"/>
+    <cellStyle name="40% - Énfasis4 36" xfId="1427"/>
+    <cellStyle name="40% - Énfasis4 37" xfId="1441"/>
+    <cellStyle name="40% - Énfasis4 38" xfId="1455"/>
+    <cellStyle name="40% - Énfasis4 39" xfId="1469"/>
+    <cellStyle name="40% - Énfasis4 4" xfId="82"/>
+    <cellStyle name="40% - Énfasis4 4 2" xfId="377"/>
+    <cellStyle name="40% - Énfasis4 4 2 2" xfId="1064"/>
+    <cellStyle name="40% - Énfasis4 4 3" xfId="1063"/>
+    <cellStyle name="40% - Énfasis4 40" xfId="1484"/>
+    <cellStyle name="40% - Énfasis4 5" xfId="96"/>
+    <cellStyle name="40% - Énfasis4 5 2" xfId="391"/>
+    <cellStyle name="40% - Énfasis4 5 2 2" xfId="1066"/>
+    <cellStyle name="40% - Énfasis4 5 3" xfId="1065"/>
+    <cellStyle name="40% - Énfasis4 6" xfId="110"/>
+    <cellStyle name="40% - Énfasis4 6 2" xfId="405"/>
+    <cellStyle name="40% - Énfasis4 6 2 2" xfId="1068"/>
+    <cellStyle name="40% - Énfasis4 6 3" xfId="1067"/>
+    <cellStyle name="40% - Énfasis4 7" xfId="124"/>
+    <cellStyle name="40% - Énfasis4 7 2" xfId="419"/>
+    <cellStyle name="40% - Énfasis4 7 2 2" xfId="1070"/>
+    <cellStyle name="40% - Énfasis4 7 3" xfId="1069"/>
+    <cellStyle name="40% - Énfasis4 8" xfId="138"/>
+    <cellStyle name="40% - Énfasis4 8 2" xfId="433"/>
+    <cellStyle name="40% - Énfasis4 8 2 2" xfId="1072"/>
+    <cellStyle name="40% - Énfasis4 8 3" xfId="1071"/>
+    <cellStyle name="40% - Énfasis4 9" xfId="152"/>
+    <cellStyle name="40% - Énfasis4 9 2" xfId="447"/>
+    <cellStyle name="40% - Énfasis4 9 2 2" xfId="1074"/>
+    <cellStyle name="40% - Énfasis4 9 3" xfId="1073"/>
     <cellStyle name="40% - Énfasis5" xfId="37" builtinId="47" customBuiltin="1"/>
-    <cellStyle name="40% - Énfasis5 10" xfId="168" xr:uid="{00000000-0005-0000-0000-000007040000}"/>
-    <cellStyle name="40% - Énfasis5 10 2" xfId="463" xr:uid="{00000000-0005-0000-0000-000008040000}"/>
-    <cellStyle name="40% - Énfasis5 10 2 2" xfId="1077" xr:uid="{00000000-0005-0000-0000-000009040000}"/>
-    <cellStyle name="40% - Énfasis5 10 3" xfId="1076" xr:uid="{00000000-0005-0000-0000-00000A040000}"/>
-    <cellStyle name="40% - Énfasis5 11" xfId="182" xr:uid="{00000000-0005-0000-0000-00000B040000}"/>
-    <cellStyle name="40% - Énfasis5 11 2" xfId="477" xr:uid="{00000000-0005-0000-0000-00000C040000}"/>
-    <cellStyle name="40% - Énfasis5 11 2 2" xfId="1079" xr:uid="{00000000-0005-0000-0000-00000D040000}"/>
-    <cellStyle name="40% - Énfasis5 11 3" xfId="1078" xr:uid="{00000000-0005-0000-0000-00000E040000}"/>
-    <cellStyle name="40% - Énfasis5 12" xfId="196" xr:uid="{00000000-0005-0000-0000-00000F040000}"/>
-    <cellStyle name="40% - Énfasis5 12 2" xfId="491" xr:uid="{00000000-0005-0000-0000-000010040000}"/>
-    <cellStyle name="40% - Énfasis5 12 2 2" xfId="1081" xr:uid="{00000000-0005-0000-0000-000011040000}"/>
-    <cellStyle name="40% - Énfasis5 12 3" xfId="1080" xr:uid="{00000000-0005-0000-0000-000012040000}"/>
-    <cellStyle name="40% - Énfasis5 13" xfId="210" xr:uid="{00000000-0005-0000-0000-000013040000}"/>
-    <cellStyle name="40% - Énfasis5 13 2" xfId="505" xr:uid="{00000000-0005-0000-0000-000014040000}"/>
-    <cellStyle name="40% - Énfasis5 13 2 2" xfId="1083" xr:uid="{00000000-0005-0000-0000-000015040000}"/>
-    <cellStyle name="40% - Énfasis5 13 3" xfId="1082" xr:uid="{00000000-0005-0000-0000-000016040000}"/>
-    <cellStyle name="40% - Énfasis5 14" xfId="224" xr:uid="{00000000-0005-0000-0000-000017040000}"/>
-    <cellStyle name="40% - Énfasis5 14 2" xfId="519" xr:uid="{00000000-0005-0000-0000-000018040000}"/>
-    <cellStyle name="40% - Énfasis5 14 2 2" xfId="1085" xr:uid="{00000000-0005-0000-0000-000019040000}"/>
-    <cellStyle name="40% - Énfasis5 14 3" xfId="1084" xr:uid="{00000000-0005-0000-0000-00001A040000}"/>
-    <cellStyle name="40% - Énfasis5 15" xfId="238" xr:uid="{00000000-0005-0000-0000-00001B040000}"/>
-    <cellStyle name="40% - Énfasis5 15 2" xfId="533" xr:uid="{00000000-0005-0000-0000-00001C040000}"/>
-    <cellStyle name="40% - Énfasis5 15 2 2" xfId="1087" xr:uid="{00000000-0005-0000-0000-00001D040000}"/>
-    <cellStyle name="40% - Énfasis5 15 3" xfId="1086" xr:uid="{00000000-0005-0000-0000-00001E040000}"/>
-    <cellStyle name="40% - Énfasis5 16" xfId="252" xr:uid="{00000000-0005-0000-0000-00001F040000}"/>
-    <cellStyle name="40% - Énfasis5 16 2" xfId="547" xr:uid="{00000000-0005-0000-0000-000020040000}"/>
-    <cellStyle name="40% - Énfasis5 16 2 2" xfId="1089" xr:uid="{00000000-0005-0000-0000-000021040000}"/>
-    <cellStyle name="40% - Énfasis5 16 3" xfId="1088" xr:uid="{00000000-0005-0000-0000-000022040000}"/>
-    <cellStyle name="40% - Énfasis5 17" xfId="266" xr:uid="{00000000-0005-0000-0000-000023040000}"/>
-    <cellStyle name="40% - Énfasis5 17 2" xfId="561" xr:uid="{00000000-0005-0000-0000-000024040000}"/>
-    <cellStyle name="40% - Énfasis5 17 2 2" xfId="1091" xr:uid="{00000000-0005-0000-0000-000025040000}"/>
-    <cellStyle name="40% - Énfasis5 17 3" xfId="1090" xr:uid="{00000000-0005-0000-0000-000026040000}"/>
-    <cellStyle name="40% - Énfasis5 18" xfId="280" xr:uid="{00000000-0005-0000-0000-000027040000}"/>
-    <cellStyle name="40% - Énfasis5 18 2" xfId="575" xr:uid="{00000000-0005-0000-0000-000028040000}"/>
-    <cellStyle name="40% - Énfasis5 18 2 2" xfId="1093" xr:uid="{00000000-0005-0000-0000-000029040000}"/>
-    <cellStyle name="40% - Énfasis5 18 3" xfId="1092" xr:uid="{00000000-0005-0000-0000-00002A040000}"/>
-    <cellStyle name="40% - Énfasis5 19" xfId="294" xr:uid="{00000000-0005-0000-0000-00002B040000}"/>
-    <cellStyle name="40% - Énfasis5 19 2" xfId="589" xr:uid="{00000000-0005-0000-0000-00002C040000}"/>
-    <cellStyle name="40% - Énfasis5 19 2 2" xfId="1095" xr:uid="{00000000-0005-0000-0000-00002D040000}"/>
-    <cellStyle name="40% - Énfasis5 19 3" xfId="1094" xr:uid="{00000000-0005-0000-0000-00002E040000}"/>
-    <cellStyle name="40% - Énfasis5 2" xfId="56" xr:uid="{00000000-0005-0000-0000-00002F040000}"/>
-    <cellStyle name="40% - Énfasis5 2 2" xfId="351" xr:uid="{00000000-0005-0000-0000-000030040000}"/>
-    <cellStyle name="40% - Énfasis5 2 2 2" xfId="1097" xr:uid="{00000000-0005-0000-0000-000031040000}"/>
-    <cellStyle name="40% - Énfasis5 2 3" xfId="1096" xr:uid="{00000000-0005-0000-0000-000032040000}"/>
-    <cellStyle name="40% - Énfasis5 20" xfId="308" xr:uid="{00000000-0005-0000-0000-000033040000}"/>
-    <cellStyle name="40% - Énfasis5 20 2" xfId="603" xr:uid="{00000000-0005-0000-0000-000034040000}"/>
-    <cellStyle name="40% - Énfasis5 20 2 2" xfId="1099" xr:uid="{00000000-0005-0000-0000-000035040000}"/>
-    <cellStyle name="40% - Énfasis5 20 3" xfId="1098" xr:uid="{00000000-0005-0000-0000-000036040000}"/>
-    <cellStyle name="40% - Énfasis5 21" xfId="322" xr:uid="{00000000-0005-0000-0000-000037040000}"/>
-    <cellStyle name="40% - Énfasis5 21 2" xfId="617" xr:uid="{00000000-0005-0000-0000-000038040000}"/>
-    <cellStyle name="40% - Énfasis5 21 2 2" xfId="1101" xr:uid="{00000000-0005-0000-0000-000039040000}"/>
-    <cellStyle name="40% - Énfasis5 21 3" xfId="1100" xr:uid="{00000000-0005-0000-0000-00003A040000}"/>
-    <cellStyle name="40% - Énfasis5 22" xfId="631" xr:uid="{00000000-0005-0000-0000-00003B040000}"/>
-    <cellStyle name="40% - Énfasis5 22 2" xfId="1103" xr:uid="{00000000-0005-0000-0000-00003C040000}"/>
-    <cellStyle name="40% - Énfasis5 22 3" xfId="1102" xr:uid="{00000000-0005-0000-0000-00003D040000}"/>
-    <cellStyle name="40% - Énfasis5 23" xfId="335" xr:uid="{00000000-0005-0000-0000-00003E040000}"/>
-    <cellStyle name="40% - Énfasis5 23 2" xfId="1104" xr:uid="{00000000-0005-0000-0000-00003F040000}"/>
-    <cellStyle name="40% - Énfasis5 24" xfId="1075" xr:uid="{00000000-0005-0000-0000-000040040000}"/>
-    <cellStyle name="40% - Énfasis5 25" xfId="1275" xr:uid="{00000000-0005-0000-0000-000041040000}"/>
-    <cellStyle name="40% - Énfasis5 26" xfId="1289" xr:uid="{00000000-0005-0000-0000-000042040000}"/>
-    <cellStyle name="40% - Énfasis5 27" xfId="1303" xr:uid="{00000000-0005-0000-0000-000043040000}"/>
-    <cellStyle name="40% - Énfasis5 28" xfId="1317" xr:uid="{00000000-0005-0000-0000-000044040000}"/>
-    <cellStyle name="40% - Énfasis5 29" xfId="1331" xr:uid="{00000000-0005-0000-0000-000045040000}"/>
-    <cellStyle name="40% - Énfasis5 3" xfId="70" xr:uid="{00000000-0005-0000-0000-000046040000}"/>
-    <cellStyle name="40% - Énfasis5 3 2" xfId="365" xr:uid="{00000000-0005-0000-0000-000047040000}"/>
-    <cellStyle name="40% - Énfasis5 3 2 2" xfId="1106" xr:uid="{00000000-0005-0000-0000-000048040000}"/>
-    <cellStyle name="40% - Énfasis5 3 3" xfId="1105" xr:uid="{00000000-0005-0000-0000-000049040000}"/>
-    <cellStyle name="40% - Énfasis5 30" xfId="1345" xr:uid="{00000000-0005-0000-0000-00004A040000}"/>
-    <cellStyle name="40% - Énfasis5 31" xfId="1359" xr:uid="{00000000-0005-0000-0000-00004B040000}"/>
-    <cellStyle name="40% - Énfasis5 32" xfId="1373" xr:uid="{00000000-0005-0000-0000-00004C040000}"/>
-    <cellStyle name="40% - Énfasis5 33" xfId="1387" xr:uid="{00000000-0005-0000-0000-00004D040000}"/>
-    <cellStyle name="40% - Énfasis5 34" xfId="1401" xr:uid="{00000000-0005-0000-0000-00004E040000}"/>
-    <cellStyle name="40% - Énfasis5 35" xfId="1415" xr:uid="{00000000-0005-0000-0000-00004F040000}"/>
-    <cellStyle name="40% - Énfasis5 36" xfId="1429" xr:uid="{00000000-0005-0000-0000-000050040000}"/>
-    <cellStyle name="40% - Énfasis5 37" xfId="1443" xr:uid="{00000000-0005-0000-0000-000051040000}"/>
-    <cellStyle name="40% - Énfasis5 38" xfId="1457" xr:uid="{00000000-0005-0000-0000-000052040000}"/>
-    <cellStyle name="40% - Énfasis5 39" xfId="1471" xr:uid="{00000000-0005-0000-0000-000053040000}"/>
-    <cellStyle name="40% - Énfasis5 4" xfId="84" xr:uid="{00000000-0005-0000-0000-000054040000}"/>
-    <cellStyle name="40% - Énfasis5 4 2" xfId="379" xr:uid="{00000000-0005-0000-0000-000055040000}"/>
-    <cellStyle name="40% - Énfasis5 4 2 2" xfId="1108" xr:uid="{00000000-0005-0000-0000-000056040000}"/>
-    <cellStyle name="40% - Énfasis5 4 3" xfId="1107" xr:uid="{00000000-0005-0000-0000-000057040000}"/>
-    <cellStyle name="40% - Énfasis5 40" xfId="1486" xr:uid="{00000000-0005-0000-0000-000058040000}"/>
-    <cellStyle name="40% - Énfasis5 5" xfId="98" xr:uid="{00000000-0005-0000-0000-000059040000}"/>
-    <cellStyle name="40% - Énfasis5 5 2" xfId="393" xr:uid="{00000000-0005-0000-0000-00005A040000}"/>
-    <cellStyle name="40% - Énfasis5 5 2 2" xfId="1110" xr:uid="{00000000-0005-0000-0000-00005B040000}"/>
-    <cellStyle name="40% - Énfasis5 5 3" xfId="1109" xr:uid="{00000000-0005-0000-0000-00005C040000}"/>
-    <cellStyle name="40% - Énfasis5 6" xfId="112" xr:uid="{00000000-0005-0000-0000-00005D040000}"/>
-    <cellStyle name="40% - Énfasis5 6 2" xfId="407" xr:uid="{00000000-0005-0000-0000-00005E040000}"/>
-    <cellStyle name="40% - Énfasis5 6 2 2" xfId="1112" xr:uid="{00000000-0005-0000-0000-00005F040000}"/>
-    <cellStyle name="40% - Énfasis5 6 3" xfId="1111" xr:uid="{00000000-0005-0000-0000-000060040000}"/>
-    <cellStyle name="40% - Énfasis5 7" xfId="126" xr:uid="{00000000-0005-0000-0000-000061040000}"/>
-    <cellStyle name="40% - Énfasis5 7 2" xfId="421" xr:uid="{00000000-0005-0000-0000-000062040000}"/>
-    <cellStyle name="40% - Énfasis5 7 2 2" xfId="1114" xr:uid="{00000000-0005-0000-0000-000063040000}"/>
-    <cellStyle name="40% - Énfasis5 7 3" xfId="1113" xr:uid="{00000000-0005-0000-0000-000064040000}"/>
-    <cellStyle name="40% - Énfasis5 8" xfId="140" xr:uid="{00000000-0005-0000-0000-000065040000}"/>
-    <cellStyle name="40% - Énfasis5 8 2" xfId="435" xr:uid="{00000000-0005-0000-0000-000066040000}"/>
-    <cellStyle name="40% - Énfasis5 8 2 2" xfId="1116" xr:uid="{00000000-0005-0000-0000-000067040000}"/>
-    <cellStyle name="40% - Énfasis5 8 3" xfId="1115" xr:uid="{00000000-0005-0000-0000-000068040000}"/>
-    <cellStyle name="40% - Énfasis5 9" xfId="154" xr:uid="{00000000-0005-0000-0000-000069040000}"/>
-    <cellStyle name="40% - Énfasis5 9 2" xfId="449" xr:uid="{00000000-0005-0000-0000-00006A040000}"/>
-    <cellStyle name="40% - Énfasis5 9 2 2" xfId="1118" xr:uid="{00000000-0005-0000-0000-00006B040000}"/>
-    <cellStyle name="40% - Énfasis5 9 3" xfId="1117" xr:uid="{00000000-0005-0000-0000-00006C040000}"/>
+    <cellStyle name="40% - Énfasis5 10" xfId="168"/>
+    <cellStyle name="40% - Énfasis5 10 2" xfId="463"/>
+    <cellStyle name="40% - Énfasis5 10 2 2" xfId="1077"/>
+    <cellStyle name="40% - Énfasis5 10 3" xfId="1076"/>
+    <cellStyle name="40% - Énfasis5 11" xfId="182"/>
+    <cellStyle name="40% - Énfasis5 11 2" xfId="477"/>
+    <cellStyle name="40% - Énfasis5 11 2 2" xfId="1079"/>
+    <cellStyle name="40% - Énfasis5 11 3" xfId="1078"/>
+    <cellStyle name="40% - Énfasis5 12" xfId="196"/>
+    <cellStyle name="40% - Énfasis5 12 2" xfId="491"/>
+    <cellStyle name="40% - Énfasis5 12 2 2" xfId="1081"/>
+    <cellStyle name="40% - Énfasis5 12 3" xfId="1080"/>
+    <cellStyle name="40% - Énfasis5 13" xfId="210"/>
+    <cellStyle name="40% - Énfasis5 13 2" xfId="505"/>
+    <cellStyle name="40% - Énfasis5 13 2 2" xfId="1083"/>
+    <cellStyle name="40% - Énfasis5 13 3" xfId="1082"/>
+    <cellStyle name="40% - Énfasis5 14" xfId="224"/>
+    <cellStyle name="40% - Énfasis5 14 2" xfId="519"/>
+    <cellStyle name="40% - Énfasis5 14 2 2" xfId="1085"/>
+    <cellStyle name="40% - Énfasis5 14 3" xfId="1084"/>
+    <cellStyle name="40% - Énfasis5 15" xfId="238"/>
+    <cellStyle name="40% - Énfasis5 15 2" xfId="533"/>
+    <cellStyle name="40% - Énfasis5 15 2 2" xfId="1087"/>
+    <cellStyle name="40% - Énfasis5 15 3" xfId="1086"/>
+    <cellStyle name="40% - Énfasis5 16" xfId="252"/>
+    <cellStyle name="40% - Énfasis5 16 2" xfId="547"/>
+    <cellStyle name="40% - Énfasis5 16 2 2" xfId="1089"/>
+    <cellStyle name="40% - Énfasis5 16 3" xfId="1088"/>
+    <cellStyle name="40% - Énfasis5 17" xfId="266"/>
+    <cellStyle name="40% - Énfasis5 17 2" xfId="561"/>
+    <cellStyle name="40% - Énfasis5 17 2 2" xfId="1091"/>
+    <cellStyle name="40% - Énfasis5 17 3" xfId="1090"/>
+    <cellStyle name="40% - Énfasis5 18" xfId="280"/>
+    <cellStyle name="40% - Énfasis5 18 2" xfId="575"/>
+    <cellStyle name="40% - Énfasis5 18 2 2" xfId="1093"/>
+    <cellStyle name="40% - Énfasis5 18 3" xfId="1092"/>
+    <cellStyle name="40% - Énfasis5 19" xfId="294"/>
+    <cellStyle name="40% - Énfasis5 19 2" xfId="589"/>
+    <cellStyle name="40% - Énfasis5 19 2 2" xfId="1095"/>
+    <cellStyle name="40% - Énfasis5 19 3" xfId="1094"/>
+    <cellStyle name="40% - Énfasis5 2" xfId="56"/>
+    <cellStyle name="40% - Énfasis5 2 2" xfId="351"/>
+    <cellStyle name="40% - Énfasis5 2 2 2" xfId="1097"/>
+    <cellStyle name="40% - Énfasis5 2 3" xfId="1096"/>
+    <cellStyle name="40% - Énfasis5 20" xfId="308"/>
+    <cellStyle name="40% - Énfasis5 20 2" xfId="603"/>
+    <cellStyle name="40% - Énfasis5 20 2 2" xfId="1099"/>
+    <cellStyle name="40% - Énfasis5 20 3" xfId="1098"/>
+    <cellStyle name="40% - Énfasis5 21" xfId="322"/>
+    <cellStyle name="40% - Énfasis5 21 2" xfId="617"/>
+    <cellStyle name="40% - Énfasis5 21 2 2" xfId="1101"/>
+    <cellStyle name="40% - Énfasis5 21 3" xfId="1100"/>
+    <cellStyle name="40% - Énfasis5 22" xfId="631"/>
+    <cellStyle name="40% - Énfasis5 22 2" xfId="1103"/>
+    <cellStyle name="40% - Énfasis5 22 3" xfId="1102"/>
+    <cellStyle name="40% - Énfasis5 23" xfId="335"/>
+    <cellStyle name="40% - Énfasis5 23 2" xfId="1104"/>
+    <cellStyle name="40% - Énfasis5 24" xfId="1075"/>
+    <cellStyle name="40% - Énfasis5 25" xfId="1275"/>
+    <cellStyle name="40% - Énfasis5 26" xfId="1289"/>
+    <cellStyle name="40% - Énfasis5 27" xfId="1303"/>
+    <cellStyle name="40% - Énfasis5 28" xfId="1317"/>
+    <cellStyle name="40% - Énfasis5 29" xfId="1331"/>
+    <cellStyle name="40% - Énfasis5 3" xfId="70"/>
+    <cellStyle name="40% - Énfasis5 3 2" xfId="365"/>
+    <cellStyle name="40% - Énfasis5 3 2 2" xfId="1106"/>
+    <cellStyle name="40% - Énfasis5 3 3" xfId="1105"/>
+    <cellStyle name="40% - Énfasis5 30" xfId="1345"/>
+    <cellStyle name="40% - Énfasis5 31" xfId="1359"/>
+    <cellStyle name="40% - Énfasis5 32" xfId="1373"/>
+    <cellStyle name="40% - Énfasis5 33" xfId="1387"/>
+    <cellStyle name="40% - Énfasis5 34" xfId="1401"/>
+    <cellStyle name="40% - Énfasis5 35" xfId="1415"/>
+    <cellStyle name="40% - Énfasis5 36" xfId="1429"/>
+    <cellStyle name="40% - Énfasis5 37" xfId="1443"/>
+    <cellStyle name="40% - Énfasis5 38" xfId="1457"/>
+    <cellStyle name="40% - Énfasis5 39" xfId="1471"/>
+    <cellStyle name="40% - Énfasis5 4" xfId="84"/>
+    <cellStyle name="40% - Énfasis5 4 2" xfId="379"/>
+    <cellStyle name="40% - Énfasis5 4 2 2" xfId="1108"/>
+    <cellStyle name="40% - Énfasis5 4 3" xfId="1107"/>
+    <cellStyle name="40% - Énfasis5 40" xfId="1486"/>
+    <cellStyle name="40% - Énfasis5 5" xfId="98"/>
+    <cellStyle name="40% - Énfasis5 5 2" xfId="393"/>
+    <cellStyle name="40% - Énfasis5 5 2 2" xfId="1110"/>
+    <cellStyle name="40% - Énfasis5 5 3" xfId="1109"/>
+    <cellStyle name="40% - Énfasis5 6" xfId="112"/>
+    <cellStyle name="40% - Énfasis5 6 2" xfId="407"/>
+    <cellStyle name="40% - Énfasis5 6 2 2" xfId="1112"/>
+    <cellStyle name="40% - Énfasis5 6 3" xfId="1111"/>
+    <cellStyle name="40% - Énfasis5 7" xfId="126"/>
+    <cellStyle name="40% - Énfasis5 7 2" xfId="421"/>
+    <cellStyle name="40% - Énfasis5 7 2 2" xfId="1114"/>
+    <cellStyle name="40% - Énfasis5 7 3" xfId="1113"/>
+    <cellStyle name="40% - Énfasis5 8" xfId="140"/>
+    <cellStyle name="40% - Énfasis5 8 2" xfId="435"/>
+    <cellStyle name="40% - Énfasis5 8 2 2" xfId="1116"/>
+    <cellStyle name="40% - Énfasis5 8 3" xfId="1115"/>
+    <cellStyle name="40% - Énfasis5 9" xfId="154"/>
+    <cellStyle name="40% - Énfasis5 9 2" xfId="449"/>
+    <cellStyle name="40% - Énfasis5 9 2 2" xfId="1118"/>
+    <cellStyle name="40% - Énfasis5 9 3" xfId="1117"/>
     <cellStyle name="40% - Énfasis6" xfId="41" builtinId="51" customBuiltin="1"/>
-    <cellStyle name="40% - Énfasis6 10" xfId="170" xr:uid="{00000000-0005-0000-0000-00006E040000}"/>
-    <cellStyle name="40% - Énfasis6 10 2" xfId="465" xr:uid="{00000000-0005-0000-0000-00006F040000}"/>
-    <cellStyle name="40% - Énfasis6 10 2 2" xfId="1121" xr:uid="{00000000-0005-0000-0000-000070040000}"/>
-    <cellStyle name="40% - Énfasis6 10 3" xfId="1120" xr:uid="{00000000-0005-0000-0000-000071040000}"/>
-    <cellStyle name="40% - Énfasis6 11" xfId="184" xr:uid="{00000000-0005-0000-0000-000072040000}"/>
-    <cellStyle name="40% - Énfasis6 11 2" xfId="479" xr:uid="{00000000-0005-0000-0000-000073040000}"/>
-    <cellStyle name="40% - Énfasis6 11 2 2" xfId="1123" xr:uid="{00000000-0005-0000-0000-000074040000}"/>
-    <cellStyle name="40% - Énfasis6 11 3" xfId="1122" xr:uid="{00000000-0005-0000-0000-000075040000}"/>
-    <cellStyle name="40% - Énfasis6 12" xfId="198" xr:uid="{00000000-0005-0000-0000-000076040000}"/>
-    <cellStyle name="40% - Énfasis6 12 2" xfId="493" xr:uid="{00000000-0005-0000-0000-000077040000}"/>
-    <cellStyle name="40% - Énfasis6 12 2 2" xfId="1125" xr:uid="{00000000-0005-0000-0000-000078040000}"/>
-    <cellStyle name="40% - Énfasis6 12 3" xfId="1124" xr:uid="{00000000-0005-0000-0000-000079040000}"/>
-    <cellStyle name="40% - Énfasis6 13" xfId="212" xr:uid="{00000000-0005-0000-0000-00007A040000}"/>
-    <cellStyle name="40% - Énfasis6 13 2" xfId="507" xr:uid="{00000000-0005-0000-0000-00007B040000}"/>
-    <cellStyle name="40% - Énfasis6 13 2 2" xfId="1127" xr:uid="{00000000-0005-0000-0000-00007C040000}"/>
-    <cellStyle name="40% - Énfasis6 13 3" xfId="1126" xr:uid="{00000000-0005-0000-0000-00007D040000}"/>
-    <cellStyle name="40% - Énfasis6 14" xfId="226" xr:uid="{00000000-0005-0000-0000-00007E040000}"/>
-    <cellStyle name="40% - Énfasis6 14 2" xfId="521" xr:uid="{00000000-0005-0000-0000-00007F040000}"/>
-    <cellStyle name="40% - Énfasis6 14 2 2" xfId="1129" xr:uid="{00000000-0005-0000-0000-000080040000}"/>
-    <cellStyle name="40% - Énfasis6 14 3" xfId="1128" xr:uid="{00000000-0005-0000-0000-000081040000}"/>
-    <cellStyle name="40% - Énfasis6 15" xfId="240" xr:uid="{00000000-0005-0000-0000-000082040000}"/>
-    <cellStyle name="40% - Énfasis6 15 2" xfId="535" xr:uid="{00000000-0005-0000-0000-000083040000}"/>
-    <cellStyle name="40% - Énfasis6 15 2 2" xfId="1131" xr:uid="{00000000-0005-0000-0000-000084040000}"/>
-    <cellStyle name="40% - Énfasis6 15 3" xfId="1130" xr:uid="{00000000-0005-0000-0000-000085040000}"/>
-    <cellStyle name="40% - Énfasis6 16" xfId="254" xr:uid="{00000000-0005-0000-0000-000086040000}"/>
-    <cellStyle name="40% - Énfasis6 16 2" xfId="549" xr:uid="{00000000-0005-0000-0000-000087040000}"/>
-    <cellStyle name="40% - Énfasis6 16 2 2" xfId="1133" xr:uid="{00000000-0005-0000-0000-000088040000}"/>
-    <cellStyle name="40% - Énfasis6 16 3" xfId="1132" xr:uid="{00000000-0005-0000-0000-000089040000}"/>
-    <cellStyle name="40% - Énfasis6 17" xfId="268" xr:uid="{00000000-0005-0000-0000-00008A040000}"/>
-    <cellStyle name="40% - Énfasis6 17 2" xfId="563" xr:uid="{00000000-0005-0000-0000-00008B040000}"/>
-    <cellStyle name="40% - Énfasis6 17 2 2" xfId="1135" xr:uid="{00000000-0005-0000-0000-00008C040000}"/>
-    <cellStyle name="40% - Énfasis6 17 3" xfId="1134" xr:uid="{00000000-0005-0000-0000-00008D040000}"/>
-    <cellStyle name="40% - Énfasis6 18" xfId="282" xr:uid="{00000000-0005-0000-0000-00008E040000}"/>
-    <cellStyle name="40% - Énfasis6 18 2" xfId="577" xr:uid="{00000000-0005-0000-0000-00008F040000}"/>
-    <cellStyle name="40% - Énfasis6 18 2 2" xfId="1137" xr:uid="{00000000-0005-0000-0000-000090040000}"/>
-    <cellStyle name="40% - Énfasis6 18 3" xfId="1136" xr:uid="{00000000-0005-0000-0000-000091040000}"/>
-    <cellStyle name="40% - Énfasis6 19" xfId="296" xr:uid="{00000000-0005-0000-0000-000092040000}"/>
-    <cellStyle name="40% - Énfasis6 19 2" xfId="591" xr:uid="{00000000-0005-0000-0000-000093040000}"/>
-    <cellStyle name="40% - Énfasis6 19 2 2" xfId="1139" xr:uid="{00000000-0005-0000-0000-000094040000}"/>
-    <cellStyle name="40% - Énfasis6 19 3" xfId="1138" xr:uid="{00000000-0005-0000-0000-000095040000}"/>
-    <cellStyle name="40% - Énfasis6 2" xfId="58" xr:uid="{00000000-0005-0000-0000-000096040000}"/>
-    <cellStyle name="40% - Énfasis6 2 2" xfId="353" xr:uid="{00000000-0005-0000-0000-000097040000}"/>
-    <cellStyle name="40% - Énfasis6 2 2 2" xfId="1141" xr:uid="{00000000-0005-0000-0000-000098040000}"/>
-    <cellStyle name="40% - Énfasis6 2 3" xfId="1140" xr:uid="{00000000-0005-0000-0000-000099040000}"/>
-    <cellStyle name="40% - Énfasis6 20" xfId="310" xr:uid="{00000000-0005-0000-0000-00009A040000}"/>
-    <cellStyle name="40% - Énfasis6 20 2" xfId="605" xr:uid="{00000000-0005-0000-0000-00009B040000}"/>
-    <cellStyle name="40% - Énfasis6 20 2 2" xfId="1143" xr:uid="{00000000-0005-0000-0000-00009C040000}"/>
-    <cellStyle name="40% - Énfasis6 20 3" xfId="1142" xr:uid="{00000000-0005-0000-0000-00009D040000}"/>
-    <cellStyle name="40% - Énfasis6 21" xfId="324" xr:uid="{00000000-0005-0000-0000-00009E040000}"/>
-    <cellStyle name="40% - Énfasis6 21 2" xfId="619" xr:uid="{00000000-0005-0000-0000-00009F040000}"/>
-    <cellStyle name="40% - Énfasis6 21 2 2" xfId="1145" xr:uid="{00000000-0005-0000-0000-0000A0040000}"/>
-    <cellStyle name="40% - Énfasis6 21 3" xfId="1144" xr:uid="{00000000-0005-0000-0000-0000A1040000}"/>
-    <cellStyle name="40% - Énfasis6 22" xfId="633" xr:uid="{00000000-0005-0000-0000-0000A2040000}"/>
-    <cellStyle name="40% - Énfasis6 22 2" xfId="1147" xr:uid="{00000000-0005-0000-0000-0000A3040000}"/>
-    <cellStyle name="40% - Énfasis6 22 3" xfId="1146" xr:uid="{00000000-0005-0000-0000-0000A4040000}"/>
-    <cellStyle name="40% - Énfasis6 23" xfId="337" xr:uid="{00000000-0005-0000-0000-0000A5040000}"/>
-    <cellStyle name="40% - Énfasis6 23 2" xfId="1148" xr:uid="{00000000-0005-0000-0000-0000A6040000}"/>
-    <cellStyle name="40% - Énfasis6 24" xfId="1119" xr:uid="{00000000-0005-0000-0000-0000A7040000}"/>
-    <cellStyle name="40% - Énfasis6 25" xfId="1277" xr:uid="{00000000-0005-0000-0000-0000A8040000}"/>
-    <cellStyle name="40% - Énfasis6 26" xfId="1291" xr:uid="{00000000-0005-0000-0000-0000A9040000}"/>
-    <cellStyle name="40% - Énfasis6 27" xfId="1305" xr:uid="{00000000-0005-0000-0000-0000AA040000}"/>
-    <cellStyle name="40% - Énfasis6 28" xfId="1319" xr:uid="{00000000-0005-0000-0000-0000AB040000}"/>
-    <cellStyle name="40% - Énfasis6 29" xfId="1333" xr:uid="{00000000-0005-0000-0000-0000AC040000}"/>
-    <cellStyle name="40% - Énfasis6 3" xfId="72" xr:uid="{00000000-0005-0000-0000-0000AD040000}"/>
-    <cellStyle name="40% - Énfasis6 3 2" xfId="367" xr:uid="{00000000-0005-0000-0000-0000AE040000}"/>
-    <cellStyle name="40% - Énfasis6 3 2 2" xfId="1150" xr:uid="{00000000-0005-0000-0000-0000AF040000}"/>
-    <cellStyle name="40% - Énfasis6 3 3" xfId="1149" xr:uid="{00000000-0005-0000-0000-0000B0040000}"/>
-    <cellStyle name="40% - Énfasis6 30" xfId="1347" xr:uid="{00000000-0005-0000-0000-0000B1040000}"/>
-    <cellStyle name="40% - Énfasis6 31" xfId="1361" xr:uid="{00000000-0005-0000-0000-0000B2040000}"/>
-    <cellStyle name="40% - Énfasis6 32" xfId="1375" xr:uid="{00000000-0005-0000-0000-0000B3040000}"/>
-    <cellStyle name="40% - Énfasis6 33" xfId="1389" xr:uid="{00000000-0005-0000-0000-0000B4040000}"/>
-    <cellStyle name="40% - Énfasis6 34" xfId="1403" xr:uid="{00000000-0005-0000-0000-0000B5040000}"/>
-    <cellStyle name="40% - Énfasis6 35" xfId="1417" xr:uid="{00000000-0005-0000-0000-0000B6040000}"/>
-    <cellStyle name="40% - Énfasis6 36" xfId="1431" xr:uid="{00000000-0005-0000-0000-0000B7040000}"/>
-    <cellStyle name="40% - Énfasis6 37" xfId="1445" xr:uid="{00000000-0005-0000-0000-0000B8040000}"/>
-    <cellStyle name="40% - Énfasis6 38" xfId="1459" xr:uid="{00000000-0005-0000-0000-0000B9040000}"/>
-    <cellStyle name="40% - Énfasis6 39" xfId="1473" xr:uid="{00000000-0005-0000-0000-0000BA040000}"/>
-    <cellStyle name="40% - Énfasis6 4" xfId="86" xr:uid="{00000000-0005-0000-0000-0000BB040000}"/>
-    <cellStyle name="40% - Énfasis6 4 2" xfId="381" xr:uid="{00000000-0005-0000-0000-0000BC040000}"/>
-    <cellStyle name="40% - Énfasis6 4 2 2" xfId="1152" xr:uid="{00000000-0005-0000-0000-0000BD040000}"/>
-    <cellStyle name="40% - Énfasis6 4 3" xfId="1151" xr:uid="{00000000-0005-0000-0000-0000BE040000}"/>
-    <cellStyle name="40% - Énfasis6 40" xfId="1488" xr:uid="{00000000-0005-0000-0000-0000BF040000}"/>
-    <cellStyle name="40% - Énfasis6 5" xfId="100" xr:uid="{00000000-0005-0000-0000-0000C0040000}"/>
-    <cellStyle name="40% - Énfasis6 5 2" xfId="395" xr:uid="{00000000-0005-0000-0000-0000C1040000}"/>
-    <cellStyle name="40% - Énfasis6 5 2 2" xfId="1154" xr:uid="{00000000-0005-0000-0000-0000C2040000}"/>
-    <cellStyle name="40% - Énfasis6 5 3" xfId="1153" xr:uid="{00000000-0005-0000-0000-0000C3040000}"/>
-    <cellStyle name="40% - Énfasis6 6" xfId="114" xr:uid="{00000000-0005-0000-0000-0000C4040000}"/>
-    <cellStyle name="40% - Énfasis6 6 2" xfId="409" xr:uid="{00000000-0005-0000-0000-0000C5040000}"/>
-    <cellStyle name="40% - Énfasis6 6 2 2" xfId="1156" xr:uid="{00000000-0005-0000-0000-0000C6040000}"/>
-    <cellStyle name="40% - Énfasis6 6 3" xfId="1155" xr:uid="{00000000-0005-0000-0000-0000C7040000}"/>
-    <cellStyle name="40% - Énfasis6 7" xfId="128" xr:uid="{00000000-0005-0000-0000-0000C8040000}"/>
-    <cellStyle name="40% - Énfasis6 7 2" xfId="423" xr:uid="{00000000-0005-0000-0000-0000C9040000}"/>
-    <cellStyle name="40% - Énfasis6 7 2 2" xfId="1158" xr:uid="{00000000-0005-0000-0000-0000CA040000}"/>
-    <cellStyle name="40% - Énfasis6 7 3" xfId="1157" xr:uid="{00000000-0005-0000-0000-0000CB040000}"/>
-    <cellStyle name="40% - Énfasis6 8" xfId="142" xr:uid="{00000000-0005-0000-0000-0000CC040000}"/>
-    <cellStyle name="40% - Énfasis6 8 2" xfId="437" xr:uid="{00000000-0005-0000-0000-0000CD040000}"/>
-    <cellStyle name="40% - Énfasis6 8 2 2" xfId="1160" xr:uid="{00000000-0005-0000-0000-0000CE040000}"/>
-    <cellStyle name="40% - Énfasis6 8 3" xfId="1159" xr:uid="{00000000-0005-0000-0000-0000CF040000}"/>
-    <cellStyle name="40% - Énfasis6 9" xfId="156" xr:uid="{00000000-0005-0000-0000-0000D0040000}"/>
-    <cellStyle name="40% - Énfasis6 9 2" xfId="451" xr:uid="{00000000-0005-0000-0000-0000D1040000}"/>
-    <cellStyle name="40% - Énfasis6 9 2 2" xfId="1162" xr:uid="{00000000-0005-0000-0000-0000D2040000}"/>
-    <cellStyle name="40% - Énfasis6 9 3" xfId="1161" xr:uid="{00000000-0005-0000-0000-0000D3040000}"/>
+    <cellStyle name="40% - Énfasis6 10" xfId="170"/>
+    <cellStyle name="40% - Énfasis6 10 2" xfId="465"/>
+    <cellStyle name="40% - Énfasis6 10 2 2" xfId="1121"/>
+    <cellStyle name="40% - Énfasis6 10 3" xfId="1120"/>
+    <cellStyle name="40% - Énfasis6 11" xfId="184"/>
+    <cellStyle name="40% - Énfasis6 11 2" xfId="479"/>
+    <cellStyle name="40% - Énfasis6 11 2 2" xfId="1123"/>
+    <cellStyle name="40% - Énfasis6 11 3" xfId="1122"/>
+    <cellStyle name="40% - Énfasis6 12" xfId="198"/>
+    <cellStyle name="40% - Énfasis6 12 2" xfId="493"/>
+    <cellStyle name="40% - Énfasis6 12 2 2" xfId="1125"/>
+    <cellStyle name="40% - Énfasis6 12 3" xfId="1124"/>
+    <cellStyle name="40% - Énfasis6 13" xfId="212"/>
+    <cellStyle name="40% - Énfasis6 13 2" xfId="507"/>
+    <cellStyle name="40% - Énfasis6 13 2 2" xfId="1127"/>
+    <cellStyle name="40% - Énfasis6 13 3" xfId="1126"/>
+    <cellStyle name="40% - Énfasis6 14" xfId="226"/>
+    <cellStyle name="40% - Énfasis6 14 2" xfId="521"/>
+    <cellStyle name="40% - Énfasis6 14 2 2" xfId="1129"/>
+    <cellStyle name="40% - Énfasis6 14 3" xfId="1128"/>
+    <cellStyle name="40% - Énfasis6 15" xfId="240"/>
+    <cellStyle name="40% - Énfasis6 15 2" xfId="535"/>
+    <cellStyle name="40% - Énfasis6 15 2 2" xfId="1131"/>
+    <cellStyle name="40% - Énfasis6 15 3" xfId="1130"/>
+    <cellStyle name="40% - Énfasis6 16" xfId="254"/>
+    <cellStyle name="40% - Énfasis6 16 2" xfId="549"/>
+    <cellStyle name="40% - Énfasis6 16 2 2" xfId="1133"/>
+    <cellStyle name="40% - Énfasis6 16 3" xfId="1132"/>
+    <cellStyle name="40% - Énfasis6 17" xfId="268"/>
+    <cellStyle name="40% - Énfasis6 17 2" xfId="563"/>
+    <cellStyle name="40% - Énfasis6 17 2 2" xfId="1135"/>
+    <cellStyle name="40% - Énfasis6 17 3" xfId="1134"/>
+    <cellStyle name="40% - Énfasis6 18" xfId="282"/>
+    <cellStyle name="40% - Énfasis6 18 2" xfId="577"/>
+    <cellStyle name="40% - Énfasis6 18 2 2" xfId="1137"/>
+    <cellStyle name="40% - Énfasis6 18 3" xfId="1136"/>
+    <cellStyle name="40% - Énfasis6 19" xfId="296"/>
+    <cellStyle name="40% - Énfasis6 19 2" xfId="591"/>
+    <cellStyle name="40% - Énfasis6 19 2 2" xfId="1139"/>
+    <cellStyle name="40% - Énfasis6 19 3" xfId="1138"/>
+    <cellStyle name="40% - Énfasis6 2" xfId="58"/>
+    <cellStyle name="40% - Énfasis6 2 2" xfId="353"/>
+    <cellStyle name="40% - Énfasis6 2 2 2" xfId="1141"/>
+    <cellStyle name="40% - Énfasis6 2 3" xfId="1140"/>
+    <cellStyle name="40% - Énfasis6 20" xfId="310"/>
+    <cellStyle name="40% - Énfasis6 20 2" xfId="605"/>
+    <cellStyle name="40% - Énfasis6 20 2 2" xfId="1143"/>
+    <cellStyle name="40% - Énfasis6 20 3" xfId="1142"/>
+    <cellStyle name="40% - Énfasis6 21" xfId="324"/>
+    <cellStyle name="40% - Énfasis6 21 2" xfId="619"/>
+    <cellStyle name="40% - Énfasis6 21 2 2" xfId="1145"/>
+    <cellStyle name="40% - Énfasis6 21 3" xfId="1144"/>
+    <cellStyle name="40% - Énfasis6 22" xfId="633"/>
+    <cellStyle name="40% - Énfasis6 22 2" xfId="1147"/>
+    <cellStyle name="40% - Énfasis6 22 3" xfId="1146"/>
+    <cellStyle name="40% - Énfasis6 23" xfId="337"/>
+    <cellStyle name="40% - Énfasis6 23 2" xfId="1148"/>
+    <cellStyle name="40% - Énfasis6 24" xfId="1119"/>
+    <cellStyle name="40% - Énfasis6 25" xfId="1277"/>
+    <cellStyle name="40% - Énfasis6 26" xfId="1291"/>
+    <cellStyle name="40% - Énfasis6 27" xfId="1305"/>
+    <cellStyle name="40% - Énfasis6 28" xfId="1319"/>
+    <cellStyle name="40% - Énfasis6 29" xfId="1333"/>
+    <cellStyle name="40% - Énfasis6 3" xfId="72"/>
+    <cellStyle name="40% - Énfasis6 3 2" xfId="367"/>
+    <cellStyle name="40% - Énfasis6 3 2 2" xfId="1150"/>
+    <cellStyle name="40% - Énfasis6 3 3" xfId="1149"/>
+    <cellStyle name="40% - Énfasis6 30" xfId="1347"/>
+    <cellStyle name="40% - Énfasis6 31" xfId="1361"/>
+    <cellStyle name="40% - Énfasis6 32" xfId="1375"/>
+    <cellStyle name="40% - Énfasis6 33" xfId="1389"/>
+    <cellStyle name="40% - Énfasis6 34" xfId="1403"/>
+    <cellStyle name="40% - Énfasis6 35" xfId="1417"/>
+    <cellStyle name="40% - Énfasis6 36" xfId="1431"/>
+    <cellStyle name="40% - Énfasis6 37" xfId="1445"/>
+    <cellStyle name="40% - Énfasis6 38" xfId="1459"/>
+    <cellStyle name="40% - Énfasis6 39" xfId="1473"/>
+    <cellStyle name="40% - Énfasis6 4" xfId="86"/>
+    <cellStyle name="40% - Énfasis6 4 2" xfId="381"/>
+    <cellStyle name="40% - Énfasis6 4 2 2" xfId="1152"/>
+    <cellStyle name="40% - Énfasis6 4 3" xfId="1151"/>
+    <cellStyle name="40% - Énfasis6 40" xfId="1488"/>
+    <cellStyle name="40% - Énfasis6 5" xfId="100"/>
+    <cellStyle name="40% - Énfasis6 5 2" xfId="395"/>
+    <cellStyle name="40% - Énfasis6 5 2 2" xfId="1154"/>
+    <cellStyle name="40% - Énfasis6 5 3" xfId="1153"/>
+    <cellStyle name="40% - Énfasis6 6" xfId="114"/>
+    <cellStyle name="40% - Énfasis6 6 2" xfId="409"/>
+    <cellStyle name="40% - Énfasis6 6 2 2" xfId="1156"/>
+    <cellStyle name="40% - Énfasis6 6 3" xfId="1155"/>
+    <cellStyle name="40% - Énfasis6 7" xfId="128"/>
+    <cellStyle name="40% - Énfasis6 7 2" xfId="423"/>
+    <cellStyle name="40% - Énfasis6 7 2 2" xfId="1158"/>
+    <cellStyle name="40% - Énfasis6 7 3" xfId="1157"/>
+    <cellStyle name="40% - Énfasis6 8" xfId="142"/>
+    <cellStyle name="40% - Énfasis6 8 2" xfId="437"/>
+    <cellStyle name="40% - Énfasis6 8 2 2" xfId="1160"/>
+    <cellStyle name="40% - Énfasis6 8 3" xfId="1159"/>
+    <cellStyle name="40% - Énfasis6 9" xfId="156"/>
+    <cellStyle name="40% - Énfasis6 9 2" xfId="451"/>
+    <cellStyle name="40% - Énfasis6 9 2 2" xfId="1162"/>
+    <cellStyle name="40% - Énfasis6 9 3" xfId="1161"/>
     <cellStyle name="60% - Énfasis1" xfId="22" builtinId="32" customBuiltin="1"/>
     <cellStyle name="60% - Énfasis2" xfId="26" builtinId="36" customBuiltin="1"/>
     <cellStyle name="60% - Énfasis3" xfId="30" builtinId="40" customBuiltin="1"/>
@@ -4204,8 +4216,8 @@
     <cellStyle name="60% - Énfasis6" xfId="42" builtinId="52" customBuiltin="1"/>
     <cellStyle name="Bueno" xfId="8" builtinId="26" customBuiltin="1"/>
     <cellStyle name="Cálculo" xfId="13" builtinId="22" customBuiltin="1"/>
-    <cellStyle name="Cálculo 2" xfId="1163" xr:uid="{00000000-0005-0000-0000-0000DC040000}"/>
-    <cellStyle name="Cálculo 3" xfId="1164" xr:uid="{00000000-0005-0000-0000-0000DD040000}"/>
+    <cellStyle name="Cálculo 2" xfId="1163"/>
+    <cellStyle name="Cálculo 3" xfId="1164"/>
     <cellStyle name="Celda de comprobación" xfId="15" builtinId="23" customBuiltin="1"/>
     <cellStyle name="Celda vinculada" xfId="14" builtinId="24" customBuiltin="1"/>
     <cellStyle name="Encabezado 1" xfId="4" builtinId="16" customBuiltin="1"/>
@@ -4220,234 +4232,234 @@
     <cellStyle name="Incorrecto" xfId="9" builtinId="27" customBuiltin="1"/>
     <cellStyle name="Neutral" xfId="10" builtinId="28" customBuiltin="1"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 10" xfId="129" xr:uid="{00000000-0005-0000-0000-0000EC040000}"/>
-    <cellStyle name="Normal 10 2" xfId="424" xr:uid="{00000000-0005-0000-0000-0000ED040000}"/>
-    <cellStyle name="Normal 10 2 2" xfId="1166" xr:uid="{00000000-0005-0000-0000-0000EE040000}"/>
-    <cellStyle name="Normal 10 3" xfId="1165" xr:uid="{00000000-0005-0000-0000-0000EF040000}"/>
-    <cellStyle name="Normal 11" xfId="143" xr:uid="{00000000-0005-0000-0000-0000F0040000}"/>
-    <cellStyle name="Normal 11 2" xfId="438" xr:uid="{00000000-0005-0000-0000-0000F1040000}"/>
-    <cellStyle name="Normal 11 2 2" xfId="1168" xr:uid="{00000000-0005-0000-0000-0000F2040000}"/>
-    <cellStyle name="Normal 11 3" xfId="1167" xr:uid="{00000000-0005-0000-0000-0000F3040000}"/>
-    <cellStyle name="Normal 12" xfId="157" xr:uid="{00000000-0005-0000-0000-0000F4040000}"/>
-    <cellStyle name="Normal 12 2" xfId="452" xr:uid="{00000000-0005-0000-0000-0000F5040000}"/>
-    <cellStyle name="Normal 12 2 2" xfId="1170" xr:uid="{00000000-0005-0000-0000-0000F6040000}"/>
-    <cellStyle name="Normal 12 3" xfId="1169" xr:uid="{00000000-0005-0000-0000-0000F7040000}"/>
-    <cellStyle name="Normal 13" xfId="171" xr:uid="{00000000-0005-0000-0000-0000F8040000}"/>
-    <cellStyle name="Normal 13 2" xfId="466" xr:uid="{00000000-0005-0000-0000-0000F9040000}"/>
-    <cellStyle name="Normal 13 2 2" xfId="1172" xr:uid="{00000000-0005-0000-0000-0000FA040000}"/>
-    <cellStyle name="Normal 13 3" xfId="1171" xr:uid="{00000000-0005-0000-0000-0000FB040000}"/>
-    <cellStyle name="Normal 14" xfId="185" xr:uid="{00000000-0005-0000-0000-0000FC040000}"/>
-    <cellStyle name="Normal 14 2" xfId="480" xr:uid="{00000000-0005-0000-0000-0000FD040000}"/>
-    <cellStyle name="Normal 14 2 2" xfId="1174" xr:uid="{00000000-0005-0000-0000-0000FE040000}"/>
-    <cellStyle name="Normal 14 3" xfId="1173" xr:uid="{00000000-0005-0000-0000-0000FF040000}"/>
-    <cellStyle name="Normal 15" xfId="199" xr:uid="{00000000-0005-0000-0000-000000050000}"/>
-    <cellStyle name="Normal 15 2" xfId="494" xr:uid="{00000000-0005-0000-0000-000001050000}"/>
-    <cellStyle name="Normal 15 2 2" xfId="1176" xr:uid="{00000000-0005-0000-0000-000002050000}"/>
-    <cellStyle name="Normal 15 3" xfId="1175" xr:uid="{00000000-0005-0000-0000-000003050000}"/>
-    <cellStyle name="Normal 16" xfId="213" xr:uid="{00000000-0005-0000-0000-000004050000}"/>
-    <cellStyle name="Normal 16 2" xfId="508" xr:uid="{00000000-0005-0000-0000-000005050000}"/>
-    <cellStyle name="Normal 16 2 2" xfId="1178" xr:uid="{00000000-0005-0000-0000-000006050000}"/>
-    <cellStyle name="Normal 16 3" xfId="1177" xr:uid="{00000000-0005-0000-0000-000007050000}"/>
-    <cellStyle name="Normal 17" xfId="227" xr:uid="{00000000-0005-0000-0000-000008050000}"/>
-    <cellStyle name="Normal 17 2" xfId="522" xr:uid="{00000000-0005-0000-0000-000009050000}"/>
-    <cellStyle name="Normal 17 2 2" xfId="1180" xr:uid="{00000000-0005-0000-0000-00000A050000}"/>
-    <cellStyle name="Normal 17 3" xfId="1179" xr:uid="{00000000-0005-0000-0000-00000B050000}"/>
-    <cellStyle name="Normal 18" xfId="241" xr:uid="{00000000-0005-0000-0000-00000C050000}"/>
-    <cellStyle name="Normal 18 2" xfId="536" xr:uid="{00000000-0005-0000-0000-00000D050000}"/>
-    <cellStyle name="Normal 18 2 2" xfId="1182" xr:uid="{00000000-0005-0000-0000-00000E050000}"/>
-    <cellStyle name="Normal 18 3" xfId="1181" xr:uid="{00000000-0005-0000-0000-00000F050000}"/>
-    <cellStyle name="Normal 19" xfId="255" xr:uid="{00000000-0005-0000-0000-000010050000}"/>
-    <cellStyle name="Normal 19 2" xfId="550" xr:uid="{00000000-0005-0000-0000-000011050000}"/>
-    <cellStyle name="Normal 19 2 2" xfId="1184" xr:uid="{00000000-0005-0000-0000-000012050000}"/>
-    <cellStyle name="Normal 19 3" xfId="1183" xr:uid="{00000000-0005-0000-0000-000013050000}"/>
-    <cellStyle name="Normal 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000014050000}"/>
-    <cellStyle name="Normal 2 2" xfId="325" xr:uid="{00000000-0005-0000-0000-000015050000}"/>
-    <cellStyle name="Normal 2 2 2" xfId="1186" xr:uid="{00000000-0005-0000-0000-000016050000}"/>
-    <cellStyle name="Normal 2 3" xfId="2" xr:uid="{00000000-0005-0000-0000-000017050000}"/>
-    <cellStyle name="Normal 2 4" xfId="1187" xr:uid="{00000000-0005-0000-0000-000018050000}"/>
-    <cellStyle name="Normal 2 5" xfId="1185" xr:uid="{00000000-0005-0000-0000-000019050000}"/>
-    <cellStyle name="Normal 20" xfId="269" xr:uid="{00000000-0005-0000-0000-00001A050000}"/>
-    <cellStyle name="Normal 20 2" xfId="564" xr:uid="{00000000-0005-0000-0000-00001B050000}"/>
-    <cellStyle name="Normal 20 2 2" xfId="1189" xr:uid="{00000000-0005-0000-0000-00001C050000}"/>
-    <cellStyle name="Normal 20 3" xfId="1188" xr:uid="{00000000-0005-0000-0000-00001D050000}"/>
-    <cellStyle name="Normal 21" xfId="283" xr:uid="{00000000-0005-0000-0000-00001E050000}"/>
-    <cellStyle name="Normal 21 2" xfId="578" xr:uid="{00000000-0005-0000-0000-00001F050000}"/>
-    <cellStyle name="Normal 21 2 2" xfId="1191" xr:uid="{00000000-0005-0000-0000-000020050000}"/>
-    <cellStyle name="Normal 21 3" xfId="1190" xr:uid="{00000000-0005-0000-0000-000021050000}"/>
-    <cellStyle name="Normal 22" xfId="297" xr:uid="{00000000-0005-0000-0000-000022050000}"/>
-    <cellStyle name="Normal 22 2" xfId="592" xr:uid="{00000000-0005-0000-0000-000023050000}"/>
-    <cellStyle name="Normal 22 2 2" xfId="1193" xr:uid="{00000000-0005-0000-0000-000024050000}"/>
-    <cellStyle name="Normal 22 3" xfId="1192" xr:uid="{00000000-0005-0000-0000-000025050000}"/>
-    <cellStyle name="Normal 23" xfId="311" xr:uid="{00000000-0005-0000-0000-000026050000}"/>
-    <cellStyle name="Normal 23 2" xfId="606" xr:uid="{00000000-0005-0000-0000-000027050000}"/>
-    <cellStyle name="Normal 23 2 2" xfId="1195" xr:uid="{00000000-0005-0000-0000-000028050000}"/>
-    <cellStyle name="Normal 23 3" xfId="1194" xr:uid="{00000000-0005-0000-0000-000029050000}"/>
-    <cellStyle name="Normal 24" xfId="620" xr:uid="{00000000-0005-0000-0000-00002A050000}"/>
-    <cellStyle name="Normal 24 2" xfId="1197" xr:uid="{00000000-0005-0000-0000-00002B050000}"/>
-    <cellStyle name="Normal 24 3" xfId="1198" xr:uid="{00000000-0005-0000-0000-00002C050000}"/>
-    <cellStyle name="Normal 24 4" xfId="1196" xr:uid="{00000000-0005-0000-0000-00002D050000}"/>
-    <cellStyle name="Normal 25" xfId="1199" xr:uid="{00000000-0005-0000-0000-00002E050000}"/>
-    <cellStyle name="Normal 26" xfId="1200" xr:uid="{00000000-0005-0000-0000-00002F050000}"/>
-    <cellStyle name="Normal 26 2" xfId="1201" xr:uid="{00000000-0005-0000-0000-000030050000}"/>
-    <cellStyle name="Normal 27" xfId="1202" xr:uid="{00000000-0005-0000-0000-000031050000}"/>
-    <cellStyle name="Normal 28" xfId="634" xr:uid="{00000000-0005-0000-0000-000032050000}"/>
-    <cellStyle name="Normal 29" xfId="1264" xr:uid="{00000000-0005-0000-0000-000033050000}"/>
-    <cellStyle name="Normal 3" xfId="43" xr:uid="{00000000-0005-0000-0000-000034050000}"/>
-    <cellStyle name="Normal 3 2" xfId="338" xr:uid="{00000000-0005-0000-0000-000035050000}"/>
-    <cellStyle name="Normal 3 2 2" xfId="1204" xr:uid="{00000000-0005-0000-0000-000036050000}"/>
-    <cellStyle name="Normal 3 3" xfId="1203" xr:uid="{00000000-0005-0000-0000-000037050000}"/>
-    <cellStyle name="Normal 30" xfId="1278" xr:uid="{00000000-0005-0000-0000-000038050000}"/>
-    <cellStyle name="Normal 31" xfId="1292" xr:uid="{00000000-0005-0000-0000-000039050000}"/>
-    <cellStyle name="Normal 32" xfId="1306" xr:uid="{00000000-0005-0000-0000-00003A050000}"/>
-    <cellStyle name="Normal 33" xfId="1320" xr:uid="{00000000-0005-0000-0000-00003B050000}"/>
-    <cellStyle name="Normal 34" xfId="1334" xr:uid="{00000000-0005-0000-0000-00003C050000}"/>
-    <cellStyle name="Normal 35" xfId="1348" xr:uid="{00000000-0005-0000-0000-00003D050000}"/>
-    <cellStyle name="Normal 36" xfId="1362" xr:uid="{00000000-0005-0000-0000-00003E050000}"/>
-    <cellStyle name="Normal 37" xfId="1376" xr:uid="{00000000-0005-0000-0000-00003F050000}"/>
-    <cellStyle name="Normal 38" xfId="1390" xr:uid="{00000000-0005-0000-0000-000040050000}"/>
-    <cellStyle name="Normal 39" xfId="1404" xr:uid="{00000000-0005-0000-0000-000041050000}"/>
-    <cellStyle name="Normal 4" xfId="45" xr:uid="{00000000-0005-0000-0000-000042050000}"/>
-    <cellStyle name="Normal 4 2" xfId="340" xr:uid="{00000000-0005-0000-0000-000043050000}"/>
-    <cellStyle name="Normal 4 2 2" xfId="1206" xr:uid="{00000000-0005-0000-0000-000044050000}"/>
-    <cellStyle name="Normal 4 3" xfId="1207" xr:uid="{00000000-0005-0000-0000-000045050000}"/>
-    <cellStyle name="Normal 4 4" xfId="1205" xr:uid="{00000000-0005-0000-0000-000046050000}"/>
-    <cellStyle name="Normal 40" xfId="1418" xr:uid="{00000000-0005-0000-0000-000047050000}"/>
-    <cellStyle name="Normal 41" xfId="1432" xr:uid="{00000000-0005-0000-0000-000048050000}"/>
-    <cellStyle name="Normal 42" xfId="1446" xr:uid="{00000000-0005-0000-0000-000049050000}"/>
-    <cellStyle name="Normal 43" xfId="1460" xr:uid="{00000000-0005-0000-0000-00004A050000}"/>
-    <cellStyle name="Normal 44" xfId="1474" xr:uid="{00000000-0005-0000-0000-00004B050000}"/>
-    <cellStyle name="Normal 5" xfId="59" xr:uid="{00000000-0005-0000-0000-00004C050000}"/>
-    <cellStyle name="Normal 5 2" xfId="354" xr:uid="{00000000-0005-0000-0000-00004D050000}"/>
-    <cellStyle name="Normal 5 2 2" xfId="1209" xr:uid="{00000000-0005-0000-0000-00004E050000}"/>
-    <cellStyle name="Normal 5 3" xfId="1208" xr:uid="{00000000-0005-0000-0000-00004F050000}"/>
-    <cellStyle name="Normal 6" xfId="73" xr:uid="{00000000-0005-0000-0000-000050050000}"/>
-    <cellStyle name="Normal 6 2" xfId="368" xr:uid="{00000000-0005-0000-0000-000051050000}"/>
-    <cellStyle name="Normal 6 2 2" xfId="1211" xr:uid="{00000000-0005-0000-0000-000052050000}"/>
-    <cellStyle name="Normal 6 3" xfId="1210" xr:uid="{00000000-0005-0000-0000-000053050000}"/>
-    <cellStyle name="Normal 7" xfId="87" xr:uid="{00000000-0005-0000-0000-000054050000}"/>
-    <cellStyle name="Normal 7 2" xfId="382" xr:uid="{00000000-0005-0000-0000-000055050000}"/>
-    <cellStyle name="Normal 7 2 2" xfId="1213" xr:uid="{00000000-0005-0000-0000-000056050000}"/>
-    <cellStyle name="Normal 7 3" xfId="1212" xr:uid="{00000000-0005-0000-0000-000057050000}"/>
-    <cellStyle name="Normal 8" xfId="101" xr:uid="{00000000-0005-0000-0000-000058050000}"/>
-    <cellStyle name="Normal 8 2" xfId="396" xr:uid="{00000000-0005-0000-0000-000059050000}"/>
-    <cellStyle name="Normal 8 2 2" xfId="1215" xr:uid="{00000000-0005-0000-0000-00005A050000}"/>
-    <cellStyle name="Normal 8 3" xfId="1214" xr:uid="{00000000-0005-0000-0000-00005B050000}"/>
-    <cellStyle name="Normal 9" xfId="115" xr:uid="{00000000-0005-0000-0000-00005C050000}"/>
-    <cellStyle name="Normal 9 2" xfId="410" xr:uid="{00000000-0005-0000-0000-00005D050000}"/>
-    <cellStyle name="Normal 9 2 2" xfId="1217" xr:uid="{00000000-0005-0000-0000-00005E050000}"/>
-    <cellStyle name="Normal 9 3" xfId="1216" xr:uid="{00000000-0005-0000-0000-00005F050000}"/>
-    <cellStyle name="Notas 10" xfId="144" xr:uid="{00000000-0005-0000-0000-000060050000}"/>
-    <cellStyle name="Notas 10 2" xfId="439" xr:uid="{00000000-0005-0000-0000-000061050000}"/>
-    <cellStyle name="Notas 10 2 2" xfId="1220" xr:uid="{00000000-0005-0000-0000-000062050000}"/>
-    <cellStyle name="Notas 10 3" xfId="1219" xr:uid="{00000000-0005-0000-0000-000063050000}"/>
-    <cellStyle name="Notas 11" xfId="158" xr:uid="{00000000-0005-0000-0000-000064050000}"/>
-    <cellStyle name="Notas 11 2" xfId="453" xr:uid="{00000000-0005-0000-0000-000065050000}"/>
-    <cellStyle name="Notas 11 2 2" xfId="1222" xr:uid="{00000000-0005-0000-0000-000066050000}"/>
-    <cellStyle name="Notas 11 3" xfId="1221" xr:uid="{00000000-0005-0000-0000-000067050000}"/>
-    <cellStyle name="Notas 12" xfId="172" xr:uid="{00000000-0005-0000-0000-000068050000}"/>
-    <cellStyle name="Notas 12 2" xfId="467" xr:uid="{00000000-0005-0000-0000-000069050000}"/>
-    <cellStyle name="Notas 12 2 2" xfId="1224" xr:uid="{00000000-0005-0000-0000-00006A050000}"/>
-    <cellStyle name="Notas 12 3" xfId="1223" xr:uid="{00000000-0005-0000-0000-00006B050000}"/>
-    <cellStyle name="Notas 13" xfId="186" xr:uid="{00000000-0005-0000-0000-00006C050000}"/>
-    <cellStyle name="Notas 13 2" xfId="481" xr:uid="{00000000-0005-0000-0000-00006D050000}"/>
-    <cellStyle name="Notas 13 2 2" xfId="1226" xr:uid="{00000000-0005-0000-0000-00006E050000}"/>
-    <cellStyle name="Notas 13 3" xfId="1225" xr:uid="{00000000-0005-0000-0000-00006F050000}"/>
-    <cellStyle name="Notas 14" xfId="200" xr:uid="{00000000-0005-0000-0000-000070050000}"/>
-    <cellStyle name="Notas 14 2" xfId="495" xr:uid="{00000000-0005-0000-0000-000071050000}"/>
-    <cellStyle name="Notas 14 2 2" xfId="1228" xr:uid="{00000000-0005-0000-0000-000072050000}"/>
-    <cellStyle name="Notas 14 3" xfId="1227" xr:uid="{00000000-0005-0000-0000-000073050000}"/>
-    <cellStyle name="Notas 15" xfId="214" xr:uid="{00000000-0005-0000-0000-000074050000}"/>
-    <cellStyle name="Notas 15 2" xfId="509" xr:uid="{00000000-0005-0000-0000-000075050000}"/>
-    <cellStyle name="Notas 15 2 2" xfId="1230" xr:uid="{00000000-0005-0000-0000-000076050000}"/>
-    <cellStyle name="Notas 15 3" xfId="1229" xr:uid="{00000000-0005-0000-0000-000077050000}"/>
-    <cellStyle name="Notas 16" xfId="228" xr:uid="{00000000-0005-0000-0000-000078050000}"/>
-    <cellStyle name="Notas 16 2" xfId="523" xr:uid="{00000000-0005-0000-0000-000079050000}"/>
-    <cellStyle name="Notas 16 2 2" xfId="1232" xr:uid="{00000000-0005-0000-0000-00007A050000}"/>
-    <cellStyle name="Notas 16 3" xfId="1231" xr:uid="{00000000-0005-0000-0000-00007B050000}"/>
-    <cellStyle name="Notas 17" xfId="242" xr:uid="{00000000-0005-0000-0000-00007C050000}"/>
-    <cellStyle name="Notas 17 2" xfId="537" xr:uid="{00000000-0005-0000-0000-00007D050000}"/>
-    <cellStyle name="Notas 17 2 2" xfId="1234" xr:uid="{00000000-0005-0000-0000-00007E050000}"/>
-    <cellStyle name="Notas 17 3" xfId="1233" xr:uid="{00000000-0005-0000-0000-00007F050000}"/>
-    <cellStyle name="Notas 18" xfId="256" xr:uid="{00000000-0005-0000-0000-000080050000}"/>
-    <cellStyle name="Notas 18 2" xfId="551" xr:uid="{00000000-0005-0000-0000-000081050000}"/>
-    <cellStyle name="Notas 18 2 2" xfId="1236" xr:uid="{00000000-0005-0000-0000-000082050000}"/>
-    <cellStyle name="Notas 18 3" xfId="1235" xr:uid="{00000000-0005-0000-0000-000083050000}"/>
-    <cellStyle name="Notas 19" xfId="270" xr:uid="{00000000-0005-0000-0000-000084050000}"/>
-    <cellStyle name="Notas 19 2" xfId="565" xr:uid="{00000000-0005-0000-0000-000085050000}"/>
-    <cellStyle name="Notas 19 2 2" xfId="1238" xr:uid="{00000000-0005-0000-0000-000086050000}"/>
-    <cellStyle name="Notas 19 3" xfId="1237" xr:uid="{00000000-0005-0000-0000-000087050000}"/>
-    <cellStyle name="Notas 2" xfId="44" xr:uid="{00000000-0005-0000-0000-000088050000}"/>
-    <cellStyle name="Notas 2 2" xfId="339" xr:uid="{00000000-0005-0000-0000-000089050000}"/>
-    <cellStyle name="Notas 2 2 2" xfId="1240" xr:uid="{00000000-0005-0000-0000-00008A050000}"/>
-    <cellStyle name="Notas 2 3" xfId="1239" xr:uid="{00000000-0005-0000-0000-00008B050000}"/>
-    <cellStyle name="Notas 20" xfId="284" xr:uid="{00000000-0005-0000-0000-00008C050000}"/>
-    <cellStyle name="Notas 20 2" xfId="579" xr:uid="{00000000-0005-0000-0000-00008D050000}"/>
-    <cellStyle name="Notas 20 2 2" xfId="1242" xr:uid="{00000000-0005-0000-0000-00008E050000}"/>
-    <cellStyle name="Notas 20 3" xfId="1241" xr:uid="{00000000-0005-0000-0000-00008F050000}"/>
-    <cellStyle name="Notas 21" xfId="298" xr:uid="{00000000-0005-0000-0000-000090050000}"/>
-    <cellStyle name="Notas 21 2" xfId="593" xr:uid="{00000000-0005-0000-0000-000091050000}"/>
-    <cellStyle name="Notas 21 2 2" xfId="1244" xr:uid="{00000000-0005-0000-0000-000092050000}"/>
-    <cellStyle name="Notas 21 3" xfId="1243" xr:uid="{00000000-0005-0000-0000-000093050000}"/>
-    <cellStyle name="Notas 22" xfId="312" xr:uid="{00000000-0005-0000-0000-000094050000}"/>
-    <cellStyle name="Notas 22 2" xfId="607" xr:uid="{00000000-0005-0000-0000-000095050000}"/>
-    <cellStyle name="Notas 22 2 2" xfId="1246" xr:uid="{00000000-0005-0000-0000-000096050000}"/>
-    <cellStyle name="Notas 22 3" xfId="1245" xr:uid="{00000000-0005-0000-0000-000097050000}"/>
-    <cellStyle name="Notas 23" xfId="621" xr:uid="{00000000-0005-0000-0000-000098050000}"/>
-    <cellStyle name="Notas 23 2" xfId="1248" xr:uid="{00000000-0005-0000-0000-000099050000}"/>
-    <cellStyle name="Notas 23 3" xfId="1247" xr:uid="{00000000-0005-0000-0000-00009A050000}"/>
-    <cellStyle name="Notas 24" xfId="1218" xr:uid="{00000000-0005-0000-0000-00009B050000}"/>
-    <cellStyle name="Notas 25" xfId="1265" xr:uid="{00000000-0005-0000-0000-00009C050000}"/>
-    <cellStyle name="Notas 26" xfId="1279" xr:uid="{00000000-0005-0000-0000-00009D050000}"/>
-    <cellStyle name="Notas 27" xfId="1293" xr:uid="{00000000-0005-0000-0000-00009E050000}"/>
-    <cellStyle name="Notas 28" xfId="1307" xr:uid="{00000000-0005-0000-0000-00009F050000}"/>
-    <cellStyle name="Notas 29" xfId="1321" xr:uid="{00000000-0005-0000-0000-0000A0050000}"/>
-    <cellStyle name="Notas 3" xfId="46" xr:uid="{00000000-0005-0000-0000-0000A1050000}"/>
-    <cellStyle name="Notas 3 2" xfId="341" xr:uid="{00000000-0005-0000-0000-0000A2050000}"/>
-    <cellStyle name="Notas 3 2 2" xfId="1250" xr:uid="{00000000-0005-0000-0000-0000A3050000}"/>
-    <cellStyle name="Notas 3 3" xfId="1249" xr:uid="{00000000-0005-0000-0000-0000A4050000}"/>
-    <cellStyle name="Notas 30" xfId="1335" xr:uid="{00000000-0005-0000-0000-0000A5050000}"/>
-    <cellStyle name="Notas 31" xfId="1349" xr:uid="{00000000-0005-0000-0000-0000A6050000}"/>
-    <cellStyle name="Notas 32" xfId="1363" xr:uid="{00000000-0005-0000-0000-0000A7050000}"/>
-    <cellStyle name="Notas 33" xfId="1377" xr:uid="{00000000-0005-0000-0000-0000A8050000}"/>
-    <cellStyle name="Notas 34" xfId="1391" xr:uid="{00000000-0005-0000-0000-0000A9050000}"/>
-    <cellStyle name="Notas 35" xfId="1405" xr:uid="{00000000-0005-0000-0000-0000AA050000}"/>
-    <cellStyle name="Notas 36" xfId="1419" xr:uid="{00000000-0005-0000-0000-0000AB050000}"/>
-    <cellStyle name="Notas 37" xfId="1433" xr:uid="{00000000-0005-0000-0000-0000AC050000}"/>
-    <cellStyle name="Notas 38" xfId="1447" xr:uid="{00000000-0005-0000-0000-0000AD050000}"/>
-    <cellStyle name="Notas 39" xfId="1461" xr:uid="{00000000-0005-0000-0000-0000AE050000}"/>
-    <cellStyle name="Notas 4" xfId="60" xr:uid="{00000000-0005-0000-0000-0000AF050000}"/>
-    <cellStyle name="Notas 4 2" xfId="355" xr:uid="{00000000-0005-0000-0000-0000B0050000}"/>
-    <cellStyle name="Notas 4 2 2" xfId="1252" xr:uid="{00000000-0005-0000-0000-0000B1050000}"/>
-    <cellStyle name="Notas 4 3" xfId="1251" xr:uid="{00000000-0005-0000-0000-0000B2050000}"/>
-    <cellStyle name="Notas 40" xfId="1476" xr:uid="{00000000-0005-0000-0000-0000B3050000}"/>
-    <cellStyle name="Notas 5" xfId="74" xr:uid="{00000000-0005-0000-0000-0000B4050000}"/>
-    <cellStyle name="Notas 5 2" xfId="369" xr:uid="{00000000-0005-0000-0000-0000B5050000}"/>
-    <cellStyle name="Notas 5 2 2" xfId="1254" xr:uid="{00000000-0005-0000-0000-0000B6050000}"/>
-    <cellStyle name="Notas 5 3" xfId="1253" xr:uid="{00000000-0005-0000-0000-0000B7050000}"/>
-    <cellStyle name="Notas 6" xfId="88" xr:uid="{00000000-0005-0000-0000-0000B8050000}"/>
-    <cellStyle name="Notas 6 2" xfId="383" xr:uid="{00000000-0005-0000-0000-0000B9050000}"/>
-    <cellStyle name="Notas 6 2 2" xfId="1256" xr:uid="{00000000-0005-0000-0000-0000BA050000}"/>
-    <cellStyle name="Notas 6 3" xfId="1255" xr:uid="{00000000-0005-0000-0000-0000BB050000}"/>
-    <cellStyle name="Notas 7" xfId="102" xr:uid="{00000000-0005-0000-0000-0000BC050000}"/>
-    <cellStyle name="Notas 7 2" xfId="397" xr:uid="{00000000-0005-0000-0000-0000BD050000}"/>
-    <cellStyle name="Notas 7 2 2" xfId="1258" xr:uid="{00000000-0005-0000-0000-0000BE050000}"/>
-    <cellStyle name="Notas 7 3" xfId="1257" xr:uid="{00000000-0005-0000-0000-0000BF050000}"/>
-    <cellStyle name="Notas 8" xfId="116" xr:uid="{00000000-0005-0000-0000-0000C0050000}"/>
-    <cellStyle name="Notas 8 2" xfId="411" xr:uid="{00000000-0005-0000-0000-0000C1050000}"/>
-    <cellStyle name="Notas 8 2 2" xfId="1260" xr:uid="{00000000-0005-0000-0000-0000C2050000}"/>
-    <cellStyle name="Notas 8 3" xfId="1259" xr:uid="{00000000-0005-0000-0000-0000C3050000}"/>
-    <cellStyle name="Notas 9" xfId="130" xr:uid="{00000000-0005-0000-0000-0000C4050000}"/>
-    <cellStyle name="Notas 9 2" xfId="425" xr:uid="{00000000-0005-0000-0000-0000C5050000}"/>
-    <cellStyle name="Notas 9 2 2" xfId="1262" xr:uid="{00000000-0005-0000-0000-0000C6050000}"/>
-    <cellStyle name="Notas 9 3" xfId="1261" xr:uid="{00000000-0005-0000-0000-0000C7050000}"/>
-    <cellStyle name="Porcentaje 2" xfId="1263" xr:uid="{00000000-0005-0000-0000-0000C8050000}"/>
+    <cellStyle name="Normal 10" xfId="129"/>
+    <cellStyle name="Normal 10 2" xfId="424"/>
+    <cellStyle name="Normal 10 2 2" xfId="1166"/>
+    <cellStyle name="Normal 10 3" xfId="1165"/>
+    <cellStyle name="Normal 11" xfId="143"/>
+    <cellStyle name="Normal 11 2" xfId="438"/>
+    <cellStyle name="Normal 11 2 2" xfId="1168"/>
+    <cellStyle name="Normal 11 3" xfId="1167"/>
+    <cellStyle name="Normal 12" xfId="157"/>
+    <cellStyle name="Normal 12 2" xfId="452"/>
+    <cellStyle name="Normal 12 2 2" xfId="1170"/>
+    <cellStyle name="Normal 12 3" xfId="1169"/>
+    <cellStyle name="Normal 13" xfId="171"/>
+    <cellStyle name="Normal 13 2" xfId="466"/>
+    <cellStyle name="Normal 13 2 2" xfId="1172"/>
+    <cellStyle name="Normal 13 3" xfId="1171"/>
+    <cellStyle name="Normal 14" xfId="185"/>
+    <cellStyle name="Normal 14 2" xfId="480"/>
+    <cellStyle name="Normal 14 2 2" xfId="1174"/>
+    <cellStyle name="Normal 14 3" xfId="1173"/>
+    <cellStyle name="Normal 15" xfId="199"/>
+    <cellStyle name="Normal 15 2" xfId="494"/>
+    <cellStyle name="Normal 15 2 2" xfId="1176"/>
+    <cellStyle name="Normal 15 3" xfId="1175"/>
+    <cellStyle name="Normal 16" xfId="213"/>
+    <cellStyle name="Normal 16 2" xfId="508"/>
+    <cellStyle name="Normal 16 2 2" xfId="1178"/>
+    <cellStyle name="Normal 16 3" xfId="1177"/>
+    <cellStyle name="Normal 17" xfId="227"/>
+    <cellStyle name="Normal 17 2" xfId="522"/>
+    <cellStyle name="Normal 17 2 2" xfId="1180"/>
+    <cellStyle name="Normal 17 3" xfId="1179"/>
+    <cellStyle name="Normal 18" xfId="241"/>
+    <cellStyle name="Normal 18 2" xfId="536"/>
+    <cellStyle name="Normal 18 2 2" xfId="1182"/>
+    <cellStyle name="Normal 18 3" xfId="1181"/>
+    <cellStyle name="Normal 19" xfId="255"/>
+    <cellStyle name="Normal 19 2" xfId="550"/>
+    <cellStyle name="Normal 19 2 2" xfId="1184"/>
+    <cellStyle name="Normal 19 3" xfId="1183"/>
+    <cellStyle name="Normal 2" xfId="1"/>
+    <cellStyle name="Normal 2 2" xfId="325"/>
+    <cellStyle name="Normal 2 2 2" xfId="1186"/>
+    <cellStyle name="Normal 2 3" xfId="2"/>
+    <cellStyle name="Normal 2 4" xfId="1187"/>
+    <cellStyle name="Normal 2 5" xfId="1185"/>
+    <cellStyle name="Normal 20" xfId="269"/>
+    <cellStyle name="Normal 20 2" xfId="564"/>
+    <cellStyle name="Normal 20 2 2" xfId="1189"/>
+    <cellStyle name="Normal 20 3" xfId="1188"/>
+    <cellStyle name="Normal 21" xfId="283"/>
+    <cellStyle name="Normal 21 2" xfId="578"/>
+    <cellStyle name="Normal 21 2 2" xfId="1191"/>
+    <cellStyle name="Normal 21 3" xfId="1190"/>
+    <cellStyle name="Normal 22" xfId="297"/>
+    <cellStyle name="Normal 22 2" xfId="592"/>
+    <cellStyle name="Normal 22 2 2" xfId="1193"/>
+    <cellStyle name="Normal 22 3" xfId="1192"/>
+    <cellStyle name="Normal 23" xfId="311"/>
+    <cellStyle name="Normal 23 2" xfId="606"/>
+    <cellStyle name="Normal 23 2 2" xfId="1195"/>
+    <cellStyle name="Normal 23 3" xfId="1194"/>
+    <cellStyle name="Normal 24" xfId="620"/>
+    <cellStyle name="Normal 24 2" xfId="1197"/>
+    <cellStyle name="Normal 24 3" xfId="1198"/>
+    <cellStyle name="Normal 24 4" xfId="1196"/>
+    <cellStyle name="Normal 25" xfId="1199"/>
+    <cellStyle name="Normal 26" xfId="1200"/>
+    <cellStyle name="Normal 26 2" xfId="1201"/>
+    <cellStyle name="Normal 27" xfId="1202"/>
+    <cellStyle name="Normal 28" xfId="634"/>
+    <cellStyle name="Normal 29" xfId="1264"/>
+    <cellStyle name="Normal 3" xfId="43"/>
+    <cellStyle name="Normal 3 2" xfId="338"/>
+    <cellStyle name="Normal 3 2 2" xfId="1204"/>
+    <cellStyle name="Normal 3 3" xfId="1203"/>
+    <cellStyle name="Normal 30" xfId="1278"/>
+    <cellStyle name="Normal 31" xfId="1292"/>
+    <cellStyle name="Normal 32" xfId="1306"/>
+    <cellStyle name="Normal 33" xfId="1320"/>
+    <cellStyle name="Normal 34" xfId="1334"/>
+    <cellStyle name="Normal 35" xfId="1348"/>
+    <cellStyle name="Normal 36" xfId="1362"/>
+    <cellStyle name="Normal 37" xfId="1376"/>
+    <cellStyle name="Normal 38" xfId="1390"/>
+    <cellStyle name="Normal 39" xfId="1404"/>
+    <cellStyle name="Normal 4" xfId="45"/>
+    <cellStyle name="Normal 4 2" xfId="340"/>
+    <cellStyle name="Normal 4 2 2" xfId="1206"/>
+    <cellStyle name="Normal 4 3" xfId="1207"/>
+    <cellStyle name="Normal 4 4" xfId="1205"/>
+    <cellStyle name="Normal 40" xfId="1418"/>
+    <cellStyle name="Normal 41" xfId="1432"/>
+    <cellStyle name="Normal 42" xfId="1446"/>
+    <cellStyle name="Normal 43" xfId="1460"/>
+    <cellStyle name="Normal 44" xfId="1474"/>
+    <cellStyle name="Normal 5" xfId="59"/>
+    <cellStyle name="Normal 5 2" xfId="354"/>
+    <cellStyle name="Normal 5 2 2" xfId="1209"/>
+    <cellStyle name="Normal 5 3" xfId="1208"/>
+    <cellStyle name="Normal 6" xfId="73"/>
+    <cellStyle name="Normal 6 2" xfId="368"/>
+    <cellStyle name="Normal 6 2 2" xfId="1211"/>
+    <cellStyle name="Normal 6 3" xfId="1210"/>
+    <cellStyle name="Normal 7" xfId="87"/>
+    <cellStyle name="Normal 7 2" xfId="382"/>
+    <cellStyle name="Normal 7 2 2" xfId="1213"/>
+    <cellStyle name="Normal 7 3" xfId="1212"/>
+    <cellStyle name="Normal 8" xfId="101"/>
+    <cellStyle name="Normal 8 2" xfId="396"/>
+    <cellStyle name="Normal 8 2 2" xfId="1215"/>
+    <cellStyle name="Normal 8 3" xfId="1214"/>
+    <cellStyle name="Normal 9" xfId="115"/>
+    <cellStyle name="Normal 9 2" xfId="410"/>
+    <cellStyle name="Normal 9 2 2" xfId="1217"/>
+    <cellStyle name="Normal 9 3" xfId="1216"/>
+    <cellStyle name="Notas 10" xfId="144"/>
+    <cellStyle name="Notas 10 2" xfId="439"/>
+    <cellStyle name="Notas 10 2 2" xfId="1220"/>
+    <cellStyle name="Notas 10 3" xfId="1219"/>
+    <cellStyle name="Notas 11" xfId="158"/>
+    <cellStyle name="Notas 11 2" xfId="453"/>
+    <cellStyle name="Notas 11 2 2" xfId="1222"/>
+    <cellStyle name="Notas 11 3" xfId="1221"/>
+    <cellStyle name="Notas 12" xfId="172"/>
+    <cellStyle name="Notas 12 2" xfId="467"/>
+    <cellStyle name="Notas 12 2 2" xfId="1224"/>
+    <cellStyle name="Notas 12 3" xfId="1223"/>
+    <cellStyle name="Notas 13" xfId="186"/>
+    <cellStyle name="Notas 13 2" xfId="481"/>
+    <cellStyle name="Notas 13 2 2" xfId="1226"/>
+    <cellStyle name="Notas 13 3" xfId="1225"/>
+    <cellStyle name="Notas 14" xfId="200"/>
+    <cellStyle name="Notas 14 2" xfId="495"/>
+    <cellStyle name="Notas 14 2 2" xfId="1228"/>
+    <cellStyle name="Notas 14 3" xfId="1227"/>
+    <cellStyle name="Notas 15" xfId="214"/>
+    <cellStyle name="Notas 15 2" xfId="509"/>
+    <cellStyle name="Notas 15 2 2" xfId="1230"/>
+    <cellStyle name="Notas 15 3" xfId="1229"/>
+    <cellStyle name="Notas 16" xfId="228"/>
+    <cellStyle name="Notas 16 2" xfId="523"/>
+    <cellStyle name="Notas 16 2 2" xfId="1232"/>
+    <cellStyle name="Notas 16 3" xfId="1231"/>
+    <cellStyle name="Notas 17" xfId="242"/>
+    <cellStyle name="Notas 17 2" xfId="537"/>
+    <cellStyle name="Notas 17 2 2" xfId="1234"/>
+    <cellStyle name="Notas 17 3" xfId="1233"/>
+    <cellStyle name="Notas 18" xfId="256"/>
+    <cellStyle name="Notas 18 2" xfId="551"/>
+    <cellStyle name="Notas 18 2 2" xfId="1236"/>
+    <cellStyle name="Notas 18 3" xfId="1235"/>
+    <cellStyle name="Notas 19" xfId="270"/>
+    <cellStyle name="Notas 19 2" xfId="565"/>
+    <cellStyle name="Notas 19 2 2" xfId="1238"/>
+    <cellStyle name="Notas 19 3" xfId="1237"/>
+    <cellStyle name="Notas 2" xfId="44"/>
+    <cellStyle name="Notas 2 2" xfId="339"/>
+    <cellStyle name="Notas 2 2 2" xfId="1240"/>
+    <cellStyle name="Notas 2 3" xfId="1239"/>
+    <cellStyle name="Notas 20" xfId="284"/>
+    <cellStyle name="Notas 20 2" xfId="579"/>
+    <cellStyle name="Notas 20 2 2" xfId="1242"/>
+    <cellStyle name="Notas 20 3" xfId="1241"/>
+    <cellStyle name="Notas 21" xfId="298"/>
+    <cellStyle name="Notas 21 2" xfId="593"/>
+    <cellStyle name="Notas 21 2 2" xfId="1244"/>
+    <cellStyle name="Notas 21 3" xfId="1243"/>
+    <cellStyle name="Notas 22" xfId="312"/>
+    <cellStyle name="Notas 22 2" xfId="607"/>
+    <cellStyle name="Notas 22 2 2" xfId="1246"/>
+    <cellStyle name="Notas 22 3" xfId="1245"/>
+    <cellStyle name="Notas 23" xfId="621"/>
+    <cellStyle name="Notas 23 2" xfId="1248"/>
+    <cellStyle name="Notas 23 3" xfId="1247"/>
+    <cellStyle name="Notas 24" xfId="1218"/>
+    <cellStyle name="Notas 25" xfId="1265"/>
+    <cellStyle name="Notas 26" xfId="1279"/>
+    <cellStyle name="Notas 27" xfId="1293"/>
+    <cellStyle name="Notas 28" xfId="1307"/>
+    <cellStyle name="Notas 29" xfId="1321"/>
+    <cellStyle name="Notas 3" xfId="46"/>
+    <cellStyle name="Notas 3 2" xfId="341"/>
+    <cellStyle name="Notas 3 2 2" xfId="1250"/>
+    <cellStyle name="Notas 3 3" xfId="1249"/>
+    <cellStyle name="Notas 30" xfId="1335"/>
+    <cellStyle name="Notas 31" xfId="1349"/>
+    <cellStyle name="Notas 32" xfId="1363"/>
+    <cellStyle name="Notas 33" xfId="1377"/>
+    <cellStyle name="Notas 34" xfId="1391"/>
+    <cellStyle name="Notas 35" xfId="1405"/>
+    <cellStyle name="Notas 36" xfId="1419"/>
+    <cellStyle name="Notas 37" xfId="1433"/>
+    <cellStyle name="Notas 38" xfId="1447"/>
+    <cellStyle name="Notas 39" xfId="1461"/>
+    <cellStyle name="Notas 4" xfId="60"/>
+    <cellStyle name="Notas 4 2" xfId="355"/>
+    <cellStyle name="Notas 4 2 2" xfId="1252"/>
+    <cellStyle name="Notas 4 3" xfId="1251"/>
+    <cellStyle name="Notas 40" xfId="1476"/>
+    <cellStyle name="Notas 5" xfId="74"/>
+    <cellStyle name="Notas 5 2" xfId="369"/>
+    <cellStyle name="Notas 5 2 2" xfId="1254"/>
+    <cellStyle name="Notas 5 3" xfId="1253"/>
+    <cellStyle name="Notas 6" xfId="88"/>
+    <cellStyle name="Notas 6 2" xfId="383"/>
+    <cellStyle name="Notas 6 2 2" xfId="1256"/>
+    <cellStyle name="Notas 6 3" xfId="1255"/>
+    <cellStyle name="Notas 7" xfId="102"/>
+    <cellStyle name="Notas 7 2" xfId="397"/>
+    <cellStyle name="Notas 7 2 2" xfId="1258"/>
+    <cellStyle name="Notas 7 3" xfId="1257"/>
+    <cellStyle name="Notas 8" xfId="116"/>
+    <cellStyle name="Notas 8 2" xfId="411"/>
+    <cellStyle name="Notas 8 2 2" xfId="1260"/>
+    <cellStyle name="Notas 8 3" xfId="1259"/>
+    <cellStyle name="Notas 9" xfId="130"/>
+    <cellStyle name="Notas 9 2" xfId="425"/>
+    <cellStyle name="Notas 9 2 2" xfId="1262"/>
+    <cellStyle name="Notas 9 3" xfId="1261"/>
+    <cellStyle name="Porcentaje 2" xfId="1263"/>
     <cellStyle name="Salida" xfId="12" builtinId="21" customBuiltin="1"/>
     <cellStyle name="Texto de advertencia" xfId="16" builtinId="11" customBuiltin="1"/>
     <cellStyle name="Texto explicativo" xfId="17" builtinId="53" customBuiltin="1"/>
     <cellStyle name="Título" xfId="3" builtinId="15" customBuiltin="1"/>
     <cellStyle name="Título 2" xfId="5" builtinId="17" customBuiltin="1"/>
     <cellStyle name="Título 3" xfId="6" builtinId="18" customBuiltin="1"/>
-    <cellStyle name="Título 4" xfId="1475" xr:uid="{00000000-0005-0000-0000-0000CF050000}"/>
+    <cellStyle name="Título 4" xfId="1475"/>
     <cellStyle name="Total" xfId="18" builtinId="25" customBuiltin="1"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -4464,9 +4476,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -4504,9 +4516,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -4541,7 +4553,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -4576,7 +4588,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -4749,57 +4761,57 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AD69"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:AD76"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="9" width="12.6640625" style="24" customWidth="1"/>
-    <col min="10" max="16384" width="11.44140625" style="24"/>
+    <col min="1" max="9" width="12.7109375" style="27" customWidth="1"/>
+    <col min="10" max="16384" width="11.42578125" style="27"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="36" t="s">
+    <row r="1" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="41" t="s">
         <v>43</v>
       </c>
-      <c r="B1" s="36"/>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36"/>
-      <c r="E1" s="36"/>
-      <c r="F1" s="36"/>
-      <c r="G1" s="36"/>
-      <c r="H1" s="36"/>
-      <c r="I1" s="36"/>
-    </row>
-    <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="36"/>
-      <c r="B2" s="36"/>
-      <c r="C2" s="36"/>
-      <c r="D2" s="36"/>
-      <c r="E2" s="36"/>
-      <c r="F2" s="36"/>
-      <c r="G2" s="36"/>
-      <c r="H2" s="36"/>
-      <c r="I2" s="36"/>
-    </row>
-    <row r="3" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="38" t="s">
+      <c r="B1" s="41"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41"/>
+      <c r="E1" s="41"/>
+      <c r="F1" s="41"/>
+      <c r="G1" s="41"/>
+      <c r="H1" s="41"/>
+      <c r="I1" s="41"/>
+    </row>
+    <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="41"/>
+      <c r="B2" s="41"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="41"/>
+      <c r="E2" s="41"/>
+      <c r="F2" s="41"/>
+      <c r="G2" s="41"/>
+      <c r="H2" s="41"/>
+      <c r="I2" s="41"/>
+    </row>
+    <row r="3" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="43" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="37" t="s">
+      <c r="B3" s="42" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="37"/>
-      <c r="D3" s="37"/>
-      <c r="E3" s="37"/>
-      <c r="F3" s="37" t="s">
+      <c r="C3" s="42"/>
+      <c r="D3" s="42"/>
+      <c r="E3" s="42"/>
+      <c r="F3" s="42" t="s">
         <v>1</v>
       </c>
-      <c r="G3" s="37"/>
-      <c r="H3" s="37"/>
-      <c r="I3" s="37"/>
-    </row>
-    <row r="4" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="39"/>
+      <c r="G3" s="42"/>
+      <c r="H3" s="42"/>
+      <c r="I3" s="42"/>
+    </row>
+    <row r="4" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="44"/>
       <c r="B4" s="4" t="s">
         <v>2</v>
       </c>
@@ -4821,24 +4833,24 @@
       <c r="H4" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="I4" s="4" t="s">
+      <c r="I4" s="5" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="23">
+    <row r="5" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="26">
         <v>44593</v>
       </c>
-      <c r="B5" s="33">
+      <c r="B5" s="38">
         <v>128.59</v>
       </c>
-      <c r="C5" s="33">
+      <c r="C5" s="38">
         <v>142.13</v>
       </c>
-      <c r="D5" s="33">
+      <c r="D5" s="38">
         <v>117.11</v>
       </c>
-      <c r="E5" s="33">
+      <c r="E5" s="38">
         <v>129.63999999999999</v>
       </c>
       <c r="F5" s="3" t="s">
@@ -4854,20 +4866,20 @@
         <v>36</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="23">
+    <row r="6" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="26">
         <v>44621</v>
       </c>
-      <c r="B6" s="33">
+      <c r="B6" s="38">
         <v>136.12</v>
       </c>
-      <c r="C6" s="33">
+      <c r="C6" s="38">
         <v>144.96</v>
       </c>
-      <c r="D6" s="33">
+      <c r="D6" s="38">
         <v>129.44</v>
       </c>
-      <c r="E6" s="33">
+      <c r="E6" s="38">
         <v>136.6</v>
       </c>
       <c r="F6" s="3">
@@ -4883,20 +4895,20 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="23">
+    <row r="7" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="26">
         <v>44652</v>
       </c>
-      <c r="B7" s="33">
+      <c r="B7" s="38">
         <v>143.28</v>
       </c>
-      <c r="C7" s="33">
+      <c r="C7" s="38">
         <v>154.36000000000001</v>
       </c>
-      <c r="D7" s="33">
+      <c r="D7" s="38">
         <v>135.1</v>
       </c>
-      <c r="E7" s="33">
+      <c r="E7" s="38">
         <v>143.83000000000001</v>
       </c>
       <c r="F7" s="3">
@@ -4912,20 +4924,20 @@
         <v>5.3</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="23">
+    <row r="8" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="26">
         <v>44682</v>
       </c>
-      <c r="B8" s="33">
+      <c r="B8" s="38">
         <v>151.18</v>
       </c>
-      <c r="C8" s="33">
+      <c r="C8" s="38">
         <v>154.19</v>
       </c>
-      <c r="D8" s="33">
+      <c r="D8" s="38">
         <v>142.16</v>
       </c>
-      <c r="E8" s="33">
+      <c r="E8" s="38">
         <v>153.1</v>
       </c>
       <c r="F8" s="3">
@@ -4941,20 +4953,20 @@
         <v>6.4</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="23">
+    <row r="9" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="26">
         <v>44713</v>
       </c>
-      <c r="B9" s="33">
+      <c r="B9" s="38">
         <v>158.91999999999999</v>
       </c>
-      <c r="C9" s="33">
+      <c r="C9" s="38">
         <v>163.93</v>
       </c>
-      <c r="D9" s="33">
+      <c r="D9" s="38">
         <v>150.25</v>
       </c>
-      <c r="E9" s="33">
+      <c r="E9" s="38">
         <v>160.47</v>
       </c>
       <c r="F9" s="3">
@@ -4970,20 +4982,20 @@
         <v>4.8</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="23">
+    <row r="10" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="26">
         <v>44743</v>
       </c>
-      <c r="B10" s="33">
+      <c r="B10" s="38">
         <v>171.1</v>
       </c>
-      <c r="C10" s="33">
+      <c r="C10" s="38">
         <v>188.73</v>
       </c>
-      <c r="D10" s="33">
+      <c r="D10" s="38">
         <v>156.63999999999999</v>
       </c>
-      <c r="E10" s="33">
+      <c r="E10" s="38">
         <v>172.36</v>
       </c>
       <c r="F10" s="3">
@@ -4999,20 +5011,20 @@
         <v>7.4</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="23">
+    <row r="11" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="26">
         <v>44774</v>
       </c>
-      <c r="B11" s="33">
+      <c r="B11" s="38">
         <v>181.72</v>
       </c>
-      <c r="C11" s="33">
+      <c r="C11" s="38">
         <v>197.7</v>
       </c>
-      <c r="D11" s="33">
+      <c r="D11" s="38">
         <v>166.72</v>
       </c>
-      <c r="E11" s="33">
+      <c r="E11" s="38">
         <v>183.34</v>
       </c>
       <c r="F11" s="3">
@@ -5028,20 +5040,20 @@
         <v>6.4</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="23">
+    <row r="12" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="26">
         <v>44805</v>
       </c>
-      <c r="B12" s="33">
+      <c r="B12" s="38">
         <v>191.95</v>
       </c>
-      <c r="C12" s="33">
+      <c r="C12" s="38">
         <v>214.91</v>
       </c>
-      <c r="D12" s="33">
+      <c r="D12" s="38">
         <v>170.72</v>
       </c>
-      <c r="E12" s="33">
+      <c r="E12" s="38">
         <v>194.2</v>
       </c>
       <c r="F12" s="3">
@@ -5057,20 +5069,20 @@
         <v>5.9</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="23">
+    <row r="13" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="26">
         <v>44835</v>
       </c>
-      <c r="B13" s="33">
+      <c r="B13" s="38">
         <v>205.31</v>
       </c>
-      <c r="C13" s="33">
+      <c r="C13" s="38">
         <v>230.1</v>
       </c>
-      <c r="D13" s="33">
+      <c r="D13" s="38">
         <v>188.6</v>
       </c>
-      <c r="E13" s="33">
+      <c r="E13" s="38">
         <v>206.13</v>
       </c>
       <c r="F13" s="3">
@@ -5086,20 +5098,20 @@
         <v>6.1</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="23">
+    <row r="14" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="26">
         <v>44866</v>
       </c>
-      <c r="B14" s="33">
+      <c r="B14" s="38">
         <v>217.2</v>
       </c>
-      <c r="C14" s="33">
+      <c r="C14" s="38">
         <v>240.71</v>
       </c>
-      <c r="D14" s="33">
+      <c r="D14" s="38">
         <v>200.7</v>
       </c>
-      <c r="E14" s="33">
+      <c r="E14" s="38">
         <v>218.15</v>
       </c>
       <c r="F14" s="3">
@@ -5115,20 +5127,20 @@
         <v>5.8</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="23">
+    <row r="15" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="26">
         <v>44896</v>
       </c>
-      <c r="B15" s="33">
+      <c r="B15" s="38">
         <v>229.69</v>
       </c>
-      <c r="C15" s="33">
+      <c r="C15" s="38">
         <v>257.74</v>
       </c>
-      <c r="D15" s="33">
+      <c r="D15" s="38">
         <v>210.89</v>
       </c>
-      <c r="E15" s="33">
+      <c r="E15" s="38">
         <v>230.59</v>
       </c>
       <c r="F15" s="3">
@@ -5144,20 +5156,20 @@
         <v>5.7</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="23">
+    <row r="16" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="26">
         <v>44927</v>
       </c>
-      <c r="B16" s="33">
+      <c r="B16" s="38">
         <v>246.41</v>
       </c>
-      <c r="C16" s="33">
+      <c r="C16" s="38">
         <v>301.95999999999998</v>
       </c>
-      <c r="D16" s="33">
+      <c r="D16" s="38">
         <v>224.73</v>
       </c>
-      <c r="E16" s="33">
+      <c r="E16" s="38">
         <v>244.12</v>
       </c>
       <c r="F16" s="3">
@@ -5173,20 +5185,20 @@
         <v>5.9</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="23">
+    <row r="17" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="26">
         <v>44958</v>
       </c>
-      <c r="B17" s="33">
+      <c r="B17" s="38">
         <v>261.19</v>
       </c>
-      <c r="C17" s="33">
+      <c r="C17" s="38">
         <v>311.16000000000003</v>
       </c>
-      <c r="D17" s="33">
+      <c r="D17" s="38">
         <v>235.96</v>
       </c>
-      <c r="E17" s="33">
+      <c r="E17" s="38">
         <v>260.63</v>
       </c>
       <c r="F17" s="3">
@@ -5202,20 +5214,20 @@
         <v>6.8</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="23">
+    <row r="18" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="26">
         <v>44986</v>
       </c>
-      <c r="B18" s="33">
+      <c r="B18" s="38">
         <v>279.75</v>
       </c>
-      <c r="C18" s="33">
+      <c r="C18" s="38">
         <v>316.43</v>
       </c>
-      <c r="D18" s="33">
+      <c r="D18" s="38">
         <v>263.48</v>
       </c>
-      <c r="E18" s="33">
+      <c r="E18" s="38">
         <v>278.75</v>
       </c>
       <c r="F18" s="3">
@@ -5231,20 +5243,20 @@
         <v>7</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="23">
+    <row r="19" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="26">
         <v>45017</v>
       </c>
-      <c r="B19" s="33">
+      <c r="B19" s="38">
         <v>301.45999999999998</v>
       </c>
-      <c r="C19" s="33">
+      <c r="C19" s="38">
         <v>351.3</v>
       </c>
-      <c r="D19" s="33">
+      <c r="D19" s="38">
         <v>274.52</v>
       </c>
-      <c r="E19" s="33">
+      <c r="E19" s="38">
         <v>301.36</v>
       </c>
       <c r="F19" s="3">
@@ -5260,20 +5272,20 @@
         <v>8.1</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="23">
+    <row r="20" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="26">
         <v>45047</v>
       </c>
-      <c r="B20" s="33">
+      <c r="B20" s="38">
         <v>324.2</v>
       </c>
-      <c r="C20" s="33">
+      <c r="C20" s="38">
         <v>363.42</v>
       </c>
-      <c r="D20" s="33">
+      <c r="D20" s="38">
         <v>302.89</v>
       </c>
-      <c r="E20" s="33">
+      <c r="E20" s="38">
         <v>324.14</v>
       </c>
       <c r="F20" s="3">
@@ -5289,20 +5301,20 @@
         <v>7.6</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="23">
+    <row r="21" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="26">
         <v>45078</v>
       </c>
-      <c r="B21" s="33">
+      <c r="B21" s="38">
         <v>347.38</v>
       </c>
-      <c r="C21" s="33">
+      <c r="C21" s="38">
         <v>373.84</v>
       </c>
-      <c r="D21" s="33">
+      <c r="D21" s="38">
         <v>324.16000000000003</v>
       </c>
-      <c r="E21" s="33">
+      <c r="E21" s="38">
         <v>349.65</v>
       </c>
       <c r="F21" s="3">
@@ -5318,20 +5330,20 @@
         <v>7.9</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="23">
+    <row r="22" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="26">
         <v>45108</v>
       </c>
-      <c r="B22" s="33">
+      <c r="B22" s="38">
         <v>372.82</v>
       </c>
-      <c r="C22" s="33">
+      <c r="C22" s="38">
         <v>408.43</v>
       </c>
-      <c r="D22" s="33">
+      <c r="D22" s="38">
         <v>345.81</v>
       </c>
-      <c r="E22" s="33">
+      <c r="E22" s="38">
         <v>374.77</v>
       </c>
       <c r="F22" s="3">
@@ -5347,20 +5359,20 @@
         <v>7.2</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="23">
+    <row r="23" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="26">
         <v>45139</v>
       </c>
-      <c r="B23" s="33">
+      <c r="B23" s="38">
         <v>413.08</v>
       </c>
-      <c r="C23" s="33">
+      <c r="C23" s="38">
         <v>435.12</v>
       </c>
-      <c r="D23" s="33">
+      <c r="D23" s="38">
         <v>384.85</v>
       </c>
-      <c r="E23" s="33">
+      <c r="E23" s="38">
         <v>417.28</v>
       </c>
       <c r="F23" s="3">
@@ -5376,20 +5388,20 @@
         <v>11.3</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="23">
+    <row r="24" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="26">
         <v>45170</v>
       </c>
-      <c r="B24" s="33">
+      <c r="B24" s="38">
         <v>462.47</v>
       </c>
-      <c r="C24" s="33">
+      <c r="C24" s="38">
         <v>505.37</v>
       </c>
-      <c r="D24" s="33">
+      <c r="D24" s="38">
         <v>407.03</v>
       </c>
-      <c r="E24" s="33">
+      <c r="E24" s="38">
         <v>470.8</v>
       </c>
       <c r="F24" s="3">
@@ -5405,20 +5417,20 @@
         <v>12.8</v>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="23">
+    <row r="25" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="26">
         <v>45200</v>
       </c>
-      <c r="B25" s="33">
+      <c r="B25" s="38">
         <v>505.82</v>
       </c>
-      <c r="C25" s="33">
+      <c r="C25" s="38">
         <v>540.57000000000005</v>
       </c>
-      <c r="D25" s="33">
+      <c r="D25" s="38">
         <v>439.63</v>
       </c>
-      <c r="E25" s="33">
+      <c r="E25" s="38">
         <v>518.12</v>
       </c>
       <c r="F25" s="3">
@@ -5434,20 +5446,20 @@
         <v>10.1</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="23">
+    <row r="26" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="26">
         <v>45231</v>
       </c>
-      <c r="B26" s="33">
+      <c r="B26" s="38">
         <v>565.99</v>
       </c>
-      <c r="C26" s="33">
+      <c r="C26" s="38">
         <v>604.88</v>
       </c>
-      <c r="D26" s="33">
+      <c r="D26" s="38">
         <v>475.83</v>
       </c>
-      <c r="E26" s="33">
+      <c r="E26" s="38">
         <v>583.95000000000005</v>
       </c>
       <c r="F26" s="3">
@@ -5463,20 +5475,20 @@
         <v>12.7</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="23">
+    <row r="27" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="26">
         <v>45261</v>
       </c>
-      <c r="B27" s="33">
+      <c r="B27" s="38">
         <v>685.4</v>
       </c>
-      <c r="C27" s="33">
+      <c r="C27" s="38">
         <v>721.77</v>
       </c>
-      <c r="D27" s="33">
+      <c r="D27" s="38">
         <v>557.36</v>
       </c>
-      <c r="E27" s="33">
+      <c r="E27" s="38">
         <v>713.61</v>
       </c>
       <c r="F27" s="3">
@@ -5492,20 +5504,20 @@
         <v>22.2</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="23">
+    <row r="28" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="26">
         <v>45292</v>
       </c>
-      <c r="B28" s="33">
+      <c r="B28" s="38">
         <v>834.2</v>
       </c>
-      <c r="C28" s="33">
+      <c r="C28" s="38">
         <v>971</v>
       </c>
-      <c r="D28" s="33">
+      <c r="D28" s="38">
         <v>681.77</v>
       </c>
-      <c r="E28" s="33">
+      <c r="E28" s="38">
         <v>854.4</v>
       </c>
       <c r="F28" s="3">
@@ -5521,20 +5533,20 @@
         <v>19.7</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="23">
+    <row r="29" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="26">
         <v>45323</v>
       </c>
-      <c r="B29" s="33">
+      <c r="B29" s="38">
         <v>951.99</v>
       </c>
-      <c r="C29" s="33">
+      <c r="C29" s="38">
         <v>993.87</v>
       </c>
-      <c r="D29" s="33">
+      <c r="D29" s="38">
         <v>862.76</v>
       </c>
-      <c r="E29" s="33">
+      <c r="E29" s="38">
         <v>969.29</v>
       </c>
       <c r="F29" s="3">
@@ -5550,20 +5562,20 @@
         <v>13.4</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="23">
+    <row r="30" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="26">
         <v>45352</v>
       </c>
-      <c r="B30" s="33">
+      <c r="B30" s="38">
         <v>1077.95</v>
       </c>
-      <c r="C30" s="33">
+      <c r="C30" s="38">
         <v>1047.8399999999999</v>
       </c>
-      <c r="D30" s="33">
+      <c r="D30" s="38">
         <v>1056.08</v>
       </c>
-      <c r="E30" s="33">
+      <c r="E30" s="38">
         <v>1087.97</v>
       </c>
       <c r="F30" s="3">
@@ -5579,20 +5591,20 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="31" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="23">
+    <row r="31" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="26">
         <v>45383</v>
       </c>
-      <c r="B31" s="33">
+      <c r="B31" s="38">
         <v>1183.17</v>
       </c>
-      <c r="C31" s="33">
+      <c r="C31" s="38">
         <v>1070.95</v>
       </c>
-      <c r="D31" s="33">
+      <c r="D31" s="38">
         <v>1299.47</v>
       </c>
-      <c r="E31" s="33">
+      <c r="E31" s="38">
         <v>1168.8800000000001</v>
       </c>
       <c r="F31" s="3">
@@ -5608,20 +5620,20 @@
         <v>7.4</v>
       </c>
     </row>
-    <row r="32" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="23">
+    <row r="32" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="26">
         <v>45413</v>
       </c>
-      <c r="B32" s="33">
+      <c r="B32" s="38">
         <v>1234.95</v>
       </c>
-      <c r="C32" s="33">
+      <c r="C32" s="38">
         <v>1112.51</v>
       </c>
-      <c r="D32" s="33">
+      <c r="D32" s="38">
         <v>1327.76</v>
       </c>
-      <c r="E32" s="33">
+      <c r="E32" s="38">
         <v>1228.25</v>
       </c>
       <c r="F32" s="3">
@@ -5637,20 +5649,20 @@
         <v>5.0999999999999996</v>
       </c>
     </row>
-    <row r="33" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="23">
+    <row r="33" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="26">
         <v>45444</v>
       </c>
-      <c r="B33" s="33">
+      <c r="B33" s="38">
         <v>1294.53</v>
       </c>
-      <c r="C33" s="33">
+      <c r="C33" s="38">
         <v>1138.8399999999999</v>
       </c>
-      <c r="D33" s="33">
+      <c r="D33" s="38">
         <v>1441.25</v>
       </c>
-      <c r="E33" s="33">
+      <c r="E33" s="38">
         <v>1278.51</v>
       </c>
       <c r="F33" s="3">
@@ -5666,20 +5678,20 @@
         <v>4.0999999999999996</v>
       </c>
     </row>
-    <row r="34" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="23">
+    <row r="34" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="26">
         <v>45474</v>
       </c>
-      <c r="B34" s="33">
+      <c r="B34" s="38">
         <v>1360.55</v>
       </c>
-      <c r="C34" s="33">
+      <c r="C34" s="38">
         <v>1264.25</v>
       </c>
-      <c r="D34" s="33">
+      <c r="D34" s="38">
         <v>1504.65</v>
       </c>
-      <c r="E34" s="33">
+      <c r="E34" s="38">
         <v>1336.72</v>
       </c>
       <c r="F34" s="3">
@@ -5695,20 +5707,20 @@
         <v>4.5999999999999996</v>
       </c>
     </row>
-    <row r="35" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="23">
+    <row r="35" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="26">
         <v>45505</v>
       </c>
-      <c r="B35" s="33">
+      <c r="B35" s="38">
         <v>1417.46</v>
       </c>
-      <c r="C35" s="33">
+      <c r="C35" s="38">
         <v>1226.4000000000001</v>
       </c>
-      <c r="D35" s="33">
+      <c r="D35" s="38">
         <v>1610.71</v>
       </c>
-      <c r="E35" s="33">
+      <c r="E35" s="38">
         <v>1394.37</v>
       </c>
       <c r="F35" s="3">
@@ -5724,20 +5736,20 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="36" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="23">
+    <row r="36" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="26">
         <v>45536</v>
       </c>
-      <c r="B36" s="33">
+      <c r="B36" s="38">
         <v>1474.29</v>
       </c>
-      <c r="C36" s="33">
+      <c r="C36" s="38">
         <v>1262.31</v>
       </c>
-      <c r="D36" s="33">
+      <c r="D36" s="38">
         <v>1687.67</v>
       </c>
-      <c r="E36" s="33">
+      <c r="E36" s="38">
         <v>1448.93</v>
       </c>
       <c r="F36" s="3">
@@ -5753,20 +5765,20 @@
         <v>3.9</v>
       </c>
     </row>
-    <row r="37" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="23">
+    <row r="37" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="26">
         <v>45566</v>
       </c>
-      <c r="B37" s="33">
+      <c r="B37" s="38">
         <v>1522.05</v>
       </c>
-      <c r="C37" s="33">
+      <c r="C37" s="38">
         <v>1269.46</v>
       </c>
-      <c r="D37" s="33">
+      <c r="D37" s="38">
         <v>1740.46</v>
       </c>
-      <c r="E37" s="33">
+      <c r="E37" s="38">
         <v>1501.2</v>
       </c>
       <c r="F37" s="3">
@@ -5782,20 +5794,20 @@
         <v>3.6</v>
       </c>
     </row>
-    <row r="38" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="23">
+    <row r="38" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="26">
         <v>45597</v>
       </c>
-      <c r="B38" s="33">
+      <c r="B38" s="38">
         <v>1570.26</v>
       </c>
-      <c r="C38" s="33">
+      <c r="C38" s="38">
         <v>1263.31</v>
       </c>
-      <c r="D38" s="33">
+      <c r="D38" s="38">
         <v>1822.05</v>
       </c>
-      <c r="E38" s="33">
+      <c r="E38" s="38">
         <v>1548.48</v>
       </c>
       <c r="F38" s="3">
@@ -5811,20 +5823,20 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="39" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="23">
+    <row r="39" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="26">
         <v>45627</v>
       </c>
-      <c r="B39" s="33">
+      <c r="B39" s="38">
         <v>1622.53</v>
       </c>
-      <c r="C39" s="33">
+      <c r="C39" s="38">
         <v>1286.93</v>
       </c>
-      <c r="D39" s="33">
+      <c r="D39" s="38">
         <v>1873.35</v>
       </c>
-      <c r="E39" s="33">
+      <c r="E39" s="38">
         <v>1605.1</v>
       </c>
       <c r="F39" s="3">
@@ -5840,20 +5852,20 @@
         <v>3.7</v>
       </c>
     </row>
-    <row r="40" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="23">
+    <row r="40" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="26">
         <v>45658</v>
       </c>
-      <c r="B40" s="33">
+      <c r="B40" s="38">
         <v>1673.49</v>
       </c>
-      <c r="C40" s="33">
+      <c r="C40" s="38">
         <v>1433.21</v>
       </c>
-      <c r="D40" s="33">
+      <c r="D40" s="38">
         <v>1902.6</v>
       </c>
-      <c r="E40" s="33">
+      <c r="E40" s="38">
         <v>1648.08</v>
       </c>
       <c r="F40" s="3">
@@ -5869,20 +5881,20 @@
         <v>2.7</v>
       </c>
     </row>
-    <row r="41" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="23">
+    <row r="41" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="26">
         <v>45689</v>
       </c>
-      <c r="B41" s="33">
+      <c r="B41" s="38">
         <v>1707.89</v>
       </c>
-      <c r="C41" s="33">
+      <c r="C41" s="38">
         <v>1364.38</v>
       </c>
-      <c r="D41" s="33">
+      <c r="D41" s="38">
         <v>1931.4</v>
       </c>
-      <c r="E41" s="33">
+      <c r="E41" s="38">
         <v>1698.71</v>
       </c>
       <c r="F41" s="3">
@@ -5898,20 +5910,20 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="42" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="23">
+    <row r="42" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="26">
         <v>45717</v>
       </c>
-      <c r="B42" s="33">
+      <c r="B42" s="38">
         <v>1761.98</v>
       </c>
-      <c r="C42" s="33">
+      <c r="C42" s="38">
         <v>1407.69</v>
       </c>
-      <c r="D42" s="33">
+      <c r="D42" s="38">
         <v>2022.4</v>
       </c>
-      <c r="E42" s="33">
+      <c r="E42" s="38">
         <v>1744.72</v>
       </c>
       <c r="F42" s="3">
@@ -5927,20 +5939,20 @@
         <v>2.7</v>
       </c>
     </row>
-    <row r="43" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="23">
+    <row r="43" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="26">
         <v>45748</v>
       </c>
-      <c r="B43" s="33">
+      <c r="B43" s="38">
         <v>1802.79</v>
       </c>
-      <c r="C43" s="33">
+      <c r="C43" s="38">
         <v>1392.12</v>
       </c>
-      <c r="D43" s="33">
+      <c r="D43" s="38">
         <v>2053.0300000000002</v>
       </c>
-      <c r="E43" s="33">
+      <c r="E43" s="38">
         <v>1796.25</v>
       </c>
       <c r="F43" s="3">
@@ -5956,20 +5968,20 @@
         <v>3</v>
       </c>
     </row>
-    <row r="44" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="23">
+    <row r="44" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="26">
         <v>45778</v>
       </c>
-      <c r="B44" s="33">
+      <c r="B44" s="38">
         <v>1831.11</v>
       </c>
-      <c r="C44" s="33">
+      <c r="C44" s="38">
         <v>1342.16</v>
       </c>
-      <c r="D44" s="33">
+      <c r="D44" s="38">
         <v>2087.1999999999998</v>
       </c>
-      <c r="E44" s="33">
+      <c r="E44" s="38">
         <v>1834.24</v>
       </c>
       <c r="F44" s="3">
@@ -5985,20 +5997,20 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="45" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="23">
+    <row r="45" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="26">
         <v>45809</v>
       </c>
-      <c r="B45" s="33">
+      <c r="B45" s="38">
         <v>1870.43</v>
       </c>
-      <c r="C45" s="33">
+      <c r="C45" s="38">
         <v>1358.84</v>
       </c>
-      <c r="D45" s="33">
+      <c r="D45" s="38">
         <v>2136.89</v>
       </c>
-      <c r="E45" s="33">
+      <c r="E45" s="38">
         <v>1874.09</v>
       </c>
       <c r="F45" s="3">
@@ -6014,20 +6026,20 @@
         <v>2.2000000000000002</v>
       </c>
     </row>
-    <row r="46" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="23">
+    <row r="46" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="26">
         <v>45839</v>
       </c>
-      <c r="B46" s="33">
+      <c r="B46" s="38">
         <v>1916.97</v>
       </c>
-      <c r="C46" s="33">
+      <c r="C46" s="38">
         <v>1481.09</v>
       </c>
-      <c r="D46" s="33">
+      <c r="D46" s="38">
         <v>2181.13</v>
       </c>
-      <c r="E46" s="33">
+      <c r="E46" s="38">
         <v>1910.4</v>
       </c>
       <c r="F46" s="3">
@@ -6043,20 +6055,20 @@
         <v>1.9</v>
       </c>
     </row>
-    <row r="47" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="23">
+    <row r="47" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="26">
         <v>45870</v>
       </c>
-      <c r="B47" s="33">
+      <c r="B47" s="38">
         <v>1947.42</v>
       </c>
-      <c r="C47" s="33">
+      <c r="C47" s="38">
         <v>1440.71</v>
       </c>
-      <c r="D47" s="33">
+      <c r="D47" s="38">
         <v>2221.6799999999998</v>
       </c>
-      <c r="E47" s="33">
+      <c r="E47" s="38">
         <v>1948.35</v>
       </c>
       <c r="F47" s="3">
@@ -6072,20 +6084,20 @@
         <v>2</v>
       </c>
     </row>
-    <row r="48" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="23">
+    <row r="48" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A48" s="26">
         <v>45901</v>
       </c>
-      <c r="B48" s="33">
+      <c r="B48" s="38">
         <v>1990.42</v>
       </c>
-      <c r="C48" s="33">
+      <c r="C48" s="38">
         <v>1478.57</v>
       </c>
-      <c r="D48" s="33">
+      <c r="D48" s="38">
         <v>2267.31</v>
       </c>
-      <c r="E48" s="33">
+      <c r="E48" s="38">
         <v>1991.39</v>
       </c>
       <c r="F48" s="3">
@@ -6101,20 +6113,20 @@
         <v>2.2000000000000002</v>
       </c>
     </row>
-    <row r="49" spans="1:30" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="23">
+    <row r="49" spans="1:30" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A49" s="26">
         <v>45931</v>
       </c>
-      <c r="B49" s="33">
+      <c r="B49" s="38">
         <v>2033.44</v>
       </c>
-      <c r="C49" s="33">
+      <c r="C49" s="38">
         <v>1519.93</v>
       </c>
-      <c r="D49" s="33">
+      <c r="D49" s="38">
         <v>2310.92</v>
       </c>
-      <c r="E49" s="33">
+      <c r="E49" s="38">
         <v>2034.51</v>
       </c>
       <c r="F49" s="3">
@@ -6130,20 +6142,20 @@
         <v>2.2000000000000002</v>
       </c>
     </row>
-    <row r="50" spans="1:30" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="23">
+    <row r="50" spans="1:30" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A50" s="26">
         <v>45962</v>
       </c>
-      <c r="B50" s="33">
+      <c r="B50" s="38">
         <v>2082.5</v>
       </c>
-      <c r="C50" s="33">
+      <c r="C50" s="38">
         <v>1533.58</v>
       </c>
-      <c r="D50" s="33">
+      <c r="D50" s="38">
         <v>2372.36</v>
       </c>
-      <c r="E50" s="33">
+      <c r="E50" s="38">
         <v>2085.4</v>
       </c>
       <c r="F50" s="3">
@@ -6159,20 +6171,20 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="51" spans="1:30" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="23">
+    <row r="51" spans="1:30" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A51" s="26">
         <v>45992</v>
       </c>
-      <c r="B51" s="33">
+      <c r="B51" s="38">
         <v>2137.9899999999998</v>
       </c>
-      <c r="C51" s="33">
+      <c r="C51" s="38">
         <v>1525.63</v>
       </c>
-      <c r="D51" s="33">
+      <c r="D51" s="38">
         <v>2449.34</v>
       </c>
-      <c r="E51" s="33">
+      <c r="E51" s="38">
         <v>2144.36</v>
       </c>
       <c r="F51" s="3">
@@ -6188,20 +6200,20 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="52" spans="1:30" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="23">
+    <row r="52" spans="1:30" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="26">
         <v>46023</v>
       </c>
-      <c r="B52" s="33">
+      <c r="B52" s="38">
         <v>2203.37</v>
       </c>
-      <c r="C52" s="33">
+      <c r="C52" s="38">
         <v>1767.41</v>
       </c>
-      <c r="D52" s="33">
+      <c r="D52" s="38">
         <v>2490.06</v>
       </c>
-      <c r="E52" s="33">
+      <c r="E52" s="38">
         <v>2190.94</v>
       </c>
       <c r="F52" s="3">
@@ -6217,20 +6229,20 @@
         <v>2.2000000000000002</v>
       </c>
     </row>
-    <row r="53" spans="1:30" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="23">
+    <row r="53" spans="1:30" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A53" s="26">
         <v>46054</v>
       </c>
-      <c r="B53" s="33">
+      <c r="B53" s="38">
         <v>2260.6</v>
       </c>
-      <c r="C53" s="33">
+      <c r="C53" s="38">
         <v>1651.93</v>
       </c>
-      <c r="D53" s="33">
+      <c r="D53" s="38">
         <v>2603</v>
       </c>
-      <c r="E53" s="33">
+      <c r="E53" s="38">
         <v>2258.35</v>
       </c>
       <c r="F53" s="3">
@@ -6246,20 +6258,20 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="54" spans="1:30" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="23">
+    <row r="54" spans="1:30" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="26">
         <v>46082</v>
       </c>
-      <c r="B54" s="33">
+      <c r="B54" s="38">
         <v>2328.35</v>
       </c>
-      <c r="C54" s="33">
+      <c r="C54" s="38">
         <v>1576.77</v>
       </c>
-      <c r="D54" s="33">
+      <c r="D54" s="38">
         <v>2772.2</v>
       </c>
-      <c r="E54" s="33">
+      <c r="E54" s="38">
         <v>2320.0700000000002</v>
       </c>
       <c r="F54" s="3">
@@ -6275,20 +6287,20 @@
         <v>2.7</v>
       </c>
     </row>
-    <row r="55" spans="1:30" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="23">
+    <row r="55" spans="1:30" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A55" s="26">
         <v>46113</v>
       </c>
-      <c r="B55" s="33">
+      <c r="B55" s="38">
         <v>2386.16</v>
       </c>
-      <c r="C55" s="33">
+      <c r="C55" s="38">
         <v>1605.08</v>
       </c>
-      <c r="D55" s="33">
+      <c r="D55" s="38">
         <v>2862.56</v>
       </c>
-      <c r="E55" s="33">
+      <c r="E55" s="38">
         <v>2373.59</v>
       </c>
       <c r="F55" s="3">
@@ -6304,20 +6316,20 @@
         <v>2.2999999999999998</v>
       </c>
     </row>
-    <row r="56" spans="1:30" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="23">
+    <row r="56" spans="1:30" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A56" s="26">
         <v>46143</v>
       </c>
-      <c r="B56" s="33">
+      <c r="B56" s="38">
         <v>2436.4299999999998</v>
       </c>
-      <c r="C56" s="33">
+      <c r="C56" s="38">
         <v>1606.71</v>
       </c>
-      <c r="D56" s="33">
+      <c r="D56" s="38">
         <v>2941.6</v>
       </c>
-      <c r="E56" s="33">
+      <c r="E56" s="38">
         <v>2423.3200000000002</v>
       </c>
       <c r="F56" s="3">
@@ -6333,20 +6345,20 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="57" spans="1:30" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="23">
+    <row r="57" spans="1:30" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A57" s="26">
         <v>46174</v>
       </c>
-      <c r="B57" s="33">
+      <c r="B57" s="38">
         <v>2480.63</v>
       </c>
-      <c r="C57" s="33">
+      <c r="C57" s="38">
         <v>1607.92</v>
       </c>
-      <c r="D57" s="33">
+      <c r="D57" s="38">
         <v>2999.94</v>
       </c>
-      <c r="E57" s="33">
+      <c r="E57" s="38">
         <v>2469.9899999999998</v>
       </c>
       <c r="F57" s="3">
@@ -6362,20 +6374,20 @@
         <v>1.9</v>
       </c>
     </row>
-    <row r="58" spans="1:30" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="23">
+    <row r="58" spans="1:30" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A58" s="26">
         <v>46204</v>
       </c>
-      <c r="B58" s="33">
+      <c r="B58" s="38">
         <v>2553.4</v>
       </c>
-      <c r="C58" s="33">
+      <c r="C58" s="38">
         <v>1783.24</v>
       </c>
-      <c r="D58" s="33">
+      <c r="D58" s="38">
         <v>3091.15</v>
       </c>
-      <c r="E58" s="33">
+      <c r="E58" s="38">
         <v>2523.2800000000002</v>
       </c>
       <c r="F58" s="3">
@@ -6391,91 +6403,156 @@
         <v>2.2000000000000002</v>
       </c>
     </row>
-    <row r="59" spans="1:30" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="28" t="s">
+    <row r="59" spans="1:30" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A59" s="26">
+        <v>46235</v>
+      </c>
+      <c r="B59" s="38">
+        <v>2596.6</v>
+      </c>
+      <c r="C59" s="38">
+        <v>1731.53</v>
+      </c>
+      <c r="D59" s="38">
+        <v>3145.48</v>
+      </c>
+      <c r="E59" s="38">
+        <v>2577.15</v>
+      </c>
+      <c r="F59" s="3">
+        <v>1.7</v>
+      </c>
+      <c r="G59" s="3">
+        <v>-2.9</v>
+      </c>
+      <c r="H59" s="3">
+        <v>1.8</v>
+      </c>
+      <c r="I59" s="3">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:30" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A60" s="31" t="s">
         <v>38</v>
       </c>
-      <c r="B59" s="26"/>
-      <c r="C59" s="26"/>
-      <c r="D59" s="26"/>
-      <c r="E59" s="26"/>
-      <c r="F59" s="27"/>
-      <c r="G59" s="27"/>
-      <c r="H59" s="27"/>
-      <c r="I59" s="27"/>
-    </row>
-    <row r="60" spans="1:30" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="2" t="s">
+      <c r="B60" s="29"/>
+      <c r="C60" s="29"/>
+      <c r="D60" s="29"/>
+      <c r="E60" s="29"/>
+      <c r="F60" s="30"/>
+      <c r="G60" s="30"/>
+      <c r="H60" s="30"/>
+      <c r="I60" s="30"/>
+    </row>
+    <row r="61" spans="1:30" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A61" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B60" s="1"/>
-      <c r="C60" s="1"/>
-      <c r="D60" s="1"/>
-      <c r="E60" s="1"/>
-      <c r="F60" s="1"/>
-      <c r="G60" s="1"/>
-      <c r="H60" s="1"/>
-      <c r="I60" s="1"/>
-    </row>
-    <row r="61" spans="1:30" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="34" t="s">
+      <c r="B61" s="1"/>
+      <c r="C61" s="1"/>
+      <c r="D61" s="1"/>
+      <c r="E61" s="1"/>
+      <c r="F61" s="1"/>
+      <c r="G61" s="1"/>
+      <c r="H61" s="1"/>
+      <c r="I61" s="1"/>
+    </row>
+    <row r="62" spans="1:30" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A62" s="39" t="s">
         <v>41</v>
       </c>
-      <c r="B61" s="35"/>
-      <c r="C61" s="35"/>
-      <c r="D61" s="35"/>
-      <c r="E61" s="35"/>
-      <c r="F61" s="35"/>
-      <c r="G61" s="35"/>
-      <c r="H61" s="35"/>
-      <c r="I61" s="35"/>
-      <c r="J61" s="22"/>
-      <c r="K61" s="22"/>
-      <c r="L61" s="22"/>
-      <c r="M61" s="22"/>
-      <c r="N61" s="22"/>
-      <c r="O61" s="22"/>
-      <c r="P61" s="22"/>
-      <c r="Q61" s="22"/>
-      <c r="R61" s="22"/>
-      <c r="S61" s="22"/>
-      <c r="T61" s="22"/>
-      <c r="U61" s="22"/>
-      <c r="V61" s="22"/>
-      <c r="W61" s="22"/>
-      <c r="X61" s="22"/>
-      <c r="Y61" s="22"/>
-      <c r="Z61" s="22"/>
-      <c r="AA61" s="22"/>
-      <c r="AB61" s="22"/>
-      <c r="AC61" s="22"/>
-      <c r="AD61" s="22"/>
-    </row>
-    <row r="63" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="B63" s="32"/>
-      <c r="C63" s="32"/>
-      <c r="D63" s="32"/>
-      <c r="E63" s="32"/>
-      <c r="F63" s="32"/>
-      <c r="G63" s="32"/>
-      <c r="H63" s="32"/>
-      <c r="I63" s="32"/>
-    </row>
-    <row r="66" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C66" s="31"/>
-    </row>
-    <row r="67" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C67" s="30"/>
-    </row>
-    <row r="68" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C68" s="30"/>
-    </row>
-    <row r="69" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C69" s="30"/>
+      <c r="B62" s="40"/>
+      <c r="C62" s="40"/>
+      <c r="D62" s="40"/>
+      <c r="E62" s="40"/>
+      <c r="F62" s="40"/>
+      <c r="G62" s="40"/>
+      <c r="H62" s="40"/>
+      <c r="I62" s="40"/>
+      <c r="J62" s="25"/>
+      <c r="K62" s="25"/>
+      <c r="L62" s="25"/>
+      <c r="M62" s="25"/>
+      <c r="N62" s="25"/>
+      <c r="O62" s="25"/>
+      <c r="P62" s="25"/>
+      <c r="Q62" s="25"/>
+      <c r="R62" s="25"/>
+      <c r="S62" s="25"/>
+      <c r="T62" s="25"/>
+      <c r="U62" s="25"/>
+      <c r="V62" s="25"/>
+      <c r="W62" s="25"/>
+      <c r="X62" s="25"/>
+      <c r="Y62" s="25"/>
+      <c r="Z62" s="25"/>
+      <c r="AA62" s="25"/>
+      <c r="AB62" s="25"/>
+      <c r="AC62" s="25"/>
+      <c r="AD62" s="25"/>
+    </row>
+    <row r="64" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="B64" s="37"/>
+      <c r="C64" s="37"/>
+      <c r="D64" s="37"/>
+      <c r="E64" s="37"/>
+      <c r="F64" s="37"/>
+      <c r="G64" s="37"/>
+      <c r="H64" s="37"/>
+      <c r="I64" s="37"/>
+    </row>
+    <row r="66" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="C66" s="36"/>
+      <c r="D66" s="36"/>
+    </row>
+    <row r="67" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="C67" s="35"/>
+      <c r="D67" s="36"/>
+    </row>
+    <row r="68" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="C68" s="34"/>
+      <c r="D68" s="36"/>
+    </row>
+    <row r="69" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="C69" s="34"/>
+      <c r="D69" s="36"/>
+    </row>
+    <row r="70" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="C70" s="34"/>
+      <c r="D70" s="36"/>
+    </row>
+    <row r="71" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="C71" s="36"/>
+      <c r="D71" s="36"/>
+    </row>
+    <row r="72" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="C72" s="36"/>
+      <c r="D72" s="36"/>
+    </row>
+    <row r="73" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="C73" s="36"/>
+      <c r="D73" s="36"/>
+      <c r="E73" s="36"/>
+    </row>
+    <row r="74" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="C74" s="36"/>
+      <c r="D74" s="36"/>
+      <c r="E74" s="36"/>
+    </row>
+    <row r="75" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="C75" s="36"/>
+      <c r="D75" s="36"/>
+      <c r="E75" s="36"/>
+    </row>
+    <row r="76" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="C76" s="36"/>
+      <c r="D76" s="36"/>
+      <c r="E76" s="36"/>
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="A61:I61"/>
+    <mergeCell ref="A62:I62"/>
     <mergeCell ref="A1:I2"/>
     <mergeCell ref="B3:E3"/>
     <mergeCell ref="F3:I3"/>
@@ -6489,172 +6566,172 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B26"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="30.6640625" style="25" customWidth="1"/>
-    <col min="2" max="2" width="98.6640625" style="25" customWidth="1"/>
-    <col min="3" max="16384" width="11.44140625" style="25"/>
+    <col min="1" max="1" width="30.7109375" style="28" customWidth="1"/>
+    <col min="2" max="2" width="98.7109375" style="28" customWidth="1"/>
+    <col min="3" max="16384" width="11.42578125" style="28"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="24.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="40" t="s">
+    <row r="1" spans="1:2" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="45" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="41"/>
-    </row>
-    <row r="2" spans="1:2" ht="24.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="5" t="s">
+      <c r="B1" s="46"/>
+    </row>
+    <row r="2" spans="1:2" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="6" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="6" t="s">
+    <row r="3" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="8" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="8" t="s">
+    <row r="4" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="29" t="s">
+      <c r="B4" s="32" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="8" t="s">
+    <row r="5" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="29" t="s">
+      <c r="B5" s="32" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="9" t="s">
+    <row r="6" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="13" t="s">
+      <c r="B6" s="16" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="24.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="9" t="s">
+    <row r="7" spans="1:2" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="B7" s="13" t="s">
+      <c r="B7" s="16" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="10" t="s">
+    <row r="8" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="14" t="s">
+      <c r="B8" s="17" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+    <row r="9" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="B9" s="15" t="s">
+      <c r="B9" s="18" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="8" t="s">
+    <row r="10" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="B10" s="16" t="s">
+      <c r="B10" s="19" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="11" t="s">
+    <row r="11" spans="1:2" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="B11" s="13" t="s">
+      <c r="B11" s="33" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="10" t="s">
+    <row r="12" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="B12" s="17" t="s">
+      <c r="B12" s="20" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="8" t="s">
+    <row r="13" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="B13" s="18" t="s">
+      <c r="B13" s="21" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="8" t="s">
+    <row r="14" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="B14" s="19" t="s">
+      <c r="B14" s="22" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="24.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="11" t="s">
+    <row r="15" spans="1:2" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="B15" s="20" t="s">
+      <c r="B15" s="23" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="6" t="s">
+    <row r="16" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="B16" s="21" t="s">
+      <c r="B16" s="24" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="6" t="s">
+    <row r="17" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="B17" s="21" t="s">
+      <c r="B17" s="24" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="8" t="s">
+    <row r="18" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="B18" s="15" t="s">
+      <c r="B18" s="18" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="24.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="11" t="s">
+    <row r="19" spans="1:2" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="B19" s="12" t="s">
+      <c r="B19" s="15" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="20" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="21" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="22" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="23" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="24" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="25" spans="1:2" ht="24.9" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="26" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="20" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="21" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="22" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="23" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="24" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="25" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="26" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:B1"/>
